--- a/output/med_shocks.xlsx
+++ b/output/med_shocks.xlsx
@@ -13,7 +13,487 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="512">
+  <si>
+    <t>med_Q_2</t>
+  </si>
+  <si>
+    <t>med_Q_3</t>
+  </si>
+  <si>
+    <t>med_Q_4</t>
+  </si>
+  <si>
+    <t>med_Q_5</t>
+  </si>
+  <si>
+    <t>med_Q_6</t>
+  </si>
+  <si>
+    <t>med_Q_7</t>
+  </si>
+  <si>
+    <t>med_Q_8</t>
+  </si>
+  <si>
+    <t>med_Q_9</t>
+  </si>
+  <si>
+    <t>med_Q_10</t>
+  </si>
+  <si>
+    <t>med_Q_11</t>
+  </si>
+  <si>
+    <t>med_Q_12</t>
+  </si>
+  <si>
+    <t>med_Q_13</t>
+  </si>
+  <si>
+    <t>med_Q_14</t>
+  </si>
+  <si>
+    <t>med_Q_15</t>
+  </si>
+  <si>
+    <t>med_Q_16</t>
+  </si>
+  <si>
+    <t>med_Q_17</t>
+  </si>
+  <si>
+    <t>med_NQ_2</t>
+  </si>
+  <si>
+    <t>med_NQ_3</t>
+  </si>
+  <si>
+    <t>med_NQ_4</t>
+  </si>
+  <si>
+    <t>med_NQ_5</t>
+  </si>
+  <si>
+    <t>med_NQ_6</t>
+  </si>
+  <si>
+    <t>med_NQ_7</t>
+  </si>
+  <si>
+    <t>med_NQ_8</t>
+  </si>
+  <si>
+    <t>med_NQ_9</t>
+  </si>
+  <si>
+    <t>med_NQ_10</t>
+  </si>
+  <si>
+    <t>med_NQ_11</t>
+  </si>
+  <si>
+    <t>med_NQ_12</t>
+  </si>
+  <si>
+    <t>med_NQ_13</t>
+  </si>
+  <si>
+    <t>med_NQ_14</t>
+  </si>
+  <si>
+    <t>med_NQ_15</t>
+  </si>
+  <si>
+    <t>med_NQ_16</t>
+  </si>
+  <si>
+    <t>med_NQ_17</t>
+  </si>
+  <si>
+    <t>med_Q_2</t>
+  </si>
+  <si>
+    <t>med_Q_3</t>
+  </si>
+  <si>
+    <t>med_Q_4</t>
+  </si>
+  <si>
+    <t>med_Q_5</t>
+  </si>
+  <si>
+    <t>med_Q_6</t>
+  </si>
+  <si>
+    <t>med_Q_7</t>
+  </si>
+  <si>
+    <t>med_Q_8</t>
+  </si>
+  <si>
+    <t>med_Q_9</t>
+  </si>
+  <si>
+    <t>med_Q_10</t>
+  </si>
+  <si>
+    <t>med_Q_11</t>
+  </si>
+  <si>
+    <t>med_Q_12</t>
+  </si>
+  <si>
+    <t>med_Q_13</t>
+  </si>
+  <si>
+    <t>med_Q_14</t>
+  </si>
+  <si>
+    <t>med_Q_15</t>
+  </si>
+  <si>
+    <t>med_Q_16</t>
+  </si>
+  <si>
+    <t>med_Q_17</t>
+  </si>
+  <si>
+    <t>med_NQ_2</t>
+  </si>
+  <si>
+    <t>med_NQ_3</t>
+  </si>
+  <si>
+    <t>med_NQ_4</t>
+  </si>
+  <si>
+    <t>med_NQ_5</t>
+  </si>
+  <si>
+    <t>med_NQ_6</t>
+  </si>
+  <si>
+    <t>med_NQ_7</t>
+  </si>
+  <si>
+    <t>med_NQ_8</t>
+  </si>
+  <si>
+    <t>med_NQ_9</t>
+  </si>
+  <si>
+    <t>med_NQ_10</t>
+  </si>
+  <si>
+    <t>med_NQ_11</t>
+  </si>
+  <si>
+    <t>med_NQ_12</t>
+  </si>
+  <si>
+    <t>med_NQ_13</t>
+  </si>
+  <si>
+    <t>med_NQ_14</t>
+  </si>
+  <si>
+    <t>med_NQ_15</t>
+  </si>
+  <si>
+    <t>med_NQ_16</t>
+  </si>
+  <si>
+    <t>med_NQ_17</t>
+  </si>
+  <si>
+    <t>med_Q_2</t>
+  </si>
+  <si>
+    <t>med_Q_3</t>
+  </si>
+  <si>
+    <t>med_Q_4</t>
+  </si>
+  <si>
+    <t>med_Q_5</t>
+  </si>
+  <si>
+    <t>med_Q_6</t>
+  </si>
+  <si>
+    <t>med_Q_7</t>
+  </si>
+  <si>
+    <t>med_Q_8</t>
+  </si>
+  <si>
+    <t>med_Q_9</t>
+  </si>
+  <si>
+    <t>med_Q_10</t>
+  </si>
+  <si>
+    <t>med_Q_11</t>
+  </si>
+  <si>
+    <t>med_Q_12</t>
+  </si>
+  <si>
+    <t>med_Q_13</t>
+  </si>
+  <si>
+    <t>med_Q_14</t>
+  </si>
+  <si>
+    <t>med_Q_15</t>
+  </si>
+  <si>
+    <t>med_Q_16</t>
+  </si>
+  <si>
+    <t>med_Q_17</t>
+  </si>
+  <si>
+    <t>med_NQ_2</t>
+  </si>
+  <si>
+    <t>med_NQ_3</t>
+  </si>
+  <si>
+    <t>med_NQ_4</t>
+  </si>
+  <si>
+    <t>med_NQ_5</t>
+  </si>
+  <si>
+    <t>med_NQ_6</t>
+  </si>
+  <si>
+    <t>med_NQ_7</t>
+  </si>
+  <si>
+    <t>med_NQ_8</t>
+  </si>
+  <si>
+    <t>med_NQ_9</t>
+  </si>
+  <si>
+    <t>med_NQ_10</t>
+  </si>
+  <si>
+    <t>med_NQ_11</t>
+  </si>
+  <si>
+    <t>med_NQ_12</t>
+  </si>
+  <si>
+    <t>med_NQ_13</t>
+  </si>
+  <si>
+    <t>med_NQ_14</t>
+  </si>
+  <si>
+    <t>med_NQ_15</t>
+  </si>
+  <si>
+    <t>med_NQ_16</t>
+  </si>
+  <si>
+    <t>med_NQ_17</t>
+  </si>
+  <si>
+    <t>med_Q_2</t>
+  </si>
+  <si>
+    <t>med_Q_3</t>
+  </si>
+  <si>
+    <t>med_Q_4</t>
+  </si>
+  <si>
+    <t>med_Q_5</t>
+  </si>
+  <si>
+    <t>med_Q_6</t>
+  </si>
+  <si>
+    <t>med_Q_7</t>
+  </si>
+  <si>
+    <t>med_Q_8</t>
+  </si>
+  <si>
+    <t>med_Q_9</t>
+  </si>
+  <si>
+    <t>med_Q_10</t>
+  </si>
+  <si>
+    <t>med_Q_11</t>
+  </si>
+  <si>
+    <t>med_Q_12</t>
+  </si>
+  <si>
+    <t>med_Q_13</t>
+  </si>
+  <si>
+    <t>med_Q_14</t>
+  </si>
+  <si>
+    <t>med_Q_15</t>
+  </si>
+  <si>
+    <t>med_Q_16</t>
+  </si>
+  <si>
+    <t>med_Q_17</t>
+  </si>
+  <si>
+    <t>med_NQ_2</t>
+  </si>
+  <si>
+    <t>med_NQ_3</t>
+  </si>
+  <si>
+    <t>med_NQ_4</t>
+  </si>
+  <si>
+    <t>med_NQ_5</t>
+  </si>
+  <si>
+    <t>med_NQ_6</t>
+  </si>
+  <si>
+    <t>med_NQ_7</t>
+  </si>
+  <si>
+    <t>med_NQ_8</t>
+  </si>
+  <si>
+    <t>med_NQ_9</t>
+  </si>
+  <si>
+    <t>med_NQ_10</t>
+  </si>
+  <si>
+    <t>med_NQ_11</t>
+  </si>
+  <si>
+    <t>med_NQ_12</t>
+  </si>
+  <si>
+    <t>med_NQ_13</t>
+  </si>
+  <si>
+    <t>med_NQ_14</t>
+  </si>
+  <si>
+    <t>med_NQ_15</t>
+  </si>
+  <si>
+    <t>med_NQ_16</t>
+  </si>
+  <si>
+    <t>med_NQ_17</t>
+  </si>
+  <si>
+    <t>med_Q_2</t>
+  </si>
+  <si>
+    <t>med_Q_3</t>
+  </si>
+  <si>
+    <t>med_Q_4</t>
+  </si>
+  <si>
+    <t>med_Q_5</t>
+  </si>
+  <si>
+    <t>med_Q_6</t>
+  </si>
+  <si>
+    <t>med_Q_7</t>
+  </si>
+  <si>
+    <t>med_Q_8</t>
+  </si>
+  <si>
+    <t>med_Q_9</t>
+  </si>
+  <si>
+    <t>med_Q_10</t>
+  </si>
+  <si>
+    <t>med_Q_11</t>
+  </si>
+  <si>
+    <t>med_Q_12</t>
+  </si>
+  <si>
+    <t>med_Q_13</t>
+  </si>
+  <si>
+    <t>med_Q_14</t>
+  </si>
+  <si>
+    <t>med_Q_15</t>
+  </si>
+  <si>
+    <t>med_Q_16</t>
+  </si>
+  <si>
+    <t>med_Q_17</t>
+  </si>
+  <si>
+    <t>med_NQ_2</t>
+  </si>
+  <si>
+    <t>med_NQ_3</t>
+  </si>
+  <si>
+    <t>med_NQ_4</t>
+  </si>
+  <si>
+    <t>med_NQ_5</t>
+  </si>
+  <si>
+    <t>med_NQ_6</t>
+  </si>
+  <si>
+    <t>med_NQ_7</t>
+  </si>
+  <si>
+    <t>med_NQ_8</t>
+  </si>
+  <si>
+    <t>med_NQ_9</t>
+  </si>
+  <si>
+    <t>med_NQ_10</t>
+  </si>
+  <si>
+    <t>med_NQ_11</t>
+  </si>
+  <si>
+    <t>med_NQ_12</t>
+  </si>
+  <si>
+    <t>med_NQ_13</t>
+  </si>
+  <si>
+    <t>med_NQ_14</t>
+  </si>
+  <si>
+    <t>med_NQ_15</t>
+  </si>
+  <si>
+    <t>med_NQ_16</t>
+  </si>
+  <si>
+    <t>med_NQ_17</t>
+  </si>
   <si>
     <t>med_Q_2</t>
   </si>
@@ -1089,7 +1569,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1108,11 +1588,16 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
@@ -1125,6 +1610,11 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1138,4046 +1628,4046 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="true"/>
-    <col min="2" max="2" width="12.42578125" customWidth="true"/>
-    <col min="3" max="3" width="12.42578125" customWidth="true"/>
-    <col min="4" max="4" width="12.42578125" customWidth="true"/>
-    <col min="5" max="5" width="12.42578125" customWidth="true"/>
-    <col min="6" max="6" width="12.42578125" customWidth="true"/>
-    <col min="7" max="7" width="12.42578125" customWidth="true"/>
-    <col min="8" max="8" width="12.42578125" customWidth="true"/>
-    <col min="9" max="9" width="12.42578125" customWidth="true"/>
-    <col min="10" max="10" width="12.42578125" customWidth="true"/>
-    <col min="11" max="11" width="12.42578125" customWidth="true"/>
-    <col min="12" max="12" width="12.42578125" customWidth="true"/>
-    <col min="13" max="13" width="12.42578125" customWidth="true"/>
-    <col min="14" max="14" width="12.42578125" customWidth="true"/>
-    <col min="15" max="15" width="12.42578125" customWidth="true"/>
-    <col min="16" max="16" width="12.42578125" customWidth="true"/>
-    <col min="17" max="17" width="12.42578125" customWidth="true"/>
-    <col min="18" max="18" width="15.5703125" customWidth="true"/>
-    <col min="19" max="19" width="12.42578125" customWidth="true"/>
-    <col min="20" max="20" width="12.42578125" customWidth="true"/>
-    <col min="21" max="21" width="12.42578125" customWidth="true"/>
-    <col min="22" max="22" width="12.42578125" customWidth="true"/>
-    <col min="23" max="23" width="12.42578125" customWidth="true"/>
-    <col min="24" max="24" width="12.42578125" customWidth="true"/>
-    <col min="25" max="25" width="12.42578125" customWidth="true"/>
-    <col min="26" max="26" width="12.42578125" customWidth="true"/>
-    <col min="27" max="27" width="12.42578125" customWidth="true"/>
-    <col min="28" max="28" width="12.42578125" customWidth="true"/>
-    <col min="29" max="29" width="12.42578125" customWidth="true"/>
-    <col min="30" max="30" width="12.42578125" customWidth="true"/>
-    <col min="31" max="31" width="12.42578125" customWidth="true"/>
-    <col min="32" max="32" width="12.42578125" customWidth="true"/>
-    <col min="33" max="33" width="12.42578125" customWidth="true"/>
-    <col min="34" max="34" width="12.42578125" customWidth="true"/>
-    <col min="35" max="35" width="12.42578125" customWidth="true"/>
-    <col min="36" max="36" width="12.42578125" customWidth="true"/>
-    <col min="37" max="37" width="12.42578125" customWidth="true"/>
-    <col min="38" max="38" width="12.42578125" customWidth="true"/>
-    <col min="39" max="39" width="12.42578125" customWidth="true"/>
-    <col min="40" max="40" width="12.42578125" customWidth="true"/>
-    <col min="41" max="41" width="12.42578125" customWidth="true"/>
+    <col min="2" max="2" width="13.42578125" customWidth="true"/>
+    <col min="3" max="3" width="14.42578125" customWidth="true"/>
+    <col min="4" max="4" width="14.42578125" customWidth="true"/>
+    <col min="5" max="5" width="14.42578125" customWidth="true"/>
+    <col min="6" max="6" width="14.42578125" customWidth="true"/>
+    <col min="7" max="7" width="14.42578125" customWidth="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true"/>
+    <col min="9" max="9" width="14.42578125" customWidth="true"/>
+    <col min="10" max="10" width="14.42578125" customWidth="true"/>
+    <col min="11" max="11" width="14.42578125" customWidth="true"/>
+    <col min="12" max="12" width="14.42578125" customWidth="true"/>
+    <col min="13" max="13" width="14.42578125" customWidth="true"/>
+    <col min="14" max="14" width="14.42578125" customWidth="true"/>
+    <col min="15" max="15" width="14.42578125" customWidth="true"/>
+    <col min="16" max="16" width="16.42578125" customWidth="true"/>
+    <col min="17" max="17" width="13.42578125" customWidth="true"/>
+    <col min="18" max="18" width="14.42578125" customWidth="true"/>
+    <col min="19" max="19" width="14.42578125" customWidth="true"/>
+    <col min="20" max="20" width="14.42578125" customWidth="true"/>
+    <col min="21" max="21" width="14.42578125" customWidth="true"/>
+    <col min="22" max="22" width="15.42578125" customWidth="true"/>
+    <col min="23" max="23" width="15.42578125" customWidth="true"/>
+    <col min="24" max="24" width="14.42578125" customWidth="true"/>
+    <col min="25" max="25" width="15.42578125" customWidth="true"/>
+    <col min="26" max="26" width="15.42578125" customWidth="true"/>
+    <col min="27" max="27" width="14.42578125" customWidth="true"/>
+    <col min="28" max="28" width="14.42578125" customWidth="true"/>
+    <col min="29" max="29" width="13.7109375" customWidth="true"/>
+    <col min="30" max="30" width="15.42578125" customWidth="true"/>
+    <col min="31" max="31" width="13.7109375" customWidth="true"/>
+    <col min="32" max="32" width="14.42578125" customWidth="true"/>
+    <col min="33" max="33" width="14.42578125" customWidth="true"/>
+    <col min="34" max="34" width="14.42578125" customWidth="true"/>
+    <col min="35" max="35" width="14.7109375" customWidth="true"/>
+    <col min="36" max="36" width="14.7109375" customWidth="true"/>
+    <col min="37" max="37" width="15.7109375" customWidth="true"/>
+    <col min="38" max="38" width="14.42578125" customWidth="true"/>
+    <col min="39" max="39" width="14.42578125" customWidth="true"/>
+    <col min="40" max="40" width="14.7109375" customWidth="true"/>
+    <col min="41" max="41" width="14.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>320</v>
+        <v>480</v>
       </c>
       <c r="B1" s="0">
-        <v>-116.6265636</v>
+        <v>13.763688546684229</v>
       </c>
       <c r="C1" s="0">
-        <v>-116.62574909999999</v>
+        <v>13.841670305400051</v>
       </c>
       <c r="D1" s="0">
-        <v>-116.6390809</v>
+        <v>12.660744399169122</v>
       </c>
       <c r="E1" s="0">
-        <v>-116.6842192</v>
+        <v>9.7627508539483259</v>
       </c>
       <c r="F1" s="0">
-        <v>-116.6216841</v>
+        <v>14.243527392431025</v>
       </c>
       <c r="G1" s="0">
-        <v>-116.619907</v>
+        <v>14.426135269246705</v>
       </c>
       <c r="H1" s="0">
-        <v>-116.61752879999999</v>
+        <v>14.677475766554258</v>
       </c>
       <c r="I1" s="0">
-        <v>-116.61592309999999</v>
+        <v>14.851863865250989</v>
       </c>
       <c r="J1" s="0">
-        <v>-116.63733169999999</v>
+        <v>12.804849116217531</v>
       </c>
       <c r="K1" s="0">
-        <v>-116.6135733</v>
+        <v>15.114183338103517</v>
       </c>
       <c r="L1" s="0">
-        <v>-116.60640889999999</v>
+        <v>15.970490714943528</v>
       </c>
       <c r="M1" s="0">
-        <v>-116.60520529999999</v>
+        <v>16.123368629965043</v>
       </c>
       <c r="N1" s="0">
-        <v>-116.6045633</v>
+        <v>16.206046887829441</v>
       </c>
       <c r="O1" s="0">
-        <v>-116.60424519999999</v>
+        <v>16.247309408568917</v>
       </c>
       <c r="P1" s="0">
-        <v>-116.60405619999999</v>
+        <v>16.271919618840013</v>
       </c>
       <c r="Q1" s="0">
-        <v>-116.6036321</v>
+        <v>16.327399581392051</v>
       </c>
       <c r="R1" s="0">
-        <v>-116.6036742</v>
+        <v>16.32187619079075</v>
       </c>
       <c r="S1" s="0">
-        <v>-116.60361709999999</v>
+        <v>16.329368387467124</v>
       </c>
       <c r="T1" s="0">
-        <v>-116.6038878</v>
+        <v>16.293906757967036</v>
       </c>
       <c r="U1" s="0">
-        <v>-116.60313309999999</v>
+        <v>16.393136484121637</v>
       </c>
       <c r="V1" s="0">
-        <v>-116.60205269999999</v>
+        <v>16.537190677403942</v>
       </c>
       <c r="W1" s="0">
-        <v>-116.60171919999999</v>
+        <v>16.582141371766326</v>
       </c>
       <c r="X1" s="0">
-        <v>-116.6015623</v>
+        <v>16.603368983842415</v>
       </c>
       <c r="Y1" s="0">
-        <v>-116.6014321</v>
+        <v>16.621023248420922</v>
       </c>
       <c r="Z1" s="0">
-        <v>-116.6013672</v>
+        <v>16.629836508323883</v>
       </c>
       <c r="AA1" s="0">
-        <v>-116.60125319999999</v>
+        <v>16.645338813776547</v>
       </c>
       <c r="AB1" s="0">
-        <v>-116.60114449999999</v>
+        <v>16.66014583946971</v>
       </c>
       <c r="AC1" s="0">
-        <v>-116.60104559999999</v>
+        <v>16.673639549032011</v>
       </c>
       <c r="AD1" s="0">
-        <v>-116.60095559999999</v>
+        <v>16.685936914494885</v>
       </c>
       <c r="AE1" s="0">
-        <v>-116.6008736</v>
+        <v>16.697156106099861</v>
       </c>
       <c r="AF1" s="0">
-        <v>-116.6007989</v>
+        <v>16.707388926810324</v>
       </c>
       <c r="AG1" s="0">
-        <v>-116.60073089999999</v>
+        <v>16.716714250533187</v>
       </c>
       <c r="AH1" s="0">
-        <v>-116.60066889999999</v>
+        <v>16.725225325706155</v>
       </c>
       <c r="AI1" s="0">
-        <v>-116.60061239999999</v>
+        <v>16.732988518781337</v>
       </c>
       <c r="AJ1" s="0">
-        <v>-116.60056089999999</v>
+        <v>16.740070636792751</v>
       </c>
       <c r="AK1" s="0">
-        <v>-116.6005139</v>
+        <v>16.74653887334723</v>
       </c>
       <c r="AL1" s="0">
-        <v>-116.60047089999999</v>
+        <v>16.752460759457247</v>
       </c>
       <c r="AM1" s="0">
-        <v>-116.6004318</v>
+        <v>16.75784897993616</v>
       </c>
       <c r="AN1" s="0">
-        <v>-116.6003961</v>
+        <v>16.762771520113017</v>
       </c>
       <c r="AO1" s="0">
-        <v>-116.6003635</v>
+        <v>16.767269000027493</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>321</v>
+        <v>481</v>
       </c>
       <c r="B2" s="0">
-        <v>-116.62946099999999</v>
+        <v>4.6728152077517064</v>
       </c>
       <c r="C2" s="0">
-        <v>0.017083028000010714</v>
+        <v>0.071112428963982385</v>
       </c>
       <c r="D2" s="0">
-        <v>0.0087946179999907059</v>
+        <v>-0.66570656558753949</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.014750017999991982</v>
+        <v>-2.0290593162406791</v>
       </c>
       <c r="F2" s="0">
-        <v>0.07935921600000917</v>
+        <v>4.5456791432856338</v>
       </c>
       <c r="G2" s="0">
-        <v>0.019434118000001277</v>
+        <v>0.29105903064158495</v>
       </c>
       <c r="H2" s="0">
-        <v>0.019699860000011782</v>
+        <v>0.31832034131072012</v>
       </c>
       <c r="I2" s="0">
-        <v>0.018527923999991813</v>
+        <v>0.19360958724971558</v>
       </c>
       <c r="J2" s="0">
-        <v>0.0052193379999838641</v>
+        <v>-1.1267409139238747</v>
       </c>
       <c r="K2" s="0">
-        <v>0.044058265999987967</v>
+        <v>2.7046756030447567</v>
       </c>
       <c r="L2" s="0">
-        <v>0.024960534000010526</v>
+        <v>0.93837843227430406</v>
       </c>
       <c r="M2" s="0">
-        <v>0.019432021999984173</v>
+        <v>0.28382720186636112</v>
       </c>
       <c r="N2" s="0">
-        <v>0.01895939400000124</v>
+        <v>0.22287933282620914</v>
       </c>
       <c r="O2" s="0">
-        <v>0.018643333999998291</v>
+        <v>0.18151749067296744</v>
       </c>
       <c r="P2" s="0">
-        <v>0.018798695999999282</v>
+        <v>0.20059699979948042</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.019166375999995822</v>
+        <v>0.24746827561451679</v>
       </c>
       <c r="R2" s="0">
-        <v>0.018908058000002725</v>
+        <v>0.21340228659883984</v>
       </c>
       <c r="S2" s="0">
-        <v>0.019006115999994577</v>
+        <v>0.22615880274326181</v>
       </c>
       <c r="T2" s="0">
-        <v>0.018743158000001259</v>
+        <v>0.19208391980472106</v>
       </c>
       <c r="U2" s="0">
-        <v>0.019733143999994596</v>
+        <v>0.32079216377166492</v>
       </c>
       <c r="V2" s="0">
-        <v>0.020360137999995587</v>
+        <v>0.40355331583391252</v>
       </c>
       <c r="W2" s="0">
-        <v>0.019743345999993167</v>
+        <v>0.32140649463286186</v>
       </c>
       <c r="X2" s="0">
-        <v>0.019728515999995366</v>
+        <v>0.31926171622851351</v>
       </c>
       <c r="Y2" s="0">
-        <v>0.01965295400000322</v>
+        <v>0.30899374240018018</v>
       </c>
       <c r="Z2" s="0">
-        <v>0.019600958000006941</v>
+        <v>0.30188942273143249</v>
       </c>
       <c r="AA2" s="0">
-        <v>0.019698956000008039</v>
+        <v>0.31508869493819708</v>
       </c>
       <c r="AB2" s="0">
-        <v>0.019728135999992347</v>
+        <v>0.31897999617784029</v>
       </c>
       <c r="AC2" s="0">
-        <v>0.019750009999990326</v>
+        <v>0.32189579760358061</v>
       </c>
       <c r="AD2" s="0">
-        <v>0.019769987999987748</v>
+        <v>0.32456790082080211</v>
       </c>
       <c r="AE2" s="0">
-        <v>0.01978838800000382</v>
+        <v>0.32703687586918812</v>
       </c>
       <c r="AF2" s="0">
-        <v>0.01980512799999623</v>
+        <v>0.32928926753684351</v>
       </c>
       <c r="AG2" s="0">
-        <v>0.019820521999998064</v>
+        <v>0.33136603364779038</v>
       </c>
       <c r="AH2" s="0">
-        <v>0.019834581999996104</v>
+        <v>0.33326726910714166</v>
       </c>
       <c r="AI2" s="0">
-        <v>0.019847521999986739</v>
+        <v>0.33502090544470747</v>
       </c>
       <c r="AJ2" s="0">
-        <v>0.019859351999992114</v>
+        <v>0.33662723316398335</v>
       </c>
       <c r="AK2" s="0">
-        <v>0.019870281999994077</v>
+        <v>0.33811413410954511</v>
       </c>
       <c r="AL2" s="0">
-        <v>0.019880322000000561</v>
+        <v>0.33948221499234915</v>
       </c>
       <c r="AM2" s="0">
-        <v>0.019889381999997013</v>
+        <v>0.34071842191046497</v>
       </c>
       <c r="AN2" s="0">
-        <v>0.019897764000001317</v>
+        <v>0.34186378307192261</v>
       </c>
       <c r="AO2" s="0">
-        <v>0.019905578000001256</v>
+        <v>0.34293297406447393</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>322</v>
+        <v>482</v>
       </c>
       <c r="B3" s="0">
-        <v>-116.63425579999998</v>
+        <v>4.2457758651727842</v>
       </c>
       <c r="C3" s="0">
-        <v>0.015369580000005101</v>
+        <v>-0.072142068225175521</v>
       </c>
       <c r="D3" s="0">
-        <v>0.012446914000001641</v>
+        <v>-0.32642781267680782</v>
       </c>
       <c r="E3" s="0">
-        <v>0.0020088100000137388</v>
+        <v>-1.0377463128940123</v>
       </c>
       <c r="F3" s="0">
-        <v>0.06434441399999713</v>
+        <v>3.5670887177465382</v>
       </c>
       <c r="G3" s="0">
-        <v>0.016155388000008486</v>
+        <v>-0.027757761363267942</v>
       </c>
       <c r="H3" s="0">
-        <v>0.0168477740000057</v>
+        <v>0.033814188109069956</v>
       </c>
       <c r="I3" s="0">
-        <v>0.015608620000001849</v>
+        <v>-0.096748243119955585</v>
       </c>
       <c r="J3" s="0">
-        <v>0.007067594000012889</v>
+        <v>-0.91308162986310015</v>
       </c>
       <c r="K3" s="0">
-        <v>0.034472194000009893</v>
+        <v>1.7992726831117625</v>
       </c>
       <c r="L3" s="0">
-        <v>0.02068826400000745</v>
+        <v>0.43313166400542391</v>
       </c>
       <c r="M3" s="0">
-        <v>0.018215173999998058</v>
+        <v>0.13857660857771562</v>
       </c>
       <c r="N3" s="0">
-        <v>0.01760972600002475</v>
+        <v>0.060723660408635152</v>
       </c>
       <c r="O3" s="0">
-        <v>0.016995464000011395</v>
+        <v>-0.016867941373918911</v>
       </c>
       <c r="P3" s="0">
-        <v>0.017181126000004099</v>
+        <v>0.0041348444385134325</v>
       </c>
       <c r="Q3" s="0">
-        <v>0.017633468000006758</v>
+        <v>0.057589869801941355</v>
       </c>
       <c r="R3" s="0">
-        <v>0.017702626000009047</v>
+        <v>0.063909368098273064</v>
       </c>
       <c r="S3" s="0">
-        <v>0.017938872000009098</v>
+        <v>0.092860592213634782</v>
       </c>
       <c r="T3" s="0">
-        <v>0.017919708000015078</v>
+        <v>0.090245460387550061</v>
       </c>
       <c r="U3" s="0">
-        <v>0.018725968000005366</v>
+        <v>0.19254500504856598</v>
       </c>
       <c r="V3" s="0">
-        <v>0.019690062000016439</v>
+        <v>0.31526195817079627</v>
       </c>
       <c r="W3" s="0">
-        <v>0.019031394000016633</v>
+        <v>0.22772827421082284</v>
       </c>
       <c r="X3" s="0">
-        <v>0.019077634000005617</v>
+        <v>0.23303504334469735</v>
       </c>
       <c r="Y3" s="0">
-        <v>0.019093474000023036</v>
+        <v>0.23459033793745981</v>
       </c>
       <c r="Z3" s="0">
-        <v>0.019175138000015579</v>
+        <v>0.24532355158059896</v>
       </c>
       <c r="AA3" s="0">
-        <v>0.01932175000001024</v>
+        <v>0.26477402364655456</v>
       </c>
       <c r="AB3" s="0">
-        <v>0.019368782000007911</v>
+        <v>0.27086619961583891</v>
       </c>
       <c r="AC3" s="0">
-        <v>0.01941810000000288</v>
+        <v>0.27732243682405194</v>
       </c>
       <c r="AD3" s="0">
-        <v>0.019463268000002643</v>
+        <v>0.28326396675860144</v>
       </c>
       <c r="AE3" s="0">
-        <v>0.019504806000007591</v>
+        <v>0.28875270753839516</v>
       </c>
       <c r="AF3" s="0">
-        <v>0.019542838000013774</v>
+        <v>0.2937983016290367</v>
       </c>
       <c r="AG3" s="0">
-        <v>0.019577880000021253</v>
+        <v>0.2984648691395797</v>
       </c>
       <c r="AH3" s="0">
-        <v>0.019609952000017472</v>
+        <v>0.30275011016091563</v>
       </c>
       <c r="AI3" s="0">
-        <v>0.019639566000002162</v>
+        <v>0.3067195988264334</v>
       </c>
       <c r="AJ3" s="0">
-        <v>0.019666840000020613</v>
+        <v>0.31038585573442545</v>
       </c>
       <c r="AK3" s="0">
-        <v>0.019691884000017978</v>
+        <v>0.31376106299279</v>
       </c>
       <c r="AL3" s="0">
-        <v>0.019714912000004858</v>
+        <v>0.31687188997003873</v>
       </c>
       <c r="AM3" s="0">
-        <v>0.019736134000019945</v>
+        <v>0.31974500579721754</v>
       </c>
       <c r="AN3" s="0">
-        <v>0.01975565800001533</v>
+        <v>0.32239350389829635</v>
       </c>
       <c r="AO3" s="0">
-        <v>0.019773792000016499</v>
+        <v>0.32485815741776086</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>323</v>
+        <v>483</v>
       </c>
       <c r="B4" s="0">
-        <v>-116.63882369999999</v>
+        <v>3.8617441345936458</v>
       </c>
       <c r="C4" s="0">
-        <v>0.014174184000012247</v>
+        <v>-0.14979585347489208</v>
       </c>
       <c r="D4" s="0">
-        <v>0.015257056000010039</v>
+        <v>-0.064377547956065193</v>
       </c>
       <c r="E4" s="0">
-        <v>0.009931432000016116</v>
+        <v>-0.471110831628968</v>
       </c>
       <c r="F4" s="0">
-        <v>0.041102061999993111</v>
+        <v>1.9920741010088645</v>
       </c>
       <c r="G4" s="0">
-        <v>0.014799121999999443</v>
+        <v>-0.1331939291429341</v>
       </c>
       <c r="H4" s="0">
-        <v>0.015946765999999002</v>
+        <v>-0.033118382580705097</v>
       </c>
       <c r="I4" s="0">
-        <v>0.014546355999996763</v>
+        <v>-0.17125586517384622</v>
       </c>
       <c r="J4" s="0">
-        <v>0.0081761160000013433</v>
+        <v>-0.74229524012292802</v>
       </c>
       <c r="K4" s="0">
-        <v>0.03089850599999977</v>
+        <v>1.4012332189599792</v>
       </c>
       <c r="L4" s="0">
-        <v>0.018094592000011289</v>
+        <v>0.1428093052771269</v>
       </c>
       <c r="M4" s="0">
-        <v>0.016763040000014939</v>
+        <v>-0.016962255357252546</v>
       </c>
       <c r="N4" s="0">
-        <v>0.016427014000015561</v>
+        <v>-0.063251766051471162</v>
       </c>
       <c r="O4" s="0">
-        <v>0.015559859999996206</v>
+        <v>-0.16734842872738823</v>
       </c>
       <c r="P4" s="0">
-        <v>0.015825930000005428</v>
+        <v>-0.13752451561889137</v>
       </c>
       <c r="Q4" s="0">
-        <v>0.015995880000005513</v>
+        <v>-0.12120867534074153</v>
       </c>
       <c r="R4" s="0">
-        <v>0.016642982000007578</v>
+        <v>-0.051119905340607563</v>
       </c>
       <c r="S4" s="0">
-        <v>0.016954401999996094</v>
+        <v>-0.017367738329386127</v>
       </c>
       <c r="T4" s="0">
-        <v>0.017318610000003787</v>
+        <v>0.024542451217253087</v>
       </c>
       <c r="U4" s="0">
-        <v>0.017528540000014914</v>
+        <v>0.049805074729334917</v>
       </c>
       <c r="V4" s="0">
-        <v>0.018535208000002967</v>
+        <v>0.17136388189526772</v>
       </c>
       <c r="W4" s="0">
-        <v>0.018112594000001536</v>
+        <v>0.11352206648272711</v>
       </c>
       <c r="X4" s="0">
-        <v>0.018332106000002568</v>
+        <v>0.13926864399558758</v>
       </c>
       <c r="Y4" s="0">
-        <v>0.018412694000005558</v>
+        <v>0.14819636356677515</v>
       </c>
       <c r="Z4" s="0">
-        <v>0.018509425999994278</v>
+        <v>0.15980677872163215</v>
       </c>
       <c r="AA4" s="0">
-        <v>0.018762691999995695</v>
+        <v>0.19242741018098053</v>
       </c>
       <c r="AB4" s="0">
-        <v>0.018867306000004191</v>
+        <v>0.2056511934430566</v>
       </c>
       <c r="AC4" s="0">
-        <v>0.018959014000003549</v>
+        <v>0.21730859432279351</v>
       </c>
       <c r="AD4" s="0">
-        <v>0.019042862000006266</v>
+        <v>0.22804412478530497</v>
       </c>
       <c r="AE4" s="0">
-        <v>0.01911968200001013</v>
+        <v>0.23794556004482573</v>
       </c>
       <c r="AF4" s="0">
-        <v>0.019189904000000979</v>
+        <v>0.2470511397849609</v>
       </c>
       <c r="AG4" s="0">
-        <v>0.019254253999989146</v>
+        <v>0.25544183656815578</v>
       </c>
       <c r="AH4" s="0">
-        <v>0.019313257999996836</v>
+        <v>0.26317463864208335</v>
       </c>
       <c r="AI4" s="0">
-        <v>0.01936743600001023</v>
+        <v>0.27030834937208936</v>
       </c>
       <c r="AJ4" s="0">
-        <v>0.019417010000012169</v>
+        <v>0.27686330119286268</v>
       </c>
       <c r="AK4" s="0">
-        <v>0.019462400000008984</v>
+        <v>0.28288805762769687</v>
       </c>
       <c r="AL4" s="0">
-        <v>0.019504118000000403</v>
+        <v>0.28844543347058466</v>
       </c>
       <c r="AM4" s="0">
-        <v>0.019542482000019845</v>
+        <v>0.2935728207266981</v>
       </c>
       <c r="AN4" s="0">
-        <v>0.019577706000006856</v>
+        <v>0.29829458291122551</v>
       </c>
       <c r="AO4" s="0">
-        <v>0.019610000000000127</v>
+        <v>0.30263539596233013</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>324</v>
+        <v>484</v>
       </c>
       <c r="B5" s="0">
-        <v>-116.64488369999999</v>
+        <v>3.3835441160236299</v>
       </c>
       <c r="C5" s="0">
-        <v>0.011476025999996864</v>
+        <v>-0.3322257951734176</v>
       </c>
       <c r="D5" s="0">
-        <v>0.014914470000007896</v>
+        <v>-0.068005746648356444</v>
       </c>
       <c r="E5" s="0">
-        <v>0.0097191980000133071</v>
+        <v>-0.47274054849669062</v>
       </c>
       <c r="F5" s="0">
-        <v>0.025667830000003278</v>
+        <v>0.78100115493630295</v>
       </c>
       <c r="G5" s="0">
-        <v>0.011624084000004586</v>
+        <v>-0.3748117461835504</v>
       </c>
       <c r="H5" s="0">
-        <v>0.013315802000008148</v>
+        <v>-0.23346862264039805</v>
       </c>
       <c r="I5" s="0">
-        <v>0.011636523999996484</v>
+        <v>-0.3854106768861843</v>
       </c>
       <c r="J5" s="0">
-        <v>0.0079255960000068626</v>
+        <v>-0.69259646011069032</v>
       </c>
       <c r="K5" s="0">
-        <v>0.027734559999998964</v>
+        <v>1.0399777588704404</v>
       </c>
       <c r="L5" s="0">
-        <v>0.014352060000007327</v>
+        <v>-0.22062648256635006</v>
       </c>
       <c r="M5" s="0">
-        <v>0.014455206000008047</v>
+        <v>-0.23003876679054727</v>
       </c>
       <c r="N5" s="0">
-        <v>0.01436923599999318</v>
+        <v>-0.256155999663847</v>
       </c>
       <c r="O5" s="0">
-        <v>0.01326733800000568</v>
+        <v>-0.381694964504738</v>
       </c>
       <c r="P5" s="0">
-        <v>0.014286298000001807</v>
+        <v>-0.27462567425654688</v>
       </c>
       <c r="Q5" s="0">
-        <v>0.014175758000007477</v>
+        <v>-0.28913135804615658</v>
       </c>
       <c r="R5" s="0">
-        <v>0.01517881000000898</v>
+        <v>-0.18674372455276722</v>
       </c>
       <c r="S5" s="0">
-        <v>0.015799890000010919</v>
+        <v>-0.12878305153647926</v>
       </c>
       <c r="T5" s="0">
-        <v>0.016807294000017237</v>
+        <v>-0.020049000013961489</v>
       </c>
       <c r="U5" s="0">
-        <v>0.016585930000005078</v>
+        <v>-0.049343955441005519</v>
       </c>
       <c r="V5" s="0">
-        <v>0.01700744400000076</v>
+        <v>-0.0017190078717112783</v>
       </c>
       <c r="W5" s="0">
-        <v>0.016650804000008179</v>
+        <v>-0.051834133435987056</v>
       </c>
       <c r="X5" s="0">
-        <v>0.017013468000001808</v>
+        <v>-0.014866914208949249</v>
       </c>
       <c r="Y5" s="0">
-        <v>0.017117098000014153</v>
+        <v>-0.0067313383491606092</v>
       </c>
       <c r="Z5" s="0">
-        <v>0.017169105999997214</v>
+        <v>-0.003095781966734761</v>
       </c>
       <c r="AA5" s="0">
-        <v>0.017463544000008824</v>
+        <v>0.031627239163851753</v>
       </c>
       <c r="AB5" s="0">
-        <v>0.017620312000019567</v>
+        <v>0.049529211978822825</v>
       </c>
       <c r="AC5" s="0">
-        <v>0.01781443000000138</v>
+        <v>0.072805023745590544</v>
       </c>
       <c r="AD5" s="0">
-        <v>0.01799179000001061</v>
+        <v>0.09432619815697095</v>
       </c>
       <c r="AE5" s="0">
-        <v>0.018154039999998872</v>
+        <v>0.11423088030835205</v>
       </c>
       <c r="AF5" s="0">
-        <v>0.018302528000006646</v>
+        <v>0.13263060914101318</v>
       </c>
       <c r="AG5" s="0">
-        <v>0.018438492000015572</v>
+        <v>0.14963426207182526</v>
       </c>
       <c r="AH5" s="0">
-        <v>0.018562972000012223</v>
+        <v>0.16533289788822461</v>
       </c>
       <c r="AI5" s="0">
-        <v>0.018677003999997055</v>
+        <v>0.17982471815499454</v>
       </c>
       <c r="AJ5" s="0">
-        <v>0.018781418000003214</v>
+        <v>0.1931876338980304</v>
       </c>
       <c r="AK5" s="0">
-        <v>0.01887724000000901</v>
+        <v>0.20553095894470491</v>
       </c>
       <c r="AL5" s="0">
-        <v>0.018965098000009561</v>
+        <v>0.21691543827766596</v>
       </c>
       <c r="AM5" s="0">
-        <v>0.019045813999994721</v>
+        <v>0.22743181429020806</v>
       </c>
       <c r="AN5" s="0">
-        <v>0.01911981199999957</v>
+        <v>0.23712057712049145</v>
       </c>
       <c r="AO5" s="0">
-        <v>0.019187610000003019</v>
+        <v>0.24603770472634595</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>325</v>
+        <v>485</v>
       </c>
       <c r="B6" s="0">
-        <v>-116.65981599999999</v>
+        <v>2.3367529798354454</v>
       </c>
       <c r="C6" s="0">
-        <v>0.0029769260000023223</v>
+        <v>-0.85963302942240349</v>
       </c>
       <c r="D6" s="0">
-        <v>0.007738376000006042</v>
+        <v>-0.53357283927478494</v>
       </c>
       <c r="E6" s="0">
-        <v>0.0031467179999964401</v>
+        <v>-0.8633059408110223</v>
       </c>
       <c r="F6" s="0">
-        <v>0.013419011999999952</v>
+        <v>-0.14521493883917475</v>
       </c>
       <c r="G6" s="0">
-        <v>0.0050273960000026818</v>
+        <v>-0.79820379927726548</v>
       </c>
       <c r="H6" s="0">
-        <v>0.0071907760000158305</v>
+        <v>-0.63997815452746809</v>
       </c>
       <c r="I6" s="0">
-        <v>0.0060024780000134115</v>
+        <v>-0.73862937929175099</v>
       </c>
       <c r="J6" s="0">
-        <v>0.0031158860000033428</v>
+        <v>-0.94147731753397457</v>
       </c>
       <c r="K6" s="0">
-        <v>0.022219605999993064</v>
+        <v>0.51641646968585486</v>
       </c>
       <c r="L6" s="0">
-        <v>0.0089165119999989884</v>
+        <v>-0.64423278370507031</v>
       </c>
       <c r="M6" s="0">
-        <v>0.010330976000005876</v>
+        <v>-0.5435744011811664</v>
       </c>
       <c r="N6" s="0">
-        <v>0.010184972000004677</v>
+        <v>-0.58716193225348279</v>
       </c>
       <c r="O6" s="0">
-        <v>0.0095808580000067423</v>
+        <v>-0.66761422379892266</v>
       </c>
       <c r="P6" s="0">
-        <v>0.010949618000012151</v>
+        <v>-0.54314775690578065</v>
       </c>
       <c r="Q6" s="0">
-        <v>0.011278368000006367</v>
+        <v>-0.52313912514745342</v>
       </c>
       <c r="R6" s="0">
-        <v>0.012581779999990772</v>
+        <v>-0.40099044869431488</v>
       </c>
       <c r="S6" s="0">
-        <v>0.013441032000002906</v>
+        <v>-0.33145769037372724</v>
       </c>
       <c r="T6" s="0">
-        <v>0.01528161800000305</v>
+        <v>-0.15932535415545362</v>
       </c>
       <c r="U6" s="0">
-        <v>0.01490170599998919</v>
+        <v>-0.212674546096733</v>
       </c>
       <c r="V6" s="0">
-        <v>0.015186515999999983</v>
+        <v>-0.18566627322467255</v>
       </c>
       <c r="W6" s="0">
-        <v>0.015243862000005493</v>
+        <v>-0.18407468873605864</v>
       </c>
       <c r="X6" s="0">
-        <v>0.01549305000000345</v>
+        <v>-0.16497217836139871</v>
       </c>
       <c r="Y6" s="0">
-        <v>0.015764480000001413</v>
+        <v>-0.1449028655212054</v>
       </c>
       <c r="Z6" s="0">
-        <v>0.015835228000000257</v>
+        <v>-0.14332011729432714</v>
       </c>
       <c r="AA6" s="0">
-        <v>0.016370556000012471</v>
+        <v>-0.084486861971282454</v>
       </c>
       <c r="AB6" s="0">
-        <v>0.016594317999988561</v>
+        <v>-0.062033087422348351</v>
       </c>
       <c r="AC6" s="0">
-        <v>0.016877257999993844</v>
+        <v>-0.031119069399627025</v>
       </c>
       <c r="AD6" s="0">
-        <v>0.017135730000006788</v>
+        <v>-0.0023206973636775538</v>
       </c>
       <c r="AE6" s="0">
-        <v>0.017371720000014079</v>
+        <v>0.024446054663122323</v>
       </c>
       <c r="AF6" s="0">
-        <v>0.017587508000005414</v>
+        <v>0.04932669299978526</v>
       </c>
       <c r="AG6" s="0">
-        <v>0.017784668000004444</v>
+        <v>0.072401690555763065</v>
       </c>
       <c r="AH6" s="0">
-        <v>0.017964861999999471</v>
+        <v>0.093782157014208736</v>
       </c>
       <c r="AI6" s="0">
-        <v>0.018129849999994008</v>
+        <v>0.11360749969971522</v>
       </c>
       <c r="AJ6" s="0">
-        <v>0.018280587999996101</v>
+        <v>0.131928697614216</v>
       </c>
       <c r="AK6" s="0">
-        <v>0.018418722000006937</v>
+        <v>0.14889745748823444</v>
       </c>
       <c r="AL6" s="0">
-        <v>0.018545197999998209</v>
+        <v>0.16458524362599089</v>
       </c>
       <c r="AM6" s="0">
-        <v>0.018660955999990847</v>
+        <v>0.17907119064722388</v>
       </c>
       <c r="AN6" s="0">
-        <v>0.018767034000006788</v>
+        <v>0.19245424140617981</v>
       </c>
       <c r="AO6" s="0">
-        <v>0.018864063999998848</v>
+        <v>0.20478665144374669</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>326</v>
+        <v>486</v>
       </c>
       <c r="B7" s="0">
-        <v>-116.6905008</v>
+        <v>0.6342573896817455</v>
       </c>
       <c r="C7" s="0">
-        <v>-0.014016119999993748</v>
+        <v>-1.5606164442804087</v>
       </c>
       <c r="D7" s="0">
-        <v>-0.0072704819999955816</v>
+        <v>-1.2179981131092623</v>
       </c>
       <c r="E7" s="0">
-        <v>-0.011544727999989846</v>
+        <v>-1.4754706996240925</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.002620269999994207</v>
+        <v>-1.0002371363335647</v>
       </c>
       <c r="G7" s="0">
-        <v>-0.0096426659999906406</v>
+        <v>-1.4680216383737419</v>
       </c>
       <c r="H7" s="0">
-        <v>-0.0066039760000080605</v>
+        <v>-1.3053290050915214</v>
       </c>
       <c r="I7" s="0">
-        <v>-0.008080299999988938</v>
+        <v>-1.4105340614582957</v>
       </c>
       <c r="J7" s="0">
-        <v>-0.011894994000002157</v>
+        <v>-1.612915512708607</v>
       </c>
       <c r="K7" s="0">
-        <v>0.012100740000008159</v>
+        <v>-0.2013953973717221</v>
       </c>
       <c r="L7" s="0">
-        <v>-0.0016672099999937018</v>
+        <v>-1.2601744464418381</v>
       </c>
       <c r="M7" s="0">
-        <v>0.0010332280000113769</v>
+        <v>-1.0918692142961031</v>
       </c>
       <c r="N7" s="0">
-        <v>0.00075117200000818229</v>
+        <v>-1.1615156450131203</v>
       </c>
       <c r="O7" s="0">
-        <v>-0.0001377840000031938</v>
+        <v>-1.2694714546364219</v>
       </c>
       <c r="P7" s="0">
-        <v>0.0034940479999931995</v>
+        <v>-1.0296294525628911</v>
       </c>
       <c r="Q7" s="0">
-        <v>0.0047604299999903787</v>
+        <v>-0.95563231170172835</v>
       </c>
       <c r="R7" s="0">
-        <v>0.0067962580000084927</v>
+        <v>-0.81275778923562081</v>
       </c>
       <c r="S7" s="0">
-        <v>0.0081692480000157275</v>
+        <v>-0.71965452274329078</v>
       </c>
       <c r="T7" s="0">
-        <v>0.011421728000001963</v>
+        <v>-0.46540955133558476</v>
       </c>
       <c r="U7" s="0">
-        <v>0.010700974000002361</v>
+        <v>-0.57265134377034155</v>
       </c>
       <c r="V7" s="0">
-        <v>0.01310480400000813</v>
+        <v>-0.35764922461547749</v>
       </c>
       <c r="W7" s="0">
-        <v>0.013712806000015121</v>
+        <v>-0.30413317219934866</v>
       </c>
       <c r="X7" s="0">
-        <v>0.013735633999999664</v>
+        <v>-0.30766078415576104</v>
       </c>
       <c r="Y7" s="0">
-        <v>0.013644421999998713</v>
+        <v>-0.32912365132445953</v>
       </c>
       <c r="Z7" s="0">
-        <v>0.013648458000005803</v>
+        <v>-0.34466894282716182</v>
       </c>
       <c r="AA7" s="0">
-        <v>0.014512831999994091</v>
+        <v>-0.26142520285895054</v>
       </c>
       <c r="AB7" s="0">
-        <v>0.014866029999993202</v>
+        <v>-0.23177425250312722</v>
       </c>
       <c r="AC7" s="0">
-        <v>0.015295688000009022</v>
+        <v>-0.19089952953604616</v>
       </c>
       <c r="AD7" s="0">
-        <v>0.015687864000000218</v>
+        <v>-0.15242549124238003</v>
       </c>
       <c r="AE7" s="0">
-        <v>0.016045902000001888</v>
+        <v>-0.11629770331817545</v>
       </c>
       <c r="AF7" s="0">
-        <v>0.016373025999996571</v>
+        <v>-0.082423018850557098</v>
       </c>
       <c r="AG7" s="0">
-        <v>0.016671759999994151</v>
+        <v>-0.05074982837032236</v>
       </c>
       <c r="AH7" s="0">
-        <v>0.016944707999996922</v>
+        <v>-0.021176824312667524</v>
       </c>
       <c r="AI7" s="0">
-        <v>0.017194463999999243</v>
+        <v>0.0064300628039393347</v>
       </c>
       <c r="AJ7" s="0">
-        <v>0.017422622000012211</v>
+        <v>0.032110306093803491</v>
       </c>
       <c r="AK7" s="0">
-        <v>0.01763145600001792</v>
+        <v>0.056013411609087203</v>
       </c>
       <c r="AL7" s="0">
-        <v>0.017822444000003657</v>
+        <v>0.078209957582743378</v>
       </c>
       <c r="AM7" s="0">
-        <v>0.017997250000007625</v>
+        <v>0.098813151104439528</v>
       </c>
       <c r="AN7" s="0">
-        <v>0.018157332000015458</v>
+        <v>0.11792616737165813</v>
       </c>
       <c r="AO7" s="0">
-        <v>0.01830394800001045</v>
+        <v>0.13563931552931624</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>327</v>
+        <v>487</v>
       </c>
       <c r="B8" s="0">
-        <v>-116.74011229999999</v>
+        <v>-1.2947345630025511</v>
       </c>
       <c r="C8" s="0">
-        <v>-0.035803915999991887</v>
+        <v>-1.8569699639107349</v>
       </c>
       <c r="D8" s="0">
-        <v>-0.023868415999999115</v>
+        <v>-1.4447994520159686</v>
       </c>
       <c r="E8" s="0">
-        <v>-0.031099687999997627</v>
+        <v>-1.7650270701389945</v>
       </c>
       <c r="F8" s="0">
-        <v>-0.018438562000000047</v>
+        <v>-1.3158592852491462</v>
       </c>
       <c r="G8" s="0">
-        <v>-0.026868105999994896</v>
+        <v>-1.7195942683255485</v>
       </c>
       <c r="H8" s="0">
-        <v>-0.020771421999995709</v>
+        <v>-1.4962252248236469</v>
       </c>
       <c r="I8" s="0">
-        <v>-0.022710395999993693</v>
+        <v>-1.6123266664659848</v>
       </c>
       <c r="J8" s="0">
-        <v>-0.030058688000011102</v>
+        <v>-1.8792530639775762</v>
       </c>
       <c r="K8" s="0">
-        <v>0.0032580800000090449</v>
+        <v>-0.51004878599025327</v>
       </c>
       <c r="L8" s="0">
-        <v>-0.013280057999992323</v>
+        <v>-1.5095780289730312</v>
       </c>
       <c r="M8" s="0">
-        <v>-0.0096319779999873845</v>
+        <v>-1.3664864319547594</v>
       </c>
       <c r="N8" s="0">
-        <v>-0.0095511020000031976</v>
+        <v>-1.4168136001430287</v>
       </c>
       <c r="O8" s="0">
-        <v>-0.010894059999998262</v>
+        <v>-1.5338388354238104</v>
       </c>
       <c r="P8" s="0">
-        <v>-0.0051816459999969311</v>
+        <v>-1.2580160308909025</v>
       </c>
       <c r="Q8" s="0">
-        <v>-0.0029967899999974179</v>
+        <v>-1.2132366801108141</v>
       </c>
       <c r="R8" s="0">
-        <v>0.00060312000000806165</v>
+        <v>-1.0335357569682713</v>
       </c>
       <c r="S8" s="0">
-        <v>0.0031609440000011091</v>
+        <v>-0.91187095152011222</v>
       </c>
       <c r="T8" s="0">
-        <v>0.0075418840000054388</v>
+        <v>-0.63895346842742884</v>
       </c>
       <c r="U8" s="0">
-        <v>0.0059964260000100467</v>
+        <v>-0.82095882317146007</v>
       </c>
       <c r="V8" s="0">
-        <v>0.010650186000006556</v>
+        <v>-0.48448995098604825</v>
       </c>
       <c r="W8" s="0">
-        <v>0.010292399999997315</v>
+        <v>-0.55380117246467486</v>
       </c>
       <c r="X8" s="0">
-        <v>0.01057084800000041</v>
+        <v>-0.54394189461860654</v>
       </c>
       <c r="Y8" s="0">
-        <v>0.010029450000004658</v>
+        <v>-0.60007729546283883</v>
       </c>
       <c r="Z8" s="0">
-        <v>0.010290939999990201</v>
+        <v>-0.59155971196372537</v>
       </c>
       <c r="AA8" s="0">
-        <v>0.011677038000001971</v>
+        <v>-0.48215243340476344</v>
       </c>
       <c r="AB8" s="0">
-        <v>0.012131790000012188</v>
+        <v>-0.45752716955655121</v>
       </c>
       <c r="AC8" s="0">
-        <v>0.012799606000001518</v>
+        <v>-0.40580809555095115</v>
       </c>
       <c r="AD8" s="0">
-        <v>0.013408994000016605</v>
+        <v>-0.35631317530455803</v>
       </c>
       <c r="AE8" s="0">
-        <v>0.013965082000012785</v>
+        <v>-0.30913502861761216</v>
       </c>
       <c r="AF8" s="0">
-        <v>0.01447267800000418</v>
+        <v>-0.26431497137974774</v>
       </c>
       <c r="AG8" s="0">
-        <v>0.014935968000003186</v>
+        <v>-0.2218822876774991</v>
       </c>
       <c r="AH8" s="0">
-        <v>0.015359024000005661</v>
+        <v>-0.18181113156123271</v>
       </c>
       <c r="AI8" s="0">
-        <v>0.015745500000008406</v>
+        <v>-0.14405844170499063</v>
       </c>
       <c r="AJ8" s="0">
-        <v>0.016098239999990938</v>
+        <v>-0.10862003048799129</v>
       </c>
       <c r="AK8" s="0">
-        <v>0.016420568000000912</v>
+        <v>-0.075387094369860838</v>
       </c>
       <c r="AL8" s="0">
-        <v>0.016715202000000318</v>
+        <v>-0.044279237808109835</v>
       </c>
       <c r="AM8" s="0">
-        <v>0.016984448000002317</v>
+        <v>-0.015227493523464374</v>
       </c>
       <c r="AN8" s="0">
-        <v>0.017230701999991993</v>
+        <v>0.011879916576076498</v>
       </c>
       <c r="AO8" s="0">
-        <v>0.017455850000004602</v>
+        <v>0.037121602047098037</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>328</v>
+        <v>488</v>
       </c>
       <c r="B9" s="0">
-        <v>-116.81824619999999</v>
+        <v>-3.2126749646342412</v>
       </c>
       <c r="C9" s="0">
-        <v>-0.065499445999989803</v>
+        <v>-1.8334626419256059</v>
       </c>
       <c r="D9" s="0">
-        <v>-0.052466793999997208</v>
+        <v>-1.5335718348560086</v>
       </c>
       <c r="E9" s="0">
-        <v>-0.065581329999986337</v>
+        <v>-1.9075131064168089</v>
       </c>
       <c r="F9" s="0">
-        <v>-0.043325958000011155</v>
+        <v>-1.4342108194785281</v>
       </c>
       <c r="G9" s="0">
-        <v>-0.057232217999995783</v>
+        <v>-1.8739355427735516</v>
       </c>
       <c r="H9" s="0">
-        <v>-0.046598828000000481</v>
+        <v>-1.6232707577576735</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.050326217999995038</v>
+        <v>-1.7848181424945087</v>
       </c>
       <c r="J9" s="0">
-        <v>-0.063580826000006141</v>
+        <v>-2.0883902591846168</v>
       </c>
       <c r="K9" s="0">
-        <v>-0.015395621999999776</v>
+        <v>-0.84211757957753375</v>
       </c>
       <c r="L9" s="0">
-        <v>-0.036678735999998935</v>
+        <v>-1.7760070814453595</v>
       </c>
       <c r="M9" s="0">
-        <v>-0.030408444000002532</v>
+        <v>-1.6522866422399425</v>
       </c>
       <c r="N9" s="0">
-        <v>-0.028463378000012085</v>
+        <v>-1.6744330049753893</v>
       </c>
       <c r="O9" s="0">
-        <v>-0.031416429999993056</v>
+        <v>-1.8277645461944341</v>
       </c>
       <c r="P9" s="0">
-        <v>-0.022666769999986514</v>
+        <v>-1.5475887212595199</v>
       </c>
       <c r="Q9" s="0">
-        <v>-0.018134281999991231</v>
+        <v>-1.4880955393425639</v>
       </c>
       <c r="R9" s="0">
-        <v>-0.012408182000001489</v>
+        <v>-1.3570266477429989</v>
       </c>
       <c r="S9" s="0">
-        <v>-0.0085076680000071292</v>
+        <v>-1.2690381324679074</v>
       </c>
       <c r="T9" s="0">
-        <v>-0.00092491199998789853</v>
+        <v>-0.95637754414134135</v>
       </c>
       <c r="U9" s="0">
-        <v>-0.0040646000000066351</v>
+        <v>-1.2315465632411828</v>
       </c>
       <c r="V9" s="0">
-        <v>0.0058831639999965546</v>
+        <v>-0.67391752468762522</v>
       </c>
       <c r="W9" s="0">
-        <v>0.006417548000001716</v>
+        <v>-0.72058210841637049</v>
       </c>
       <c r="X9" s="0">
-        <v>0.007026664000008509</v>
+        <v>-0.71515804733071497</v>
       </c>
       <c r="Y9" s="0">
-        <v>0.0065092300000202385</v>
+        <v>-0.77403124696524617</v>
       </c>
       <c r="Z9" s="0">
-        <v>0.0062112180000042372</v>
+        <v>-0.79875774578935865</v>
       </c>
       <c r="AA9" s="0">
-        <v>0.0082328120000028093</v>
+        <v>-0.66030570099129238</v>
       </c>
       <c r="AB9" s="0">
-        <v>0.0086368260000000419</v>
+        <v>-0.66345875745118366</v>
       </c>
       <c r="AC9" s="0">
-        <v>0.00957702600000232</v>
+        <v>-0.6104434077801173</v>
       </c>
       <c r="AD9" s="0">
-        <v>0.010437420000002362</v>
+        <v>-0.55823130006847688</v>
       </c>
       <c r="AE9" s="0">
-        <v>0.011224467999994658</v>
+        <v>-0.50715853064795036</v>
       </c>
       <c r="AF9" s="0">
-        <v>0.011944696000000476</v>
+        <v>-0.45745537823617138</v>
       </c>
       <c r="AG9" s="0">
-        <v>0.01260360400000593</v>
+        <v>-0.40935282645472443</v>
       </c>
       <c r="AH9" s="0">
-        <v>0.013206757999995489</v>
+        <v>-0.36298169652486389</v>
       </c>
       <c r="AI9" s="0">
-        <v>0.013758708000011666</v>
+        <v>-0.31849186254931577</v>
       </c>
       <c r="AJ9" s="0">
-        <v>0.014263777999985905</v>
+        <v>-0.27597800990619326</v>
       </c>
       <c r="AK9" s="0">
-        <v>0.014726466000013261</v>
+        <v>-0.23544155694307101</v>
       </c>
       <c r="AL9" s="0">
-        <v>0.015150160000004576</v>
+        <v>-0.19693887307331009</v>
       </c>
       <c r="AM9" s="0">
-        <v>0.015538129999995931</v>
+        <v>-0.16048169835377443</v>
       </c>
       <c r="AN9" s="0">
-        <v>0.015893726000001607</v>
+        <v>-0.12601827832887794</v>
       </c>
       <c r="AO9" s="0">
-        <v>0.01621948999999745</v>
+        <v>-0.093542462830045275</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>329</v>
+        <v>489</v>
       </c>
       <c r="B10" s="0">
-        <v>-116.94167059999999</v>
+        <v>-4.9428506831170758</v>
       </c>
       <c r="C10" s="0">
-        <v>-0.11288902399999357</v>
+        <v>-1.6505749107313774</v>
       </c>
       <c r="D10" s="0">
-        <v>-0.094351990000002939</v>
+        <v>-1.42004460674209</v>
       </c>
       <c r="E10" s="0">
-        <v>-0.10848033199999518</v>
+        <v>-1.6417556060474525</v>
       </c>
       <c r="F10" s="0">
-        <v>-0.077878996000005696</v>
+        <v>-1.2732676371382974</v>
       </c>
       <c r="G10" s="0">
-        <v>-0.1018020099999819</v>
+        <v>-1.7261158877625009</v>
       </c>
       <c r="H10" s="0">
-        <v>-0.082477477999983062</v>
+        <v>-1.4682304692465939</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.087818565999977505</v>
+        <v>-1.6192930661569931</v>
       </c>
       <c r="J10" s="0">
-        <v>-0.11126655199999957</v>
+        <v>-1.9251548721634584</v>
       </c>
       <c r="K10" s="0">
-        <v>-0.040724507999992721</v>
+        <v>-0.88113453193694746</v>
       </c>
       <c r="L10" s="0">
-        <v>-0.073273097999983161</v>
+        <v>-1.7303120233487759</v>
       </c>
       <c r="M10" s="0">
-        <v>-0.063640047999992344</v>
+        <v>-1.657516514325307</v>
       </c>
       <c r="N10" s="0">
-        <v>-0.059442971999981165</v>
+        <v>-1.7035877055107278</v>
       </c>
       <c r="O10" s="0">
-        <v>-0.06023502399998959</v>
+        <v>-1.8121144196941286</v>
       </c>
       <c r="P10" s="0">
-        <v>-0.049542187999999765</v>
+        <v>-1.598145384458004</v>
       </c>
       <c r="Q10" s="0">
-        <v>-0.044439497999998689</v>
+        <v>-1.6091823929960545</v>
       </c>
       <c r="R10" s="0">
-        <v>-0.037894606000004938</v>
+        <v>-1.5997426344639214</v>
       </c>
       <c r="S10" s="0">
-        <v>-0.029834369999985011</v>
+        <v>-1.5464630436653346</v>
       </c>
       <c r="T10" s="0">
-        <v>-0.0158319579999886</v>
+        <v>-1.2143369252771332</v>
       </c>
       <c r="U10" s="0">
-        <v>-0.020914168000000455</v>
+        <v>-1.5887779596797609</v>
       </c>
       <c r="V10" s="0">
-        <v>-0.0069056259999871195</v>
+        <v>-1.0609365869259437</v>
       </c>
       <c r="W10" s="0">
-        <v>-0.0065394119999910849</v>
+        <v>-1.2264209167555744</v>
       </c>
       <c r="X10" s="0">
-        <v>-0.0044848279999842866</v>
+        <v>-1.2380929268079226</v>
       </c>
       <c r="Y10" s="0">
-        <v>-0.0049300979999986616</v>
+        <v>-1.327517753338824</v>
       </c>
       <c r="Z10" s="0">
-        <v>-0.0058558320000048347</v>
+        <v>-1.3999981656781157</v>
       </c>
       <c r="AA10" s="0">
-        <v>-0.0021820679999922099</v>
+        <v>-1.1797483398980531</v>
       </c>
       <c r="AB10" s="0">
-        <v>-0.0019207619999792591</v>
+        <v>-1.2197624391986648</v>
       </c>
       <c r="AC10" s="0">
-        <v>-0.0001750139999887601</v>
+        <v>-1.163054174623785</v>
       </c>
       <c r="AD10" s="0">
-        <v>0.0014419759999992898</v>
+        <v>-1.1037777224778196</v>
       </c>
       <c r="AE10" s="0">
-        <v>0.0029269440000132541</v>
+        <v>-1.0430662730892157</v>
       </c>
       <c r="AF10" s="0">
-        <v>0.0042906720000144283</v>
+        <v>-0.98148100095857793</v>
       </c>
       <c r="AG10" s="0">
-        <v>0.0055426100000102174</v>
+        <v>-0.91958835394005001</v>
       </c>
       <c r="AH10" s="0">
-        <v>0.0066919619999947777</v>
+        <v>-0.85786321163769452</v>
       </c>
       <c r="AI10" s="0">
-        <v>0.007747000000013049</v>
+        <v>-0.79674865785721383</v>
       </c>
       <c r="AJ10" s="0">
-        <v>0.0087153600000005049</v>
+        <v>-0.73663059079707327</v>
       </c>
       <c r="AK10" s="0">
-        <v>0.0096046480000109291</v>
+        <v>-0.67778805519248286</v>
       </c>
       <c r="AL10" s="0">
-        <v>0.010420848000013638</v>
+        <v>-0.62054537696801093</v>
       </c>
       <c r="AM10" s="0">
-        <v>0.011170612000004798</v>
+        <v>-0.5650614997499368</v>
       </c>
       <c r="AN10" s="0">
-        <v>0.011859072000011128</v>
+        <v>-0.51154734187195461</v>
       </c>
       <c r="AO10" s="0">
-        <v>0.012491442000002184</v>
+        <v>-0.46012172661797118</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>330</v>
+        <v>490</v>
       </c>
       <c r="B11" s="0">
-        <v>-117.08719099999999</v>
+        <v>-6.091327955903342</v>
       </c>
       <c r="C11" s="0">
-        <v>-0.13801131199999039</v>
+        <v>-1.0851163346302817</v>
       </c>
       <c r="D11" s="0">
-        <v>-0.11850640599999585</v>
+        <v>-0.94612439594720521</v>
       </c>
       <c r="E11" s="0">
-        <v>-0.14087380600000321</v>
+        <v>-1.1423108745306449</v>
       </c>
       <c r="F11" s="0">
-        <v>-0.10258931000000038</v>
+        <v>-0.87524842992492158</v>
       </c>
       <c r="G11" s="0">
-        <v>-0.14182685999999611</v>
+        <v>-1.2550125394570215</v>
       </c>
       <c r="H11" s="0">
-        <v>-0.10741584400000326</v>
+        <v>-1.002647546917723</v>
       </c>
       <c r="I11" s="0">
-        <v>-0.12035405000000443</v>
+        <v>-1.1756092142785881</v>
       </c>
       <c r="J11" s="0">
-        <v>-0.16716327000000453</v>
+        <v>-1.512815550102053</v>
       </c>
       <c r="K11" s="0">
-        <v>-0.065371025999981125</v>
+        <v>-0.67372559790855269</v>
       </c>
       <c r="L11" s="0">
-        <v>-0.11146068799999531</v>
+        <v>-1.3413280255608413</v>
       </c>
       <c r="M11" s="0">
-        <v>-0.097061380000000863</v>
+        <v>-1.2598795261353286</v>
       </c>
       <c r="N11" s="0">
-        <v>-0.095698692000000474</v>
+        <v>-1.3627292908750213</v>
       </c>
       <c r="O11" s="0">
-        <v>-0.094311969999993917</v>
+        <v>-1.4568103340593281</v>
       </c>
       <c r="P11" s="0">
-        <v>-0.084577715999985426</v>
+        <v>-1.3968773986363947</v>
       </c>
       <c r="Q11" s="0">
-        <v>-0.078205565999995397</v>
+        <v>-1.4071669029487679</v>
       </c>
       <c r="R11" s="0">
-        <v>-0.07264937400000937</v>
+        <v>-1.461239852509103</v>
       </c>
       <c r="S11" s="0">
-        <v>-0.062016283999996258</v>
+        <v>-1.4677087926630947</v>
       </c>
       <c r="T11" s="0">
-        <v>-0.038751062000004222</v>
+        <v>-1.2335614306345153</v>
       </c>
       <c r="U11" s="0">
-        <v>-0.048432923999997879</v>
+        <v>-1.7078384122682095</v>
       </c>
       <c r="V11" s="0">
-        <v>-0.028516986000000966</v>
+        <v>-1.3098108904359527</v>
       </c>
       <c r="W11" s="0">
-        <v>-0.02615063599999834</v>
+        <v>-1.4569199335783618</v>
       </c>
       <c r="X11" s="0">
-        <v>-0.022693750000003288</v>
+        <v>-1.5374731922103975</v>
       </c>
       <c r="Y11" s="0">
-        <v>-0.023174013999992749</v>
+        <v>-1.7158341024678005</v>
       </c>
       <c r="Z11" s="0">
-        <v>-0.024706874000004486</v>
+        <v>-1.8370903032586885</v>
       </c>
       <c r="AA11" s="0">
-        <v>-0.01849625399999999</v>
+        <v>-1.5895508694481808</v>
       </c>
       <c r="AB11" s="0">
-        <v>-0.01930395800001028</v>
+        <v>-1.6840147668795538</v>
       </c>
       <c r="AC11" s="0">
-        <v>-0.017136442000010188</v>
+        <v>-1.6566760606573849</v>
       </c>
       <c r="AD11" s="0">
-        <v>-0.013979661999998338</v>
+        <v>-1.6035362730104443</v>
       </c>
       <c r="AE11" s="0">
-        <v>-0.011056503999982592</v>
+        <v>-1.5442178346702122</v>
       </c>
       <c r="AF11" s="0">
-        <v>-0.0083752979999913713</v>
+        <v>-1.4800471970851681</v>
       </c>
       <c r="AG11" s="0">
-        <v>-0.0059180560000000604</v>
+        <v>-1.4118634784701869</v>
       </c>
       <c r="AH11" s="0">
-        <v>-0.0036670479999982852</v>
+        <v>-1.34046390777812</v>
       </c>
       <c r="AI11" s="0">
-        <v>-0.0016064940000020123</v>
+        <v>-1.2666849357464702</v>
       </c>
       <c r="AJ11" s="0">
-        <v>0.0002792359999959082</v>
+        <v>-1.1912744094120959</v>
       </c>
       <c r="AK11" s="0">
-        <v>0.0020042240000024414</v>
+        <v>-1.1149641546076925</v>
       </c>
       <c r="AL11" s="0">
-        <v>0.0035814219999950048</v>
+        <v>-1.0384511735341293</v>
       </c>
       <c r="AM11" s="0">
-        <v>0.0050233280000058222</v>
+        <v>-0.96231931678153459</v>
       </c>
       <c r="AN11" s="0">
-        <v>0.0063407219999889186</v>
+        <v>-0.88716089225488415</v>
       </c>
       <c r="AO11" s="0">
-        <v>0.0075445340000031003</v>
+        <v>-0.81340392428703223</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>331</v>
+        <v>491</v>
       </c>
       <c r="B12" s="0">
-        <v>-117.2552001</v>
+        <v>-6.88664930758409</v>
       </c>
       <c r="C12" s="0">
-        <v>-0.16234592000000792</v>
+        <v>-0.73812807832194272</v>
       </c>
       <c r="D12" s="0">
-        <v>-0.13727407000000458</v>
+        <v>-0.63142623591496116</v>
       </c>
       <c r="E12" s="0">
-        <v>-0.16811072600000987</v>
+        <v>-0.78042571162728258</v>
       </c>
       <c r="F12" s="0">
-        <v>-0.12058750000000007</v>
+        <v>-0.57656320981038645</v>
       </c>
       <c r="G12" s="0">
-        <v>-0.17074468800000009</v>
+        <v>-0.85356937950311851</v>
       </c>
       <c r="H12" s="0">
-        <v>-0.12389136999999639</v>
+        <v>-0.63095638653898867</v>
       </c>
       <c r="I12" s="0">
-        <v>-0.14604640999999763</v>
+        <v>-0.80108369879896879</v>
       </c>
       <c r="J12" s="0">
-        <v>-0.20661575999999204</v>
+        <v>-1.057685307462775</v>
       </c>
       <c r="K12" s="0">
-        <v>-0.072870163999994908</v>
+        <v>-0.38275798618410695</v>
       </c>
       <c r="L12" s="0">
-        <v>-0.14593019000000229</v>
+        <v>-0.92478817343493791</v>
       </c>
       <c r="M12" s="0">
-        <v>-0.13298510800000063</v>
+        <v>-0.8962061959031683</v>
       </c>
       <c r="N12" s="0">
-        <v>-0.13586459600000556</v>
+        <v>-0.99057453191598277</v>
       </c>
       <c r="O12" s="0">
-        <v>-0.13158966799999039</v>
+        <v>-1.0388830104129825</v>
       </c>
       <c r="P12" s="0">
-        <v>-0.1267593019999973</v>
+        <v>-1.0760032383809497</v>
       </c>
       <c r="Q12" s="0">
-        <v>-0.1208792399999945</v>
+        <v>-1.110904361232228</v>
       </c>
       <c r="R12" s="0">
-        <v>-0.11991026399999871</v>
+        <v>-1.1904431818502008</v>
       </c>
       <c r="S12" s="0">
-        <v>-0.10709345999998821</v>
+        <v>-1.2012853818442721</v>
       </c>
       <c r="T12" s="0">
-        <v>-0.077751031999995668</v>
+        <v>-1.0895205669289825</v>
       </c>
       <c r="U12" s="0">
-        <v>-0.098590645999991899</v>
+        <v>-1.6356651404427305</v>
       </c>
       <c r="V12" s="0">
-        <v>-0.073572987999996009</v>
+        <v>-1.4435975756611903</v>
       </c>
       <c r="W12" s="0">
-        <v>-0.069756700000000116</v>
+        <v>-1.6563208386542194</v>
       </c>
       <c r="X12" s="0">
-        <v>-0.067644057999999951</v>
+        <v>-1.8557161620681046</v>
       </c>
       <c r="Y12" s="0">
-        <v>-0.067823121999993852</v>
+        <v>-2.1020877098636901</v>
       </c>
       <c r="Z12" s="0">
-        <v>-0.065978688000002172</v>
+        <v>-2.2145040890172156</v>
       </c>
       <c r="AA12" s="0">
-        <v>-0.051178280000002907</v>
+        <v>-1.9109312322286123</v>
       </c>
       <c r="AB12" s="0">
-        <v>-0.052994899999988299</v>
+        <v>-2.0551493222670985</v>
       </c>
       <c r="AC12" s="0">
-        <v>-0.051407371999986573</v>
+        <v>-2.0602927960921109</v>
       </c>
       <c r="AD12" s="0">
-        <v>-0.047985097999984738</v>
+        <v>-2.0716536475618259</v>
       </c>
       <c r="AE12" s="0">
-        <v>-0.043384635999999865</v>
+        <v>-2.0900437237286726</v>
       </c>
       <c r="AF12" s="0">
-        <v>-0.039026108000002502</v>
+        <v>-2.0996671844222035</v>
       </c>
       <c r="AG12" s="0">
-        <v>-0.034926510000006239</v>
+        <v>-2.0999668855959386</v>
       </c>
       <c r="AH12" s="0">
-        <v>-0.031076807999995459</v>
+        <v>-2.091007657845815</v>
       </c>
       <c r="AI12" s="0">
-        <v>-0.027467329999994128</v>
+        <v>-2.0730155228010565</v>
       </c>
       <c r="AJ12" s="0">
-        <v>-0.024087291999991045</v>
+        <v>-2.0463088559445266</v>
       </c>
       <c r="AK12" s="0">
-        <v>-0.020926461999992263</v>
+        <v>-2.0113777819888377</v>
       </c>
       <c r="AL12" s="0">
-        <v>-0.017973486000003369</v>
+        <v>-1.9687578985016356</v>
       </c>
       <c r="AM12" s="0">
-        <v>-0.015217561999990359</v>
+        <v>-1.9191017033215434</v>
       </c>
       <c r="AN12" s="0">
-        <v>-0.012647849999994243</v>
+        <v>-1.8631131673222965</v>
       </c>
       <c r="AO12" s="0">
-        <v>-0.01025356199998928</v>
+        <v>-1.8015324739616063</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>332</v>
+        <v>492</v>
       </c>
       <c r="B13" s="0">
-        <v>-117.38971629999999</v>
+        <v>-7.3135658288570538</v>
       </c>
       <c r="C13" s="0">
-        <v>-0.13495150199999717</v>
+        <v>-0.38835007991020476</v>
       </c>
       <c r="D13" s="0">
-        <v>-0.11737496199998976</v>
+        <v>-0.33635222706046775</v>
       </c>
       <c r="E13" s="0">
-        <v>-0.15336441200000639</v>
+        <v>-0.45386145991429877</v>
       </c>
       <c r="F13" s="0">
-        <v>-0.10278150399999664</v>
+        <v>-0.29808792889159907</v>
       </c>
       <c r="G13" s="0">
-        <v>-0.16418908000000432</v>
+        <v>-0.51158817827195824</v>
       </c>
       <c r="H13" s="0">
-        <v>-0.11216784400000268</v>
+        <v>-0.34419149143351208</v>
       </c>
       <c r="I13" s="0">
-        <v>-0.14057332799999234</v>
+        <v>-0.46678328597039498</v>
       </c>
       <c r="J13" s="0">
-        <v>-0.20619594000000507</v>
+        <v>-0.66113684570105191</v>
       </c>
       <c r="K13" s="0">
-        <v>-0.065096848000000485</v>
+        <v>-0.18968572163327146</v>
       </c>
       <c r="L13" s="0">
-        <v>-0.15309568599999057</v>
+        <v>-0.56674971099523241</v>
       </c>
       <c r="M13" s="0">
-        <v>-0.1407336159999959</v>
+        <v>-0.53654040519990664</v>
       </c>
       <c r="N13" s="0">
-        <v>-0.14504309199999899</v>
+        <v>-0.59120229849749562</v>
       </c>
       <c r="O13" s="0">
-        <v>-0.14342344999999046</v>
+        <v>-0.61988873246244935</v>
       </c>
       <c r="P13" s="0">
-        <v>-0.14381964400000857</v>
+        <v>-0.66612273503950237</v>
       </c>
       <c r="Q13" s="0">
-        <v>-0.1464821000000045</v>
+        <v>-0.72141515684445512</v>
       </c>
       <c r="R13" s="0">
-        <v>-0.1507718560000102</v>
+        <v>-0.79296423054312026</v>
       </c>
       <c r="S13" s="0">
-        <v>-0.13971167800000206</v>
+        <v>-0.79265360903453319</v>
       </c>
       <c r="T13" s="0">
-        <v>-0.11048295200000258</v>
+        <v>-0.73778552502898198</v>
       </c>
       <c r="U13" s="0">
-        <v>-0.1496911080000034</v>
+        <v>-1.1654482681870215</v>
       </c>
       <c r="V13" s="0">
-        <v>-0.12624479599999905</v>
+        <v>-1.1222032626180107</v>
       </c>
       <c r="W13" s="0">
-        <v>-0.12891606400001354</v>
+        <v>-1.3484985498321906</v>
       </c>
       <c r="X13" s="0">
-        <v>-0.13408162199998674</v>
+        <v>-1.6020300160622316</v>
       </c>
       <c r="Y13" s="0">
-        <v>-0.14111346600001173</v>
+        <v>-1.8439348939121423</v>
       </c>
       <c r="Z13" s="0">
-        <v>-0.14441736999998955</v>
+        <v>-2.0379565250556935</v>
       </c>
       <c r="AA13" s="0">
-        <v>-0.12933807200000036</v>
+        <v>-2.0094916991798106</v>
       </c>
       <c r="AB13" s="0">
-        <v>-0.13385628999998733</v>
+        <v>-2.2522204596128668</v>
       </c>
       <c r="AC13" s="0">
-        <v>-0.13122217800000602</v>
+        <v>-2.2799465397031144</v>
       </c>
       <c r="AD13" s="0">
-        <v>-0.12847926200000348</v>
+        <v>-2.3043503716303153</v>
       </c>
       <c r="AE13" s="0">
-        <v>-0.12612527200001455</v>
+        <v>-2.4030726915519702</v>
       </c>
       <c r="AF13" s="0">
-        <v>-0.12441947600000436</v>
+        <v>-2.5726802952650827</v>
       </c>
       <c r="AG13" s="0">
-        <v>-0.12240580199999318</v>
+        <v>-2.7433311011958668</v>
       </c>
       <c r="AH13" s="0">
-        <v>-0.12009978199998717</v>
+        <v>-2.912269859962425</v>
       </c>
       <c r="AI13" s="0">
-        <v>-0.11754322199999923</v>
+        <v>-3.078361887808736</v>
       </c>
       <c r="AJ13" s="0">
-        <v>-0.11477547599999571</v>
+        <v>-3.2405047294054419</v>
       </c>
       <c r="AK13" s="0">
-        <v>-0.11183206199999507</v>
+        <v>-3.3976117042306626</v>
       </c>
       <c r="AL13" s="0">
-        <v>-0.10874525999999651</v>
+        <v>-3.5486370595733296</v>
       </c>
       <c r="AM13" s="0">
-        <v>-0.10554460400000654</v>
+        <v>-3.6926092504985188</v>
       </c>
       <c r="AN13" s="0">
-        <v>-0.10225629000001835</v>
+        <v>-3.8286203807443311</v>
       </c>
       <c r="AO13" s="0">
-        <v>-0.098904273999996128</v>
+        <v>-3.9558561372328453</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>333</v>
+        <v>493</v>
       </c>
       <c r="B14" s="0">
-        <v>-117.4813461</v>
+        <v>-7.5392328889964304</v>
       </c>
       <c r="C14" s="0">
-        <v>-0.10195452599999832</v>
+        <v>-0.20801450143482741</v>
       </c>
       <c r="D14" s="0">
-        <v>-0.081374452000003927</v>
+        <v>-0.15917055545865538</v>
       </c>
       <c r="E14" s="0">
-        <v>-0.10579474399999178</v>
+        <v>-0.21945805273921204</v>
       </c>
       <c r="F14" s="0">
-        <v>-0.072890093999999905</v>
+        <v>-0.13860586423112292</v>
       </c>
       <c r="G14" s="0">
-        <v>-0.12169707999998813</v>
+        <v>-0.26465344532010188</v>
       </c>
       <c r="H14" s="0">
-        <v>-0.074889851999996537</v>
+        <v>-0.14756162810258339</v>
       </c>
       <c r="I14" s="0">
-        <v>-0.1084591979999896</v>
+        <v>-0.24212457983555324</v>
       </c>
       <c r="J14" s="0">
-        <v>-0.15274810200000211</v>
+        <v>-0.34392642614458047</v>
       </c>
       <c r="K14" s="0">
-        <v>-0.03321583000000139</v>
+        <v>-0.044124585195319081</v>
       </c>
       <c r="L14" s="0">
-        <v>-0.12254627199999213</v>
+        <v>-0.29734887769914159</v>
       </c>
       <c r="M14" s="0">
-        <v>-0.11295487599998744</v>
+        <v>-0.27544959270733571</v>
       </c>
       <c r="N14" s="0">
-        <v>-0.11500059800000706</v>
+        <v>-0.29411022481962396</v>
       </c>
       <c r="O14" s="0">
-        <v>-0.11846331199998694</v>
+        <v>-0.31837770166667684</v>
       </c>
       <c r="P14" s="0">
-        <v>-0.12598472999999721</v>
+        <v>-0.35602046404599119</v>
       </c>
       <c r="Q14" s="0">
-        <v>-0.13245493199999991</v>
+        <v>-0.39510143622012306</v>
       </c>
       <c r="R14" s="0">
-        <v>-0.14050917399999996</v>
+        <v>-0.43668374418269523</v>
       </c>
       <c r="S14" s="0">
-        <v>-0.13850086799999239</v>
+        <v>-0.45152065377813694</v>
       </c>
       <c r="T14" s="0">
-        <v>-0.12206161399998727</v>
+        <v>-0.43699062235139252</v>
       </c>
       <c r="U14" s="0">
-        <v>-0.16052229199999424</v>
+        <v>-0.66428533555778879</v>
       </c>
       <c r="V14" s="0">
-        <v>-0.14970275400000155</v>
+        <v>-0.65988453458327123</v>
       </c>
       <c r="W14" s="0">
-        <v>-0.16665191399999735</v>
+        <v>-0.82936503770999914</v>
       </c>
       <c r="X14" s="0">
-        <v>-0.18280578399999392</v>
+        <v>-0.99949161605193571</v>
       </c>
       <c r="Y14" s="0">
-        <v>-0.1997833300000007</v>
+        <v>-1.1622635436781341</v>
       </c>
       <c r="Z14" s="0">
-        <v>-0.2035004359999828</v>
+        <v>-1.2367329842825383</v>
       </c>
       <c r="AA14" s="0">
-        <v>-0.19209326800000603</v>
+        <v>-1.2430262393269012</v>
       </c>
       <c r="AB14" s="0">
-        <v>-0.20441287200000424</v>
+        <v>-1.4274637431333324</v>
       </c>
       <c r="AC14" s="0">
-        <v>-0.20513339399999886</v>
+        <v>-1.4957020407555444</v>
       </c>
       <c r="AD14" s="0">
-        <v>-0.20398975799998986</v>
+        <v>-1.5302333474507734</v>
       </c>
       <c r="AE14" s="0">
-        <v>-0.20282665999999772</v>
+        <v>-1.5654575337281822</v>
       </c>
       <c r="AF14" s="0">
-        <v>-0.20342334199999179</v>
+        <v>-1.640160927565171</v>
       </c>
       <c r="AG14" s="0">
-        <v>-0.20479517999998897</v>
+        <v>-1.743944634719206</v>
       </c>
       <c r="AH14" s="0">
-        <v>-0.20578424000001228</v>
+        <v>-1.8505532714375577</v>
       </c>
       <c r="AI14" s="0">
-        <v>-0.20639925400000259</v>
+        <v>-1.959394956060635</v>
       </c>
       <c r="AJ14" s="0">
-        <v>-0.20666158799998691</v>
+        <v>-2.0703093553434537</v>
       </c>
       <c r="AK14" s="0">
-        <v>-0.20659230599998857</v>
+        <v>-2.1831181832978621</v>
       </c>
       <c r="AL14" s="0">
-        <v>-0.20621245800000843</v>
+        <v>-2.2976348304532666</v>
       </c>
       <c r="AM14" s="0">
-        <v>-0.20554259000000563</v>
+        <v>-2.4136597923635725</v>
       </c>
       <c r="AN14" s="0">
-        <v>-0.20460264599999611</v>
+        <v>-2.5309814377057998</v>
       </c>
       <c r="AO14" s="0">
-        <v>-0.20341226399999179</v>
+        <v>-2.6493836474281607</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>334</v>
+        <v>494</v>
       </c>
       <c r="B15" s="0">
-        <v>-117.54088949999999</v>
+        <v>-7.6651419814735116</v>
       </c>
       <c r="C15" s="0">
-        <v>-0.064384521999993005</v>
+        <v>-0.095002581644028194</v>
       </c>
       <c r="D15" s="0">
-        <v>-0.044982929999984655</v>
+        <v>-0.053349547579485838</v>
       </c>
       <c r="E15" s="0">
-        <v>-0.065078821999985159</v>
+        <v>-0.096067893261691184</v>
       </c>
       <c r="F15" s="0">
-        <v>-0.042911249999984413</v>
+        <v>-0.049535955581193142</v>
       </c>
       <c r="G15" s="0">
-        <v>-0.068476465999988356</v>
+        <v>-0.10405498781324446</v>
       </c>
       <c r="H15" s="0">
-        <v>-0.041005309999998296</v>
+        <v>-0.04591340010202246</v>
       </c>
       <c r="I15" s="0">
-        <v>-0.06392340599998203</v>
+        <v>-0.097474328921851205</v>
       </c>
       <c r="J15" s="0">
-        <v>-0.086324897999996431</v>
+        <v>-0.14179817889328869</v>
       </c>
       <c r="K15" s="0">
-        <v>-0.013441551999998858</v>
+        <v>0.012014179018862729</v>
       </c>
       <c r="L15" s="0">
-        <v>-0.081254485999987303</v>
+        <v>-0.14025306646385022</v>
       </c>
       <c r="M15" s="0">
-        <v>-0.069440249999980885</v>
+        <v>-0.1139791269513839</v>
       </c>
       <c r="N15" s="0">
-        <v>-0.073683883999986044</v>
+        <v>-0.12643289839371444</v>
       </c>
       <c r="O15" s="0">
-        <v>-0.078451049999993749</v>
+        <v>-0.14219030808087033</v>
       </c>
       <c r="P15" s="0">
-        <v>-0.086981251999996623</v>
+        <v>-0.16666450578192124</v>
       </c>
       <c r="Q15" s="0">
-        <v>-0.091778049999997613</v>
+        <v>-0.18248228467051084</v>
       </c>
       <c r="R15" s="0">
-        <v>-0.10222930399998642</v>
+        <v>-0.21273895507109283</v>
       </c>
       <c r="S15" s="0">
-        <v>-0.10240134199998874</v>
+        <v>-0.21782284372899396</v>
       </c>
       <c r="T15" s="0">
-        <v>-0.092692723999998172</v>
+        <v>-0.20558249863874228</v>
       </c>
       <c r="U15" s="0">
-        <v>-0.12461319400000104</v>
+        <v>-0.31185734960943734</v>
       </c>
       <c r="V15" s="0">
-        <v>-0.096917293999989163</v>
+        <v>-0.25727868606953824</v>
       </c>
       <c r="W15" s="0">
-        <v>-0.14013606799998524</v>
+        <v>-0.39546891464508538</v>
       </c>
       <c r="X15" s="0">
-        <v>-0.15822641399999338</v>
+        <v>-0.47364427531405723</v>
       </c>
       <c r="Y15" s="0">
-        <v>-0.17770296199997926</v>
+        <v>-0.54957011559392854</v>
       </c>
       <c r="Z15" s="0">
-        <v>-0.17355242199998155</v>
+        <v>-0.54966247667542567</v>
       </c>
       <c r="AA15" s="0">
-        <v>-0.16339801000000431</v>
+        <v>-0.53635671394273043</v>
       </c>
       <c r="AB15" s="0">
-        <v>-0.17482979399998566</v>
+        <v>-0.60699109015676</v>
       </c>
       <c r="AC15" s="0">
-        <v>-0.17526182199999152</v>
+        <v>-0.63068269037124469</v>
       </c>
       <c r="AD15" s="0">
-        <v>-0.17525485399998342</v>
+        <v>-0.65020171014072681</v>
       </c>
       <c r="AE15" s="0">
-        <v>-0.17509982199998841</v>
+        <v>-0.6646581484952353</v>
       </c>
       <c r="AF15" s="0">
-        <v>-0.17487820199999771</v>
+        <v>-0.67923842680965263</v>
       </c>
       <c r="AG15" s="0">
-        <v>-0.17472923799999318</v>
+        <v>-0.69985672793717779</v>
       </c>
       <c r="AH15" s="0">
-        <v>-0.17432914399999344</v>
+        <v>-0.72475369651513255</v>
       </c>
       <c r="AI15" s="0">
-        <v>-0.17373150399998405</v>
+        <v>-0.749995595031828</v>
       </c>
       <c r="AJ15" s="0">
-        <v>-0.17295020799998451</v>
+        <v>-0.77549690848895125</v>
       </c>
       <c r="AK15" s="0">
-        <v>-0.17199645599998359</v>
+        <v>-0.80125310102822767</v>
       </c>
       <c r="AL15" s="0">
-        <v>-0.17088053999999442</v>
+        <v>-0.82725533773756543</v>
       </c>
       <c r="AM15" s="0">
-        <v>-0.16961263799998516</v>
+        <v>-0.85349403031739135</v>
       </c>
       <c r="AN15" s="0">
-        <v>-0.16820301399998083</v>
+        <v>-0.87995992428094505</v>
       </c>
       <c r="AO15" s="0">
-        <v>-0.16666161799998758</v>
+        <v>-0.90664287529725374</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>335</v>
+        <v>495</v>
       </c>
       <c r="B16" s="0">
-        <v>-117.56886899999999</v>
+        <v>-7.7195868772964538</v>
       </c>
       <c r="C16" s="0">
-        <v>-0.031009989999983389</v>
+        <v>-0.019705552145279449</v>
       </c>
       <c r="D16" s="0">
-        <v>-0.021498073999989487</v>
+        <v>-0.0010773772196410183</v>
       </c>
       <c r="E16" s="0">
-        <v>-0.030193937999992926</v>
+        <v>-0.017943814370821345</v>
       </c>
       <c r="F16" s="0">
-        <v>-0.018270405999995631</v>
+        <v>0.0051628227904002844</v>
       </c>
       <c r="G16" s="0">
-        <v>-0.033859839999987429</v>
+        <v>-0.025271801829531846</v>
       </c>
       <c r="H16" s="0">
-        <v>-0.018299215999999063</v>
+        <v>0.005021502360974559</v>
       </c>
       <c r="I16" s="0">
-        <v>-0.030539157999992739</v>
+        <v>-0.019362299525767988</v>
       </c>
       <c r="J16" s="0">
-        <v>-0.042249891999997402</v>
+        <v>-0.041494648580837921</v>
       </c>
       <c r="K16" s="0">
-        <v>-0.0033952699999808544</v>
+        <v>0.033856629959637133</v>
       </c>
       <c r="L16" s="0">
-        <v>-0.041599369999982372</v>
+        <v>-0.042189577795273769</v>
       </c>
       <c r="M16" s="0">
-        <v>-0.03308488999999426</v>
+        <v>-0.025044630711771119</v>
       </c>
       <c r="N16" s="0">
-        <v>-0.03588937000000314</v>
+        <v>-0.031204223911179274</v>
       </c>
       <c r="O16" s="0">
-        <v>-0.037131557999995124</v>
+        <v>-0.03455354853112378</v>
       </c>
       <c r="P16" s="0">
-        <v>-0.045049331999987174</v>
+        <v>-0.051729131108967152</v>
       </c>
       <c r="Q16" s="0">
-        <v>-0.048587133999983934</v>
+        <v>-0.059851294696622225</v>
       </c>
       <c r="R16" s="0">
-        <v>-0.0544581519999916</v>
+        <v>-0.072825298869628574</v>
       </c>
       <c r="S16" s="0">
-        <v>-0.055839419999994533</v>
+        <v>-0.076383092205673658</v>
       </c>
       <c r="T16" s="0">
-        <v>-0.034822751999993073</v>
+        <v>-0.035288914676088641</v>
       </c>
       <c r="U16" s="0">
-        <v>-0.043219483999987318</v>
+        <v>-0.058121009369750891</v>
       </c>
       <c r="V16" s="0">
-        <v>-0.032023219999995689</v>
+        <v>-0.03547539787448855</v>
       </c>
       <c r="W16" s="0">
-        <v>-0.017974135999988761</v>
+        <v>-0.0086619765977891585</v>
       </c>
       <c r="X16" s="0">
-        <v>-0.060980281999999164</v>
+        <v>-0.1089626598137438</v>
       </c>
       <c r="Y16" s="0">
-        <v>-0.034372899999990381</v>
+        <v>-0.048407153514077435</v>
       </c>
       <c r="Z16" s="0">
-        <v>-0.052860937999991364</v>
+        <v>-0.092219337583150388</v>
       </c>
       <c r="AA16" s="0">
-        <v>-0.071500858000003831</v>
+        <v>-0.13953848739772665</v>
       </c>
       <c r="AB16" s="0">
-        <v>-0.080719497999989898</v>
+        <v>-0.16955201176406162</v>
       </c>
       <c r="AC16" s="0">
-        <v>-0.081970971999989928</v>
+        <v>-0.1783134167691906</v>
       </c>
       <c r="AD16" s="0">
-        <v>-0.083063037999988154</v>
+        <v>-0.18711320309296564</v>
       </c>
       <c r="AE16" s="0">
-        <v>-0.084014847999991815</v>
+        <v>-0.19503330765274401</v>
       </c>
       <c r="AF16" s="0">
-        <v>-0.084659593999997895</v>
+        <v>-0.20100221661378287</v>
       </c>
       <c r="AG16" s="0">
-        <v>-0.08518779199999571</v>
+        <v>-0.20684319477129878</v>
       </c>
       <c r="AH16" s="0">
-        <v>-0.085627439999992561</v>
+        <v>-0.21409897766554567</v>
       </c>
       <c r="AI16" s="0">
-        <v>-0.086099513999993604</v>
+        <v>-0.22307816109667822</v>
       </c>
       <c r="AJ16" s="0">
-        <v>-0.086430935999995739</v>
+        <v>-0.23213662291508433</v>
       </c>
       <c r="AK16" s="0">
-        <v>-0.086620853999999525</v>
+        <v>-0.24122945107861379</v>
       </c>
       <c r="AL16" s="0">
-        <v>-0.086674689999991728</v>
+        <v>-0.25035457866931821</v>
       </c>
       <c r="AM16" s="0">
-        <v>-0.086598139999988888</v>
+        <v>-0.25951019448530527</v>
       </c>
       <c r="AN16" s="0">
-        <v>-0.086397683999987152</v>
+        <v>-0.26869617769831949</v>
       </c>
       <c r="AO16" s="0">
-        <v>-0.08607918999998887</v>
+        <v>-0.27790986255253863</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>336</v>
+        <v>496</v>
       </c>
       <c r="B17" s="0">
-        <v>-116.66050899999999</v>
+        <v>11.112193565071852</v>
       </c>
       <c r="C17" s="0">
-        <v>-116.6592694</v>
+        <v>11.192131316424655</v>
       </c>
       <c r="D17" s="0">
-        <v>-116.6921936</v>
+        <v>9.3741302829065187</v>
       </c>
       <c r="E17" s="0">
-        <v>-116.80038649999999</v>
+        <v>5.9653175970610288</v>
       </c>
       <c r="F17" s="0">
-        <v>-116.65053839999999</v>
+        <v>11.786564867301285</v>
       </c>
       <c r="G17" s="0">
-        <v>-116.64698199999999</v>
+        <v>12.045674476136387</v>
       </c>
       <c r="H17" s="0">
-        <v>-116.6422309</v>
+        <v>12.40869508713142</v>
       </c>
       <c r="I17" s="0">
-        <v>-116.63922249999999</v>
+        <v>12.649210645582901</v>
       </c>
       <c r="J17" s="0">
-        <v>-116.6946768</v>
+        <v>9.2587922090337447</v>
       </c>
       <c r="K17" s="0">
-        <v>-116.63403959999999</v>
+        <v>13.084488028157285</v>
       </c>
       <c r="L17" s="0">
-        <v>-116.61633459999999</v>
+        <v>14.806803497696549</v>
       </c>
       <c r="M17" s="0">
-        <v>-116.61413639999999</v>
+        <v>15.050532947514396</v>
       </c>
       <c r="N17" s="0">
-        <v>-116.61263</v>
+        <v>15.221950068945205</v>
       </c>
       <c r="O17" s="0">
-        <v>-116.6118573</v>
+        <v>15.311307936202594</v>
       </c>
       <c r="P17" s="0">
-        <v>-116.61141289999999</v>
+        <v>15.363147859849482</v>
       </c>
       <c r="Q17" s="0">
-        <v>-116.61031939999999</v>
+        <v>15.492122013946597</v>
       </c>
       <c r="R17" s="0">
-        <v>-116.6105788</v>
+        <v>15.461342946950905</v>
       </c>
       <c r="S17" s="0">
-        <v>-116.61055689999999</v>
+        <v>15.463937041784851</v>
       </c>
       <c r="T17" s="0">
-        <v>-116.61153759999999</v>
+        <v>15.348568149138677</v>
       </c>
       <c r="U17" s="0">
-        <v>-116.6091773</v>
+        <v>15.629019768404772</v>
       </c>
       <c r="V17" s="0">
-        <v>-116.61249189999999</v>
+        <v>15.237848447951757</v>
       </c>
       <c r="W17" s="0">
-        <v>-116.61045369999999</v>
+        <v>15.476172295196472</v>
       </c>
       <c r="X17" s="0">
-        <v>-116.60952739999999</v>
+        <v>15.586813812146698</v>
       </c>
       <c r="Y17" s="0">
-        <v>-116.60872429999999</v>
+        <v>15.683950935019105</v>
       </c>
       <c r="Z17" s="0">
-        <v>-116.6083094</v>
+        <v>15.734581825888496</v>
       </c>
       <c r="AA17" s="0">
-        <v>-116.6076085</v>
+        <v>15.820816236134835</v>
       </c>
       <c r="AB17" s="0">
-        <v>-116.6069339</v>
+        <v>15.904659400955953</v>
       </c>
       <c r="AC17" s="0">
-        <v>-116.60632</v>
+        <v>15.981689006562448</v>
       </c>
       <c r="AD17" s="0">
-        <v>-116.60576189999999</v>
+        <v>16.052329513874906</v>
       </c>
       <c r="AE17" s="0">
-        <v>-116.6052541</v>
+        <v>16.11711657206499</v>
       </c>
       <c r="AF17" s="0">
-        <v>-116.6047923</v>
+        <v>16.17646418145705</v>
       </c>
       <c r="AG17" s="0">
-        <v>-116.6043722</v>
+        <v>16.230811793332485</v>
       </c>
       <c r="AH17" s="0">
-        <v>-116.60398989999999</v>
+        <v>16.280569391892218</v>
       </c>
       <c r="AI17" s="0">
-        <v>-116.6036419</v>
+        <v>16.326113536629499</v>
       </c>
       <c r="AJ17" s="0">
-        <v>-116.60332539999999</v>
+        <v>16.367744351978008</v>
       </c>
       <c r="AK17" s="0">
-        <v>-116.60303719999999</v>
+        <v>16.405827337928233</v>
       </c>
       <c r="AL17" s="0">
-        <v>-116.60277479999999</v>
+        <v>16.440646804137184</v>
       </c>
       <c r="AM17" s="0">
-        <v>-116.60253569999999</v>
+        <v>16.472496115176465</v>
       </c>
       <c r="AN17" s="0">
-        <v>-116.6023182</v>
+        <v>16.501569518505619</v>
       </c>
       <c r="AO17" s="0">
-        <v>-116.60212</v>
+        <v>16.528147556025992</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>337</v>
+        <v>497</v>
       </c>
       <c r="B18" s="0">
-        <v>-116.66838079999999</v>
+        <v>1.8080897133163241</v>
       </c>
       <c r="C18" s="0">
-        <v>0.012027019999999666</v>
+        <v>-0.17641720644900249</v>
       </c>
       <c r="D18" s="0">
-        <v>-0.010645087999995084</v>
+        <v>-1.4092304865141752</v>
       </c>
       <c r="E18" s="0">
-        <v>-0.068563771999995637</v>
+        <v>-2.7161931911706452</v>
       </c>
       <c r="F18" s="0">
-        <v>0.16152726999998812</v>
+        <v>5.659418997783435</v>
       </c>
       <c r="G18" s="0">
-        <v>0.016966832000003151</v>
+        <v>0.11253115350294371</v>
       </c>
       <c r="H18" s="0">
-        <v>0.017109759999991425</v>
+        <v>0.11711006795277727</v>
       </c>
       <c r="I18" s="0">
-        <v>0.014080382000011937</v>
+        <v>-0.11927970972210683</v>
       </c>
       <c r="J18" s="0">
-        <v>-0.020497650000015355</v>
+        <v>-2.3399151587128708</v>
       </c>
       <c r="K18" s="0">
-        <v>0.08159886399999472</v>
+        <v>4.2823506434824274</v>
       </c>
       <c r="L18" s="0">
-        <v>0.032194207999987512</v>
+        <v>1.4932616007698876</v>
       </c>
       <c r="M18" s="0">
-        <v>0.017878107999999671</v>
+        <v>0.12212036033834474</v>
       </c>
       <c r="N18" s="0">
-        <v>0.017117772000000642</v>
+        <v>0.0331841273624583</v>
       </c>
       <c r="O18" s="0">
-        <v>0.016311899999999824</v>
+        <v>-0.061669466107211017</v>
       </c>
       <c r="P18" s="0">
-        <v>0.016900854000008181</v>
+        <v>-0.00030916580828198699</v>
       </c>
       <c r="Q18" s="0">
-        <v>0.017900541999987141</v>
+        <v>0.110785215026576</v>
       </c>
       <c r="R18" s="0">
-        <v>0.017167511999995</v>
+        <v>0.023066121834111133</v>
       </c>
       <c r="S18" s="0">
-        <v>0.017263323999992863</v>
+        <v>0.035113772923830694</v>
       </c>
       <c r="T18" s="0">
-        <v>0.016381461999992908</v>
+        <v>-0.065125399762318889</v>
       </c>
       <c r="U18" s="0">
-        <v>0.019636447999994644</v>
+        <v>0.31107318951208762</v>
       </c>
       <c r="V18" s="0">
-        <v>0.012803554000010209</v>
+        <v>-0.47425292421577658</v>
       </c>
       <c r="W18" s="0">
-        <v>0.018645962000002569</v>
+        <v>0.198104828541879</v>
       </c>
       <c r="X18" s="0">
-        <v>0.018461825999986914</v>
+        <v>0.17292666609283289</v>
       </c>
       <c r="Y18" s="0">
-        <v>0.018024551999994642</v>
+        <v>0.11945129230175003</v>
       </c>
       <c r="Z18" s="0">
-        <v>0.017694013999994596</v>
+        <v>0.077930381427799636</v>
       </c>
       <c r="AA18" s="0">
-        <v>0.018283812000001731</v>
+        <v>0.14669737276753156</v>
       </c>
       <c r="AB18" s="0">
-        <v>0.018462730000004868</v>
+        <v>0.16645176487624955</v>
       </c>
       <c r="AC18" s="0">
-        <v>0.018589622000002137</v>
+        <v>0.18033063957084611</v>
       </c>
       <c r="AD18" s="0">
-        <v>0.01870539999999643</v>
+        <v>0.19325152662394576</v>
       </c>
       <c r="AE18" s="0">
-        <v>0.018811661999999174</v>
+        <v>0.20533872379463217</v>
       </c>
       <c r="AF18" s="0">
-        <v>0.018908718000000491</v>
+        <v>0.21656676532797584</v>
       </c>
       <c r="AG18" s="0">
-        <v>0.018997854000000203</v>
+        <v>0.22704387028225659</v>
       </c>
       <c r="AH18" s="0">
-        <v>0.019079256000006595</v>
+        <v>0.2367474399796187</v>
       </c>
       <c r="AI18" s="0">
-        <v>0.019153901999994005</v>
+        <v>0.24576288834726442</v>
       </c>
       <c r="AJ18" s="0">
-        <v>0.019221862000003753</v>
+        <v>0.25406559121927891</v>
       </c>
       <c r="AK18" s="0">
-        <v>0.019284792000002327</v>
+        <v>0.26184254046370886</v>
       </c>
       <c r="AL18" s="0">
-        <v>0.019342055999993946</v>
+        <v>0.26898694622547831</v>
       </c>
       <c r="AM18" s="0">
-        <v>0.019394404000005139</v>
+        <v>0.27557640986223036</v>
       </c>
       <c r="AN18" s="0">
-        <v>0.019442385999989042</v>
+        <v>0.2816660475527657</v>
       </c>
       <c r="AO18" s="0">
-        <v>0.019486535999996946</v>
+        <v>0.28731268799349641</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>338</v>
+        <v>498</v>
       </c>
       <c r="B19" s="0">
-        <v>-116.67417329999998</v>
+        <v>1.4759070774031562</v>
       </c>
       <c r="C19" s="0">
-        <v>0.013537184000007585</v>
+        <v>-0.061042806539168694</v>
       </c>
       <c r="D19" s="0">
-        <v>0.0048721640000124466</v>
+        <v>-0.53525229574625521</v>
       </c>
       <c r="E19" s="0">
-        <v>-0.017110481999999649</v>
+        <v>-1.2628558744292957</v>
       </c>
       <c r="F19" s="0">
-        <v>0.13508653000000237</v>
+        <v>4.8266548553042394</v>
       </c>
       <c r="G19" s="0">
-        <v>0.014090670000008743</v>
+        <v>-0.069930286490449328</v>
       </c>
       <c r="H19" s="0">
-        <v>0.015744684000004838</v>
+        <v>0.032662151353418559</v>
       </c>
       <c r="I19" s="0">
-        <v>0.012465348000013421</v>
+        <v>-0.20202090004922035</v>
       </c>
       <c r="J19" s="0">
-        <v>-0.0068597179999798641</v>
+        <v>-1.4123176836212834</v>
       </c>
       <c r="K19" s="0">
-        <v>0.062115986000016221</v>
+        <v>3.1647561285986203</v>
       </c>
       <c r="L19" s="0">
-        <v>0.023540812000014455</v>
+        <v>0.67031942607997042</v>
       </c>
       <c r="M19" s="0">
-        <v>0.017090008000018031</v>
+        <v>0.055437777754306097</v>
       </c>
       <c r="N19" s="0">
-        <v>0.015701604000007308</v>
+        <v>-0.096435125335435898</v>
       </c>
       <c r="O19" s="0">
-        <v>0.014191582000016467</v>
+        <v>-0.2578888235165826</v>
       </c>
       <c r="P19" s="0">
-        <v>0.014502790000015864</v>
+        <v>-0.23130531910554503</v>
       </c>
       <c r="Q19" s="0">
-        <v>0.015357714000010958</v>
+        <v>-0.15190634856914814</v>
       </c>
       <c r="R19" s="0">
-        <v>0.01549871800002478</v>
+        <v>-0.14607546255743128</v>
       </c>
       <c r="S19" s="0">
-        <v>0.015926290000003007</v>
+        <v>-0.10197345280352471</v>
       </c>
       <c r="T19" s="0">
-        <v>0.015883722000019418</v>
+        <v>-0.10566204930256297</v>
       </c>
       <c r="U19" s="0">
-        <v>0.018503314000007265</v>
+        <v>0.18476752341085512</v>
       </c>
       <c r="V19" s="0">
-        <v>0.011118392000021515</v>
+        <v>-0.6233564629570415</v>
       </c>
       <c r="W19" s="0">
-        <v>0.018739696000004358</v>
+        <v>0.21424981328727222</v>
       </c>
       <c r="X19" s="0">
-        <v>0.01841267800001134</v>
+        <v>0.17397361017271415</v>
       </c>
       <c r="Y19" s="0">
-        <v>0.018129244000029132</v>
+        <v>0.1378621691345423</v>
       </c>
       <c r="Z19" s="0">
-        <v>0.018449054000008402</v>
+        <v>0.17331479172484701</v>
       </c>
       <c r="AA19" s="0">
-        <v>0.019098284000016008</v>
+        <v>0.24781082473548308</v>
       </c>
       <c r="AB19" s="0">
-        <v>0.019121512000005225</v>
+        <v>0.24940867714481083</v>
       </c>
       <c r="AC19" s="0">
-        <v>0.019184228000007408</v>
+        <v>0.25591897527739477</v>
       </c>
       <c r="AD19" s="0">
-        <v>0.019242388000002109</v>
+        <v>0.26210467643192814</v>
       </c>
       <c r="AE19" s="0">
-        <v>0.019296136000015451</v>
+        <v>0.2679469432480524</v>
       </c>
       <c r="AF19" s="0">
-        <v>0.019345899999997584</v>
+        <v>0.27346636451016004</v>
       </c>
       <c r="AG19" s="0">
-        <v>0.019391994000010015</v>
+        <v>0.27867440215960743</v>
       </c>
       <c r="AH19" s="0">
-        <v>0.019434428000018045</v>
+        <v>0.28354784860638388</v>
       </c>
       <c r="AI19" s="0">
-        <v>0.01947409000000988</v>
+        <v>0.28817828398265077</v>
       </c>
       <c r="AJ19" s="0">
-        <v>0.019510576000008939</v>
+        <v>0.29249636153636471</v>
       </c>
       <c r="AK19" s="0">
-        <v>0.019544756000009045</v>
+        <v>0.29659829181079878</v>
       </c>
       <c r="AL19" s="0">
-        <v>0.01957591800000813</v>
+        <v>0.30037835752611131</v>
       </c>
       <c r="AM19" s="0">
-        <v>0.019605212000008976</v>
+        <v>0.30397439802555909</v>
       </c>
       <c r="AN19" s="0">
-        <v>0.019632402000006266</v>
+        <v>0.30734610280176605</v>
       </c>
       <c r="AO19" s="0">
-        <v>0.019657448000010902</v>
+        <v>0.31047939408730996</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>339</v>
+        <v>499</v>
       </c>
       <c r="B20" s="0">
-        <v>-116.68315749999999</v>
+        <v>0.9967027992220765</v>
       </c>
       <c r="C20" s="0">
-        <v>0.0079740340000000742</v>
+        <v>-0.33268893129687355</v>
       </c>
       <c r="D20" s="0">
-        <v>0.0098972800000041161</v>
+        <v>-0.23807926234453178</v>
       </c>
       <c r="E20" s="0">
-        <v>-0.00020548400000564015</v>
+        <v>-0.67123854056298904</v>
       </c>
       <c r="F20" s="0">
-        <v>0.073094199999999887</v>
+        <v>2.7363870963110526</v>
       </c>
       <c r="G20" s="0">
-        <v>0.0087677260000020851</v>
+        <v>-0.36944242317039144</v>
       </c>
       <c r="H20" s="0">
-        <v>0.011787724000001276</v>
+        <v>-0.19444488220181913</v>
       </c>
       <c r="I20" s="0">
-        <v>0.0083975020000082168</v>
+        <v>-0.42073654653237685</v>
       </c>
       <c r="J20" s="0">
-        <v>-0.0052297719999927494</v>
+        <v>-1.1931065800411071</v>
       </c>
       <c r="K20" s="0">
-        <v>0.046955109999998967</v>
+        <v>2.0872157091429733</v>
       </c>
       <c r="L20" s="0">
-        <v>0.015752680000005626</v>
+        <v>-0.016878305568161785</v>
       </c>
       <c r="M20" s="0">
-        <v>0.012596401999999784</v>
+        <v>-0.32828763336139422</v>
       </c>
       <c r="N20" s="0">
-        <v>0.012023773999999321</v>
+        <v>-0.40678862229821355</v>
       </c>
       <c r="O20" s="0">
-        <v>0.010024288000010984</v>
+        <v>-0.60204693275768395</v>
       </c>
       <c r="P20" s="0">
-        <v>0.010664208000008557</v>
+        <v>-0.54310629283149059</v>
       </c>
       <c r="Q20" s="0">
-        <v>0.01084647199999722</v>
+        <v>-0.53699420875888926</v>
       </c>
       <c r="R20" s="0">
-        <v>0.012434956000006991</v>
+        <v>-0.41055376271705057</v>
       </c>
       <c r="S20" s="0">
-        <v>0.013089805999996429</v>
+        <v>-0.36115640960367978</v>
       </c>
       <c r="T20" s="0">
-        <v>0.013974794000006341</v>
+        <v>-0.27952375552209541</v>
       </c>
       <c r="U20" s="0">
-        <v>0.014869038000000501</v>
+        <v>-0.18778579673378121</v>
       </c>
       <c r="V20" s="0">
-        <v>0.005670766000008598</v>
+        <v>-1.0992927488656019</v>
       </c>
       <c r="W20" s="0">
-        <v>0.015629328000002829</v>
+        <v>-0.092037018626554112</v>
       </c>
       <c r="X20" s="0">
-        <v>0.015992066000009686</v>
+        <v>-0.072127343139922806</v>
       </c>
       <c r="Y20" s="0">
-        <v>0.01599726999999973</v>
+        <v>-0.083298444566019203</v>
       </c>
       <c r="Z20" s="0">
-        <v>0.016160241999997993</v>
+        <v>-0.073963037184025679</v>
       </c>
       <c r="AA20" s="0">
-        <v>0.017090859999996155</v>
+        <v>0.024195760801015549</v>
       </c>
       <c r="AB20" s="0">
-        <v>0.01733349200000589</v>
+        <v>0.046924993241142576</v>
       </c>
       <c r="AC20" s="0">
-        <v>0.017555086000001552</v>
+        <v>0.068374453855855222</v>
       </c>
       <c r="AD20" s="0">
-        <v>0.017757910000000265</v>
+        <v>0.088612637446316048</v>
       </c>
       <c r="AE20" s="0">
-        <v>0.017943518000009817</v>
+        <v>0.10765506906251607</v>
       </c>
       <c r="AF20" s="0">
-        <v>0.018113354000007575</v>
+        <v>0.12552790980116585</v>
       </c>
       <c r="AG20" s="0">
-        <v>0.018268752000011546</v>
+        <v>0.14226545839271074</v>
       </c>
       <c r="AH20" s="0">
-        <v>0.018410930000015924</v>
+        <v>0.15790774298275367</v>
       </c>
       <c r="AI20" s="0">
-        <v>0.018541196000001037</v>
+        <v>0.17252265032508263</v>
       </c>
       <c r="AJ20" s="0">
-        <v>0.018660154000002649</v>
+        <v>0.18610492653657457</v>
       </c>
       <c r="AK20" s="0">
-        <v>0.018769190000000435</v>
+        <v>0.19875990870409674</v>
       </c>
       <c r="AL20" s="0">
-        <v>0.018868890000007355</v>
+        <v>0.21050323308800814</v>
       </c>
       <c r="AM20" s="0">
-        <v>0.018960325999998418</v>
+        <v>0.22142187399731039</v>
       </c>
       <c r="AN20" s="0">
-        <v>0.019043970000012678</v>
+        <v>0.23153399519294438</v>
       </c>
       <c r="AO20" s="0">
-        <v>0.019120580000006271</v>
+        <v>0.24090169606145803</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="B21" s="0">
-        <v>-116.6947819</v>
+        <v>0.4339672446899997</v>
       </c>
       <c r="C21" s="0">
-        <v>0.0028934500000019625</v>
+        <v>-0.51909252526170202</v>
       </c>
       <c r="D21" s="0">
-        <v>0.0099600839999993696</v>
+        <v>-0.18981695315642805</v>
       </c>
       <c r="E21" s="0">
-        <v>0.00049531600001273546</v>
+        <v>-0.63225793572733202</v>
       </c>
       <c r="F21" s="0">
-        <v>0.035097128000003863</v>
+        <v>1.0123433027201632</v>
       </c>
       <c r="G21" s="0">
-        <v>0.0027552099999894608</v>
+        <v>-0.63423335332623065</v>
       </c>
       <c r="H21" s="0">
-        <v>0.0067343800000116971</v>
+        <v>-0.41820577622868255</v>
       </c>
       <c r="I21" s="0">
-        <v>0.0029812440000114293</v>
+        <v>-0.63784240970629424</v>
       </c>
       <c r="J21" s="0">
-        <v>-0.0046068420000011656</v>
+        <v>-1.0198496352117512</v>
       </c>
       <c r="K21" s="0">
-        <v>0.03877272800001208</v>
+        <v>1.4123746724955004</v>
       </c>
       <c r="L21" s="0">
-        <v>0.007985099999999079</v>
+        <v>-0.53254318135985568</v>
       </c>
       <c r="M21" s="0">
-        <v>0.0079386299999981702</v>
+        <v>-0.59157391086699851</v>
       </c>
       <c r="N21" s="0">
-        <v>0.0077239380000122537</v>
+        <v>-0.65832398056328001</v>
       </c>
       <c r="O21" s="0">
-        <v>0.0051699100000064391</v>
+        <v>-0.88541104733055076</v>
       </c>
       <c r="P21" s="0">
-        <v>0.0075947999999925742</v>
+        <v>-0.6939820782278685</v>
       </c>
       <c r="Q21" s="0">
-        <v>0.007094076000001337</v>
+        <v>-0.73870811497523325</v>
       </c>
       <c r="R21" s="0">
-        <v>0.0095014980000058813</v>
+        <v>-0.56093816176293754</v>
       </c>
       <c r="S21" s="0">
-        <v>0.010841282000001229</v>
+        <v>-0.48642421880772324</v>
       </c>
       <c r="T21" s="0">
-        <v>0.013145910000005756</v>
+        <v>-0.30200699565668121</v>
       </c>
       <c r="U21" s="0">
-        <v>0.012783794000000626</v>
+        <v>-0.34800597639611142</v>
       </c>
       <c r="V21" s="0">
-        <v>0.0011208020000168517</v>
+        <v>-1.3619182524487807</v>
       </c>
       <c r="W21" s="0">
-        <v>0.012670153999991385</v>
+        <v>-0.30561774832394811</v>
       </c>
       <c r="X21" s="0">
-        <v>0.013261642000017559</v>
+        <v>-0.28999743835139696</v>
       </c>
       <c r="Y21" s="0">
-        <v>0.013193258000001151</v>
+        <v>-0.32341554635896014</v>
       </c>
       <c r="Z21" s="0">
-        <v>0.013094179999995958</v>
+        <v>-0.35112713966673231</v>
       </c>
       <c r="AA21" s="0">
-        <v>0.01395601400000146</v>
+        <v>-0.27960539926632105</v>
       </c>
       <c r="AB21" s="0">
-        <v>0.014234831999999642</v>
+        <v>-0.26460034118039627</v>
       </c>
       <c r="AC21" s="0">
-        <v>0.014716278000008742</v>
+        <v>-0.22452107563613902</v>
       </c>
       <c r="AD21" s="0">
-        <v>0.015157404000007091</v>
+        <v>-0.186184598678931</v>
       </c>
       <c r="AE21" s="0">
-        <v>0.015561220000009257</v>
+        <v>-0.14968916405832164</v>
       </c>
       <c r="AF21" s="0">
-        <v>0.015930908000001409</v>
+        <v>-0.11505607175565304</v>
       </c>
       <c r="AG21" s="0">
-        <v>0.01626923799999247</v>
+        <v>-0.082302451436026394</v>
       </c>
       <c r="AH21" s="0">
-        <v>0.016578768000002242</v>
+        <v>-0.051424536365789045</v>
       </c>
       <c r="AI21" s="0">
-        <v>0.016862137999993365</v>
+        <v>-0.02236610746101712</v>
       </c>
       <c r="AJ21" s="0">
-        <v>0.01712138000000607</v>
+        <v>0.0048943088425406865</v>
       </c>
       <c r="AK21" s="0">
-        <v>0.017358408000006875</v>
+        <v>0.030397390605630719</v>
       </c>
       <c r="AL21" s="0">
-        <v>0.017575534000002335</v>
+        <v>0.054258730292422598</v>
       </c>
       <c r="AM21" s="0">
-        <v>0.01777415400000848</v>
+        <v>0.076510341039651222</v>
       </c>
       <c r="AN21" s="0">
-        <v>0.017955860000000712</v>
+        <v>0.097228121690554253</v>
       </c>
       <c r="AO21" s="0">
-        <v>0.018122031999993737</v>
+        <v>0.11648149903793738</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>341</v>
+        <v>501</v>
       </c>
       <c r="B22" s="0">
-        <v>-116.7165421</v>
+        <v>-0.47577486334376801</v>
       </c>
       <c r="C22" s="0">
-        <v>-0.0064081379999976207</v>
+        <v>-0.80873539099481639</v>
       </c>
       <c r="D22" s="0">
-        <v>0.0027671819999994796</v>
+        <v>-0.43298766564134644</v>
       </c>
       <c r="E22" s="0">
-        <v>-0.0055327280000057044</v>
+        <v>-0.79029546553267283</v>
       </c>
       <c r="F22" s="0">
-        <v>0.013603865999996856</v>
+        <v>0.010988212950822047</v>
       </c>
       <c r="G22" s="0">
-        <v>-0.0040136739999923066</v>
+        <v>-0.82197565351654356</v>
       </c>
       <c r="H22" s="0">
-        <v>0.0002086100000155966</v>
+        <v>-0.62769938149540383</v>
       </c>
       <c r="I22" s="0">
-        <v>-0.0022870219999902019</v>
+        <v>-0.75248873137903571</v>
       </c>
       <c r="J22" s="0">
-        <v>-0.0075601579999897695</v>
+        <v>-0.9705338458069469</v>
       </c>
       <c r="K22" s="0">
-        <v>0.030165622000012604</v>
+        <v>0.81843195980347683</v>
       </c>
       <c r="L22" s="0">
-        <v>0.0011375260000079379</v>
+        <v>-0.80544634379026947</v>
       </c>
       <c r="M22" s="0">
-        <v>0.00346962199999723</v>
+        <v>-0.70920689799576031</v>
       </c>
       <c r="N22" s="0">
-        <v>0.0025828160000003209</v>
+        <v>-0.82305389300716747</v>
       </c>
       <c r="O22" s="0">
-        <v>0.0011210699999963936</v>
+        <v>-0.96879091250142102</v>
       </c>
       <c r="P22" s="0">
-        <v>0.0040342700000053355</v>
+        <v>-0.78641727170991349</v>
       </c>
       <c r="Q22" s="0">
-        <v>0.0042306360000026189</v>
+        <v>-0.79656923918404465</v>
       </c>
       <c r="R22" s="0">
-        <v>0.0070608979999917665</v>
+        <v>-0.60790850481967917</v>
       </c>
       <c r="S22" s="0">
-        <v>0.0086799160000055053</v>
+        <v>-0.52821159576599996</v>
       </c>
       <c r="T22" s="0">
-        <v>0.012295208000011826</v>
+        <v>-0.29641427749300919</v>
       </c>
       <c r="U22" s="0">
-        <v>0.011212060000005408</v>
+        <v>-0.41726124182258856</v>
       </c>
       <c r="V22" s="0">
-        <v>-0.0010573499999964042</v>
+        <v>-1.3778918300295309</v>
       </c>
       <c r="W22" s="0">
-        <v>0.011766118000011261</v>
+        <v>-0.30146439199430769</v>
       </c>
       <c r="X22" s="0">
-        <v>0.011898540000004232</v>
+        <v>-0.32007344831118861</v>
       </c>
       <c r="Y22" s="0">
-        <v>0.011974587999986852</v>
+        <v>-0.35382820666940357</v>
       </c>
       <c r="Z22" s="0">
-        <v>0.011747139999997103</v>
+        <v>-0.40025130511444107</v>
       </c>
       <c r="AA22" s="0">
-        <v>0.013065810000000511</v>
+        <v>-0.30114572894392538</v>
       </c>
       <c r="AB22" s="0">
-        <v>0.01334903000001475</v>
+        <v>-0.2939344962343588</v>
       </c>
       <c r="AC22" s="0">
-        <v>0.013906546000015396</v>
+        <v>-0.25599896898464586</v>
       </c>
       <c r="AD22" s="0">
-        <v>0.014417993999998657</v>
+        <v>-0.21906309180313085</v>
       </c>
       <c r="AE22" s="0">
-        <v>0.014886462000006873</v>
+        <v>-0.18334700213983698</v>
       </c>
       <c r="AF22" s="0">
-        <v>0.015315616000009413</v>
+        <v>-0.14895771229706972</v>
       </c>
       <c r="AG22" s="0">
-        <v>0.015708498000009286</v>
+        <v>-0.11600782976193853</v>
       </c>
       <c r="AH22" s="0">
-        <v>0.016068130000007841</v>
+        <v>-0.084559770315822777</v>
       </c>
       <c r="AI22" s="0">
-        <v>0.016397417999996833</v>
+        <v>-0.054638869544227309</v>
       </c>
       <c r="AJ22" s="0">
-        <v>0.016698352000005912</v>
+        <v>-0.026326318307209318</v>
       </c>
       <c r="AK22" s="0">
-        <v>0.016973702000001367</v>
+        <v>0.00042458296035238335</v>
       </c>
       <c r="AL22" s="0">
-        <v>0.017225818000000004</v>
+        <v>0.02565396136998167</v>
       </c>
       <c r="AM22" s="0">
-        <v>0.017456056000000331</v>
+        <v>0.049315617771001914</v>
       </c>
       <c r="AN22" s="0">
-        <v>0.017666738000002624</v>
+        <v>0.071509443200682823</v>
       </c>
       <c r="AO22" s="0">
-        <v>0.017859386000012023</v>
+        <v>0.092265933930751165</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>342</v>
+        <v>502</v>
       </c>
       <c r="B23" s="0">
-        <v>-116.75656499999999</v>
+        <v>-1.7860605633308562</v>
       </c>
       <c r="C23" s="0">
-        <v>-0.026540341999989892</v>
+        <v>-1.239896519927727</v>
       </c>
       <c r="D23" s="0">
-        <v>-0.015208287999996628</v>
+        <v>-0.89505346042239253</v>
       </c>
       <c r="E23" s="0">
-        <v>-0.022357733999996299</v>
+        <v>-1.1504806283714273</v>
       </c>
       <c r="F23" s="0">
-        <v>-0.0082061579999930245</v>
+        <v>-0.70361570240151039</v>
       </c>
       <c r="G23" s="0">
-        <v>-0.021206367999994313</v>
+        <v>-1.2163350803554143</v>
       </c>
       <c r="H23" s="0">
-        <v>-0.016466627999989214</v>
+        <v>-1.0618320670424832</v>
       </c>
       <c r="I23" s="0">
-        <v>-0.019331272000002286</v>
+        <v>-1.178393793419747</v>
       </c>
       <c r="J23" s="0">
-        <v>-0.025392607999989991</v>
+        <v>-1.3629499396616001</v>
       </c>
       <c r="K23" s="0">
-        <v>0.015478786000002742</v>
+        <v>0.097840726129378303</v>
       </c>
       <c r="L23" s="0">
-        <v>-0.012134352000003901</v>
+        <v>-1.2128024887367956</v>
       </c>
       <c r="M23" s="0">
-        <v>-0.007956526000000963</v>
+        <v>-1.0465778605585778</v>
       </c>
       <c r="N23" s="0">
-        <v>-0.0092184179999890148</v>
+        <v>-1.1691856872248465</v>
       </c>
       <c r="O23" s="0">
-        <v>-0.011280400000003965</v>
+        <v>-1.3280401681414471</v>
       </c>
       <c r="P23" s="0">
-        <v>-0.0051837160000047788</v>
+        <v>-1.0825049225634802</v>
       </c>
       <c r="Q23" s="0">
-        <v>-0.0035261000000019749</v>
+        <v>-1.0377545351567075</v>
       </c>
       <c r="R23" s="0">
-        <v>5.7698000006212169e-05</v>
+        <v>-0.87447768148289862</v>
       </c>
       <c r="S23" s="0">
-        <v>0.0023017700000167451</v>
+        <v>-0.78058820935043438</v>
       </c>
       <c r="T23" s="0">
-        <v>0.0080325619999968012</v>
+        <v>-0.48303388826207189</v>
       </c>
       <c r="U23" s="0">
-        <v>0.0058148659999943675</v>
+        <v>-0.70757658719746497</v>
       </c>
       <c r="V23" s="0">
-        <v>-0.0031738180000075999</v>
+        <v>-1.3452029511385188</v>
       </c>
       <c r="W23" s="0">
-        <v>0.011019789999991758</v>
+        <v>-0.29446144553467113</v>
       </c>
       <c r="X23" s="0">
-        <v>0.010854817999998545</v>
+        <v>-0.31810122429193732</v>
       </c>
       <c r="Y23" s="0">
-        <v>0.010189392000015118</v>
+        <v>-0.39300946517587076</v>
       </c>
       <c r="Z23" s="0">
-        <v>0.0093821940000111681</v>
+        <v>-0.49438933562332149</v>
       </c>
       <c r="AA23" s="0">
-        <v>0.011077156000013133</v>
+        <v>-0.39171586630386079</v>
       </c>
       <c r="AB23" s="0">
-        <v>0.011481185999997479</v>
+        <v>-0.38598293776424475</v>
       </c>
       <c r="AC23" s="0">
-        <v>0.01218668799999989</v>
+        <v>-0.34888852512472646</v>
       </c>
       <c r="AD23" s="0">
-        <v>0.012835178000003111</v>
+        <v>-0.31193119922507406</v>
       </c>
       <c r="AE23" s="0">
-        <v>0.013430446000000984</v>
+        <v>-0.27542455325287929</v>
       </c>
       <c r="AF23" s="0">
-        <v>0.013976835999997661</v>
+        <v>-0.23957340734000201</v>
       </c>
       <c r="AG23" s="0">
-        <v>0.014477881999994224</v>
+        <v>-0.20460573376902366</v>
       </c>
       <c r="AH23" s="0">
-        <v>0.014937282000005325</v>
+        <v>-0.1706746388603336</v>
       </c>
       <c r="AI23" s="0">
-        <v>0.015358114000008527</v>
+        <v>-0.13793977895591658</v>
       </c>
       <c r="AJ23" s="0">
-        <v>0.015743638000003557</v>
+        <v>-0.10649102687413804</v>
       </c>
       <c r="AK23" s="0">
-        <v>0.016096779999998034</v>
+        <v>-0.076396846608717636</v>
       </c>
       <c r="AL23" s="0">
-        <v>0.01641996200000051</v>
+        <v>-0.047736461753236765</v>
       </c>
       <c r="AM23" s="0">
-        <v>0.016715877999999407</v>
+        <v>-0.020513510186051891</v>
       </c>
       <c r="AN23" s="0">
-        <v>0.016986808000012843</v>
+        <v>0.0052634382854758023</v>
       </c>
       <c r="AO23" s="0">
-        <v>0.017234818000005703</v>
+        <v>0.029597834683479263</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>343</v>
+        <v>503</v>
       </c>
       <c r="B24" s="0">
-        <v>-116.8149335</v>
+        <v>-3.1490875641051423</v>
       </c>
       <c r="C24" s="0">
-        <v>-0.048146699999989551</v>
+        <v>-1.3291196650073853</v>
       </c>
       <c r="D24" s="0">
-        <v>-0.030751331999994136</v>
+        <v>-0.95763756944841827</v>
       </c>
       <c r="E24" s="0">
-        <v>-0.041785835999988308</v>
+        <v>-1.2474656588229438</v>
       </c>
       <c r="F24" s="0">
-        <v>-0.02421084399998108</v>
+        <v>-0.86722408794613037</v>
       </c>
       <c r="G24" s="0">
-        <v>-0.037661888000002364</v>
+        <v>-1.2497601986687115</v>
       </c>
       <c r="H24" s="0">
-        <v>-0.028849747999998954</v>
+        <v>-1.0476184567951428</v>
       </c>
       <c r="I24" s="0">
-        <v>-0.032286796000008167</v>
+        <v>-1.1615303513297603</v>
       </c>
       <c r="J24" s="0">
-        <v>-0.042531209999978614</v>
+        <v>-1.3820265501981692</v>
       </c>
       <c r="K24" s="0">
-        <v>0.0067004519999898093</v>
+        <v>-0.13680372462042931</v>
       </c>
       <c r="L24" s="0">
-        <v>-0.022490826000009179</v>
+        <v>-1.1874971443667359</v>
       </c>
       <c r="M24" s="0">
-        <v>-0.01743850799999791</v>
+        <v>-1.0604943651008167</v>
       </c>
       <c r="N24" s="0">
-        <v>-0.017916188000000943</v>
+        <v>-1.1240502805796282</v>
       </c>
       <c r="O24" s="0">
-        <v>-0.020659753999993313</v>
+        <v>-1.2586253909472023</v>
       </c>
       <c r="P24" s="0">
-        <v>-0.012086913999993953</v>
+        <v>-0.99902279242343583</v>
       </c>
       <c r="Q24" s="0">
-        <v>-0.010052810000004797</v>
+        <v>-1.0167425227345794</v>
       </c>
       <c r="R24" s="0">
-        <v>-0.0047865539999918383</v>
+        <v>-0.85253228897743449</v>
       </c>
       <c r="S24" s="0">
-        <v>-0.0011927380000003041</v>
+        <v>-0.74890424006838863</v>
       </c>
       <c r="T24" s="0">
-        <v>0.0055095879999953468</v>
+        <v>-0.4691330281215636</v>
       </c>
       <c r="U24" s="0">
-        <v>0.0017891699999950106</v>
+        <v>-0.74896095980738187</v>
       </c>
       <c r="V24" s="0">
-        <v>-0.0052079799999944498</v>
+        <v>-1.1955753709594521</v>
       </c>
       <c r="W24" s="0">
-        <v>0.0076175580000068521</v>
+        <v>-0.43033887136531085</v>
       </c>
       <c r="X24" s="0">
-        <v>0.0077277620000018032</v>
+        <v>-0.44720999739607475</v>
       </c>
       <c r="Y24" s="0">
-        <v>0.0063858640000091782</v>
+        <v>-0.54044571015552711</v>
       </c>
       <c r="Z24" s="0">
-        <v>0.0063021140000074638</v>
+        <v>-0.5752265380856505</v>
       </c>
       <c r="AA24" s="0">
-        <v>0.0085251179999943361</v>
+        <v>-0.47162853237220181</v>
       </c>
       <c r="AB24" s="0">
-        <v>0.0088241559999886476</v>
+        <v>-0.48973907374620146</v>
       </c>
       <c r="AC24" s="0">
-        <v>0.0097412420000040356</v>
+        <v>-0.45515348932673666</v>
       </c>
       <c r="AD24" s="0">
-        <v>0.010586578000015834</v>
+        <v>-0.41961144236319042</v>
       </c>
       <c r="AE24" s="0">
-        <v>0.011364854000007085</v>
+        <v>-0.38348028497135439</v>
       </c>
       <c r="AF24" s="0">
-        <v>0.012080428000004417</v>
+        <v>-0.34712129939142194</v>
       </c>
       <c r="AG24" s="0">
-        <v>0.012738224000003129</v>
+        <v>-0.31080617042811309</v>
       </c>
       <c r="AH24" s="0">
-        <v>0.013342040000011934</v>
+        <v>-0.2748532335795974</v>
       </c>
       <c r="AI24" s="0">
-        <v>0.01389624200000128</v>
+        <v>-0.23947909379262533</v>
       </c>
       <c r="AJ24" s="0">
-        <v>0.014404464000008943</v>
+        <v>-0.2049087240350618</v>
       </c>
       <c r="AK24" s="0">
-        <v>0.014870126000005257</v>
+        <v>-0.17133757116025838</v>
       </c>
       <c r="AL24" s="0">
-        <v>0.015296708000008152</v>
+        <v>-0.13889565280093238</v>
       </c>
       <c r="AM24" s="0">
-        <v>0.015687776000007148</v>
+        <v>-0.10765142618726078</v>
       </c>
       <c r="AN24" s="0">
-        <v>0.016045674000011445</v>
+        <v>-0.077746446676479605</v>
       </c>
       <c r="AO24" s="0">
-        <v>0.016373323999999911</v>
+        <v>-0.049216128846108417</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>344</v>
+        <v>504</v>
       </c>
       <c r="B25" s="0">
-        <v>-116.8987995</v>
+        <v>-4.4552403480175498</v>
       </c>
       <c r="C25" s="0">
-        <v>-0.074050270000000751</v>
+        <v>-1.2457954891914167</v>
       </c>
       <c r="D25" s="0">
-        <v>-0.057024608000006083</v>
+        <v>-0.99075757345761295</v>
       </c>
       <c r="E25" s="0">
-        <v>-0.074376057999998579</v>
+        <v>-1.298071375396429</v>
       </c>
       <c r="F25" s="0">
-        <v>-0.046931905999997525</v>
+        <v>-0.91590434823970335</v>
       </c>
       <c r="G25" s="0">
-        <v>-0.06594778400000223</v>
+        <v>-1.2876459855401139</v>
       </c>
       <c r="H25" s="0">
-        <v>-0.052516483999994534</v>
+        <v>-1.0788542911021759</v>
       </c>
       <c r="I25" s="0">
-        <v>-0.058126048000005426</v>
+        <v>-1.218485298605267</v>
       </c>
       <c r="J25" s="0">
-        <v>-0.074168520000000626</v>
+        <v>-1.4533565462586175</v>
       </c>
       <c r="K25" s="0">
-        <v>-0.01208613400000047</v>
+        <v>-0.4106243147076255</v>
       </c>
       <c r="L25" s="0">
-        <v>-0.044844191999985128</v>
+        <v>-1.2675681723628467</v>
       </c>
       <c r="M25" s="0">
-        <v>-0.037190487999993138</v>
+        <v>-1.1652443137741535</v>
       </c>
       <c r="N25" s="0">
-        <v>-0.035365413999997486</v>
+        <v>-1.1924541202956451</v>
       </c>
       <c r="O25" s="0">
-        <v>-0.039734275999990132</v>
+        <v>-1.327689617521091</v>
       </c>
       <c r="P25" s="0">
-        <v>-0.027916399999995178</v>
+        <v>-1.0733801892217323</v>
       </c>
       <c r="Q25" s="0">
-        <v>-0.023387177999993014</v>
+        <v>-1.0583594110876537</v>
       </c>
       <c r="R25" s="0">
-        <v>-0.016574019999993084</v>
+        <v>-0.96533451745535082</v>
       </c>
       <c r="S25" s="0">
-        <v>-0.012167290000007824</v>
+        <v>-0.91403995719597164</v>
       </c>
       <c r="T25" s="0">
-        <v>-0.0023438719999973046</v>
+        <v>-0.64109498102401452</v>
       </c>
       <c r="U25" s="0">
-        <v>-0.0081310019999989436</v>
+        <v>-0.96530910080661125</v>
       </c>
       <c r="V25" s="0">
-        <v>-0.010478205999987722</v>
+        <v>-1.1354857717118414</v>
       </c>
       <c r="W25" s="0">
-        <v>0.0048205560000127434</v>
+        <v>-0.45580308542226788</v>
       </c>
       <c r="X25" s="0">
-        <v>0.0048979220000120449</v>
+        <v>-0.49869828963941881</v>
       </c>
       <c r="Y25" s="0">
-        <v>0.0036115880000124889</v>
+        <v>-0.58840244262981434</v>
       </c>
       <c r="Z25" s="0">
-        <v>0.0029835079999998015</v>
+        <v>-0.62412984970615804</v>
       </c>
       <c r="AA25" s="0">
-        <v>0.0061556680000052211</v>
+        <v>-0.48423636047410173</v>
       </c>
       <c r="AB25" s="0">
-        <v>0.0060499440000114646</v>
+        <v>-0.53979207027838738</v>
       </c>
       <c r="AC25" s="0">
-        <v>0.0071483860000114419</v>
+        <v>-0.51392824540961368</v>
       </c>
       <c r="AD25" s="0">
-        <v>0.0081649540000086063</v>
+        <v>-0.48609198446012958</v>
       </c>
       <c r="AE25" s="0">
-        <v>0.0091046599999913269</v>
+        <v>-0.45660502244430035</v>
       </c>
       <c r="AF25" s="0">
-        <v>0.0099721779999981663</v>
+        <v>-0.42581111603685229</v>
       </c>
       <c r="AG25" s="0">
-        <v>0.010772443999996995</v>
+        <v>-0.39402384287330355</v>
       </c>
       <c r="AH25" s="0">
-        <v>0.011509771999996588</v>
+        <v>-0.36158520437434877</v>
       </c>
       <c r="AI25" s="0">
-        <v>0.012188928000000487</v>
+        <v>-0.32876676915717978</v>
       </c>
       <c r="AJ25" s="0">
-        <v>0.012813758000007169</v>
+        <v>-0.29587964366879743</v>
       </c>
       <c r="AK25" s="0">
-        <v>0.013388661999996998</v>
+        <v>-0.26314110860577544</v>
       </c>
       <c r="AL25" s="0">
-        <v>0.013917121999995175</v>
+        <v>-0.23080371261526852</v>
       </c>
       <c r="AM25" s="0">
-        <v>0.014403082000001177</v>
+        <v>-0.19902671685605425</v>
       </c>
       <c r="AN25" s="0">
-        <v>0.014849273999999468</v>
+        <v>-0.16803668286127998</v>
       </c>
       <c r="AO25" s="0">
-        <v>0.015259184000001369</v>
+        <v>-0.13793460495570387</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>345</v>
+        <v>505</v>
       </c>
       <c r="B26" s="0">
-        <v>-117.0178883</v>
+        <v>-5.6207084853144673</v>
       </c>
       <c r="C26" s="0">
-        <v>-0.11056048999999346</v>
+        <v>-1.1002098605005526</v>
       </c>
       <c r="D26" s="0">
-        <v>-0.089769001999993048</v>
+        <v>-0.91315822554133674</v>
       </c>
       <c r="E26" s="0">
-        <v>-0.10607906799998146</v>
+        <v>-1.0888290679672601</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.072431263999984008</v>
+        <v>-0.79411476964521044</v>
       </c>
       <c r="G26" s="0">
-        <v>-0.10108380000000805</v>
+        <v>-1.1555656528055063</v>
       </c>
       <c r="H26" s="0">
-        <v>-0.079494109999994844</v>
+        <v>-0.9468432542269466</v>
       </c>
       <c r="I26" s="0">
-        <v>-0.08635584799999263</v>
+        <v>-1.0653292260660883</v>
       </c>
       <c r="J26" s="0">
-        <v>-0.11184758199999179</v>
+        <v>-1.3044089264221415</v>
       </c>
       <c r="K26" s="0">
-        <v>-0.032163877999987545</v>
+        <v>-0.46274417824802505</v>
       </c>
       <c r="L26" s="0">
-        <v>-0.07425336199998922</v>
+        <v>-1.1631823334777143</v>
       </c>
       <c r="M26" s="0">
-        <v>-0.063875477999995933</v>
+        <v>-1.0979714873255459</v>
       </c>
       <c r="N26" s="0">
-        <v>-0.06019993199999929</v>
+        <v>-1.1357336864468148</v>
       </c>
       <c r="O26" s="0">
-        <v>-0.06188994799999703</v>
+        <v>-1.224291885846067</v>
       </c>
       <c r="P26" s="0">
-        <v>-0.048995785999987884</v>
+        <v>-1.0349367157177833</v>
       </c>
       <c r="Q26" s="0">
-        <v>-0.04436460799999109</v>
+        <v>-1.0504492096758069</v>
       </c>
       <c r="R26" s="0">
-        <v>-0.038034684000006092</v>
+        <v>-1.050360050464922</v>
       </c>
       <c r="S26" s="0">
-        <v>-0.030081631999987035</v>
+        <v>-1.0236207520880107</v>
       </c>
       <c r="T26" s="0">
-        <v>-0.014126387999989998</v>
+        <v>-0.74532293723193899</v>
       </c>
       <c r="U26" s="0">
-        <v>-0.022561867999992824</v>
+        <v>-1.1240763524955786</v>
       </c>
       <c r="V26" s="0">
-        <v>-0.025706283999990642</v>
+        <v>-1.2707571571068519</v>
       </c>
       <c r="W26" s="0">
-        <v>-0.0092175359999902007</v>
+        <v>-0.80550902236683786</v>
       </c>
       <c r="X26" s="0">
-        <v>-0.0079626960000029889</v>
+        <v>-0.88296056380020094</v>
       </c>
       <c r="Y26" s="0">
-        <v>-0.0094733420000028268</v>
+        <v>-1.0102718361734704</v>
       </c>
       <c r="Z26" s="0">
-        <v>-0.011220161999996758</v>
+        <v>-1.1009655741396147</v>
       </c>
       <c r="AA26" s="0">
-        <v>-0.005424995999983917</v>
+        <v>-0.86729447439097851</v>
       </c>
       <c r="AB26" s="0">
-        <v>-0.0058564459999916885</v>
+        <v>-0.95047841529662991</v>
       </c>
       <c r="AC26" s="0">
-        <v>-0.0039326259999898916</v>
+        <v>-0.93263324912562795</v>
       </c>
       <c r="AD26" s="0">
-        <v>-0.0021245739999886659</v>
+        <v>-0.91039551368123295</v>
       </c>
       <c r="AE26" s="0">
-        <v>-0.00044217199998852763</v>
+        <v>-0.88426150150870897</v>
       </c>
       <c r="AF26" s="0">
-        <v>0.0011204800000155224</v>
+        <v>-0.85460166064083243</v>
       </c>
       <c r="AG26" s="0">
-        <v>0.0025698380000034327</v>
+        <v>-0.82180426262558592</v>
       </c>
       <c r="AH26" s="0">
-        <v>0.003912725999999811</v>
+        <v>-0.7862686530166636</v>
       </c>
       <c r="AI26" s="0">
-        <v>0.0051553340000123349</v>
+        <v>-0.74844775664999985</v>
       </c>
       <c r="AJ26" s="0">
-        <v>0.0063039140000040739</v>
+        <v>-0.70879014596343159</v>
       </c>
       <c r="AK26" s="0">
-        <v>0.0073650800000177874</v>
+        <v>-0.66769952568825597</v>
       </c>
       <c r="AL26" s="0">
-        <v>0.00834451200001185</v>
+        <v>-0.62561494990160682</v>
       </c>
       <c r="AM26" s="0">
-        <v>0.0092482540000173863</v>
+        <v>-0.58290622155154304</v>
       </c>
       <c r="AN26" s="0">
-        <v>0.010081322000023096</v>
+        <v>-0.5399761791858172</v>
       </c>
       <c r="AO26" s="0">
-        <v>0.010849296000021713</v>
+        <v>-0.49712369396056172</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>346</v>
+        <v>506</v>
       </c>
       <c r="B27" s="0">
-        <v>-117.16614799999999</v>
+        <v>-6.5130280583996081</v>
       </c>
       <c r="C27" s="0">
-        <v>-0.14209716599998634</v>
+        <v>-0.83446930723014723</v>
       </c>
       <c r="D27" s="0">
-        <v>-0.12250088000000536</v>
+        <v>-0.72607529215551392</v>
       </c>
       <c r="E27" s="0">
-        <v>-0.1456682079999907</v>
+        <v>-0.88009937986906184</v>
       </c>
       <c r="F27" s="0">
-        <v>-0.10755428000000355</v>
+        <v>-0.67383919077934562</v>
       </c>
       <c r="G27" s="0">
-        <v>-0.14860419000000169</v>
+        <v>-0.97262419822402724</v>
       </c>
       <c r="H27" s="0">
-        <v>-0.11397974599998539</v>
+        <v>-0.77666251741298387</v>
       </c>
       <c r="I27" s="0">
-        <v>-0.12823544399999909</v>
+        <v>-0.9141223550127312</v>
       </c>
       <c r="J27" s="0">
-        <v>-0.17450187199999467</v>
+        <v>-1.1717687175375799</v>
       </c>
       <c r="K27" s="0">
-        <v>-0.071017212000002328</v>
+        <v>-0.52046714080139844</v>
       </c>
       <c r="L27" s="0">
-        <v>-0.12289178599999806</v>
+        <v>-1.0607865563673347</v>
       </c>
       <c r="M27" s="0">
-        <v>-0.10833899600000185</v>
+        <v>-0.9987672244053164</v>
       </c>
       <c r="N27" s="0">
-        <v>-0.10823240399999312</v>
+        <v>-1.0879284088311167</v>
       </c>
       <c r="O27" s="0">
-        <v>-0.10789849599999135</v>
+        <v>-1.1705069193118691</v>
       </c>
       <c r="P27" s="0">
-        <v>-0.097808373999997311</v>
+        <v>-1.1256942829116023</v>
       </c>
       <c r="Q27" s="0">
-        <v>-0.091574146000000578</v>
+        <v>-1.1398761553619325</v>
       </c>
       <c r="R27" s="0">
-        <v>-0.086518415999991216</v>
+        <v>-1.1945368940142829</v>
       </c>
       <c r="S27" s="0">
-        <v>-0.075937197999992545</v>
+        <v>-1.2185488076399367</v>
       </c>
       <c r="T27" s="0">
-        <v>-0.050652192000002483</v>
+        <v>-1.0539715392105695</v>
       </c>
       <c r="U27" s="0">
-        <v>-0.063652047999995798</v>
+        <v>-1.4953746170402902</v>
       </c>
       <c r="V27" s="0">
-        <v>-0.068721360000013387</v>
+        <v>-1.6829142536377868</v>
       </c>
       <c r="W27" s="0">
-        <v>-0.044532800000000261</v>
+        <v>-1.2750721898963937</v>
       </c>
       <c r="X27" s="0">
-        <v>-0.041025687999991955</v>
+        <v>-1.4064865614034463</v>
       </c>
       <c r="Y27" s="0">
-        <v>-0.042756776000005825</v>
+        <v>-1.6267348106756949</v>
       </c>
       <c r="Z27" s="0">
-        <v>-0.045388667999988197</v>
+        <v>-1.764400493089457</v>
       </c>
       <c r="AA27" s="0">
-        <v>-0.036394541999983598</v>
+        <v>-1.5402324172232518</v>
       </c>
       <c r="AB27" s="0">
-        <v>-0.037931009999995435</v>
+        <v>-1.6559752736217095</v>
       </c>
       <c r="AC27" s="0">
-        <v>-0.035104083999998092</v>
+        <v>-1.6615731065739545</v>
       </c>
       <c r="AD27" s="0">
-        <v>-0.030916734000002943</v>
+        <v>-1.6566418021010534</v>
       </c>
       <c r="AE27" s="0">
-        <v>-0.026953379999996141</v>
+        <v>-1.6435595423358071</v>
       </c>
       <c r="AF27" s="0">
-        <v>-0.023244698000000508</v>
+        <v>-1.622598585688348</v>
       </c>
       <c r="AG27" s="0">
-        <v>-0.019783684000004964</v>
+        <v>-1.5940188196032696</v>
       </c>
       <c r="AH27" s="0">
-        <v>-0.016561065999995517</v>
+        <v>-1.5581773554493568</v>
       </c>
       <c r="AI27" s="0">
-        <v>-0.013567695999996854</v>
+        <v>-1.5156062135052706</v>
       </c>
       <c r="AJ27" s="0">
-        <v>-0.010792072000002317</v>
+        <v>-1.4668602614963977</v>
       </c>
       <c r="AK27" s="0">
-        <v>-0.0082231279999844809</v>
+        <v>-1.4126142014602678</v>
       </c>
       <c r="AL27" s="0">
-        <v>-0.0058497280000024965</v>
+        <v>-1.3536210698776703</v>
       </c>
       <c r="AM27" s="0">
-        <v>-0.0036595880000063197</v>
+        <v>-1.2905986874903121</v>
       </c>
       <c r="AN27" s="0">
-        <v>-0.0016417519999989416</v>
+        <v>-1.2243571775078337</v>
       </c>
       <c r="AO27" s="0">
-        <v>0.00021558800000187617</v>
+        <v>-1.1556281802145085</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>347</v>
+        <v>507</v>
       </c>
       <c r="B28" s="0">
-        <v>-117.3211757</v>
+        <v>-7.1129329966667791</v>
       </c>
       <c r="C28" s="0">
-        <v>-0.15009735999999041</v>
+        <v>-0.54596580193260724</v>
       </c>
       <c r="D28" s="0">
-        <v>-0.12749095400001043</v>
+        <v>-0.46558287034186974</v>
       </c>
       <c r="E28" s="0">
-        <v>-0.15670434399999156</v>
+        <v>-0.58085691062658573</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.11322242800000115</v>
+        <v>-0.42548182579144811</v>
       </c>
       <c r="G28" s="0">
-        <v>-0.16076631800000118</v>
+        <v>-0.63604810598829686</v>
       </c>
       <c r="H28" s="0">
-        <v>-0.11758129000000483</v>
+        <v>-0.46785018996300892</v>
       </c>
       <c r="I28" s="0">
-        <v>-0.1400434659999954</v>
+        <v>-0.59837312565108447</v>
       </c>
       <c r="J28" s="0">
-        <v>-0.19457042399999214</v>
+        <v>-0.79144624561860644</v>
       </c>
       <c r="K28" s="0">
-        <v>-0.070615102000005869</v>
+        <v>-0.28221201058072654</v>
       </c>
       <c r="L28" s="0">
-        <v>-0.14368610600000498</v>
+        <v>-0.69772876715462873</v>
       </c>
       <c r="M28" s="0">
-        <v>-0.13250211999999895</v>
+        <v>-0.67762374839114037</v>
       </c>
       <c r="N28" s="0">
-        <v>-0.13711236199999721</v>
+        <v>-0.75289141904964574</v>
       </c>
       <c r="O28" s="0">
-        <v>-0.13465886400000304</v>
+        <v>-0.79348787857160386</v>
       </c>
       <c r="P28" s="0">
-        <v>-0.13129249199998672</v>
+        <v>-0.82508046846913619</v>
       </c>
       <c r="Q28" s="0">
-        <v>-0.12670468000000401</v>
+        <v>-0.85482722128556887</v>
       </c>
       <c r="R28" s="0">
-        <v>-0.12717144399999913</v>
+        <v>-0.92057153540234238</v>
       </c>
       <c r="S28" s="0">
-        <v>-0.11579371800000704</v>
+        <v>-0.9347602627136018</v>
       </c>
       <c r="T28" s="0">
-        <v>-0.087667388000000734</v>
+        <v>-0.86075007074290033</v>
       </c>
       <c r="U28" s="0">
-        <v>-0.11342772999999884</v>
+        <v>-1.3182652918224245</v>
       </c>
       <c r="V28" s="0">
-        <v>-0.12355055800000603</v>
+        <v>-1.5144137957518349</v>
       </c>
       <c r="W28" s="0">
-        <v>-0.092332553999995959</v>
+        <v>-1.2578889017278605</v>
       </c>
       <c r="X28" s="0">
-        <v>-0.092461655999998449</v>
+        <v>-1.4489155259666515</v>
       </c>
       <c r="Y28" s="0">
-        <v>-0.095349573999997439</v>
+        <v>-1.6917581172928418</v>
       </c>
       <c r="Z28" s="0">
-        <v>-0.094501195999996845</v>
+        <v>-1.8174355888721012</v>
       </c>
       <c r="AA28" s="0">
-        <v>-0.075985598000003485</v>
+        <v>-1.5913434956176551</v>
       </c>
       <c r="AB28" s="0">
-        <v>-0.079227492000002009</v>
+        <v>-1.7353105970548677</v>
       </c>
       <c r="AC28" s="0">
-        <v>-0.077531845999986082</v>
+        <v>-1.7541377983866893</v>
       </c>
       <c r="AD28" s="0">
-        <v>-0.073845851999991829</v>
+        <v>-1.7958504544148988</v>
       </c>
       <c r="AE28" s="0">
-        <v>-0.068837219999978494</v>
+        <v>-1.8612894719298925</v>
       </c>
       <c r="AF28" s="0">
-        <v>-0.063928933999990001</v>
+        <v>-1.9222390295402001</v>
       </c>
       <c r="AG28" s="0">
-        <v>-0.059161775999997168</v>
+        <v>-1.9770791918795265</v>
       </c>
       <c r="AH28" s="0">
-        <v>-0.054549517999988417</v>
+        <v>-2.0249893219130608</v>
       </c>
       <c r="AI28" s="0">
-        <v>-0.05010371799998925</v>
+        <v>-2.065262651699173</v>
       </c>
       <c r="AJ28" s="0">
-        <v>-0.04583246000000063</v>
+        <v>-2.0972711841939611</v>
       </c>
       <c r="AK28" s="0">
-        <v>-0.041742326000005825</v>
+        <v>-2.1205590529838378</v>
       </c>
       <c r="AL28" s="0">
-        <v>-0.037836442000014792</v>
+        <v>-2.1347621603263214</v>
       </c>
       <c r="AM28" s="0">
-        <v>-0.034116362000006895</v>
+        <v>-2.1396780595401172</v>
       </c>
       <c r="AN28" s="0">
-        <v>-0.030582367999998361</v>
+        <v>-2.135282116327609</v>
       </c>
       <c r="AO28" s="0">
-        <v>-0.027232395999988945</v>
+        <v>-2.1216542049654405</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>348</v>
+        <v>508</v>
       </c>
       <c r="B29" s="0">
-        <v>-117.4352495</v>
+        <v>-7.4310707020244564</v>
       </c>
       <c r="C29" s="0">
-        <v>-0.11421011399999248</v>
+        <v>-0.27835954804251245</v>
       </c>
       <c r="D29" s="0">
-        <v>-0.099528648000007713</v>
+        <v>-0.23973666868941237</v>
       </c>
       <c r="E29" s="0">
-        <v>-0.13116742199999454</v>
+        <v>-0.3299005271152527</v>
       </c>
       <c r="F29" s="0">
-        <v>-0.087589864000013229</v>
+        <v>-0.21080751286849217</v>
       </c>
       <c r="G29" s="0">
-        <v>-0.14075233199999548</v>
+        <v>-0.37101454942206535</v>
       </c>
       <c r="H29" s="0">
-        <v>-0.096799190000003144</v>
+        <v>-0.24663631752951895</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.12285247000000243</v>
+        <v>-0.33951598399481026</v>
       </c>
       <c r="J29" s="0">
-        <v>-0.17758128199999579</v>
+        <v>-0.4847420892640249</v>
       </c>
       <c r="K29" s="0">
-        <v>-0.056925277999998691</v>
+        <v>-0.13247913778042306</v>
       </c>
       <c r="L29" s="0">
-        <v>-0.13590273200000969</v>
+        <v>-0.41407314602097522</v>
       </c>
       <c r="M29" s="0">
-        <v>-0.1261920940000083</v>
+        <v>-0.39308591049649527</v>
       </c>
       <c r="N29" s="0">
-        <v>-0.13159540999999297</v>
+        <v>-0.43480526803929809</v>
       </c>
       <c r="O29" s="0">
-        <v>-0.13193469799999935</v>
+        <v>-0.45836650686657826</v>
       </c>
       <c r="P29" s="0">
-        <v>-0.13419304199999704</v>
+        <v>-0.49498954621568664</v>
       </c>
       <c r="Q29" s="0">
-        <v>-0.13757825800000933</v>
+        <v>-0.53598529255515426</v>
       </c>
       <c r="R29" s="0">
-        <v>-0.14347708000000114</v>
+        <v>-0.5927090980021138</v>
       </c>
       <c r="S29" s="0">
-        <v>-0.13462014800000066</v>
+        <v>-0.5932011547283913</v>
       </c>
       <c r="T29" s="0">
-        <v>-0.1102072680000008</v>
+        <v>-0.55669368830768684</v>
       </c>
       <c r="U29" s="0">
-        <v>-0.15209788399999002</v>
+        <v>-0.88924251058560011</v>
       </c>
       <c r="V29" s="0">
-        <v>-0.16870799399999203</v>
+        <v>-1.0444949327076032</v>
       </c>
       <c r="W29" s="0">
-        <v>-0.13995691599999294</v>
+        <v>-0.92426611085854427</v>
       </c>
       <c r="X29" s="0">
-        <v>-0.15005474199999913</v>
+        <v>-1.1163457479893055</v>
       </c>
       <c r="Y29" s="0">
-        <v>-0.16102871599999435</v>
+        <v>-1.3015630861372924</v>
       </c>
       <c r="Z29" s="0">
-        <v>-0.16731340199999511</v>
+        <v>-1.4534048147688809</v>
       </c>
       <c r="AA29" s="0">
-        <v>-0.15396345399999678</v>
+        <v>-1.4537544837768679</v>
       </c>
       <c r="AB29" s="0">
-        <v>-0.16214182000000665</v>
+        <v>-1.6531388931756936</v>
       </c>
       <c r="AC29" s="0">
-        <v>-0.16043335000000969</v>
+        <v>-1.6847892329349772</v>
       </c>
       <c r="AD29" s="0">
-        <v>-0.15851968800000282</v>
+        <v>-1.7144317775745033</v>
       </c>
       <c r="AE29" s="0">
-        <v>-0.15793492800000752</v>
+        <v>-1.8095422328525677</v>
       </c>
       <c r="AF29" s="0">
-        <v>-0.15873279800000706</v>
+        <v>-1.9694375874415644</v>
       </c>
       <c r="AG29" s="0">
-        <v>-0.15904210600000557</v>
+        <v>-2.1363556948249878</v>
       </c>
       <c r="AH29" s="0">
-        <v>-0.15884442999999226</v>
+        <v>-2.3082439599284372</v>
       </c>
       <c r="AI29" s="0">
-        <v>-0.15817343600000289</v>
+        <v>-2.4843304763956184</v>
       </c>
       <c r="AJ29" s="0">
-        <v>-0.1570643319999947</v>
+        <v>-2.6637537316481374</v>
       </c>
       <c r="AK29" s="0">
-        <v>-0.15555258199998878</v>
+        <v>-2.8455648280018959</v>
       </c>
       <c r="AL29" s="0">
-        <v>-0.15367411799998809</v>
+        <v>-3.0287469320627114</v>
       </c>
       <c r="AM29" s="0">
-        <v>-0.15146444599999587</v>
+        <v>-3.2122307774623353</v>
       </c>
       <c r="AN29" s="0">
-        <v>-0.148958468000008</v>
+        <v>-3.3949028104665882</v>
       </c>
       <c r="AO29" s="0">
-        <v>-0.14618978799999116</v>
+        <v>-3.5756188881789637</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>349</v>
+        <v>509</v>
       </c>
       <c r="B30" s="0">
-        <v>-117.50855589999999</v>
+        <v>-7.5985644522885867</v>
       </c>
       <c r="C30" s="0">
-        <v>-0.081404789999991678</v>
+        <v>-0.14404377627418527</v>
       </c>
       <c r="D30" s="0">
-        <v>-0.065266645999995987</v>
+        <v>-0.10824262387552123</v>
       </c>
       <c r="E30" s="0">
-        <v>-0.086046351999994997</v>
+        <v>-0.15573535263083974</v>
       </c>
       <c r="F30" s="0">
-        <v>-0.058173295999990771</v>
+        <v>-0.09208079365711884</v>
       </c>
       <c r="G30" s="0">
-        <v>-0.098133571999992952</v>
+        <v>-0.18687728631367348</v>
       </c>
       <c r="H30" s="0">
-        <v>-0.060830571999998639</v>
+        <v>-0.10058908388307428</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.088573081999994585</v>
+        <v>-0.17093630033866183</v>
       </c>
       <c r="J30" s="0">
-        <v>-0.12382080799998896</v>
+        <v>-0.24729725557721324</v>
       </c>
       <c r="K30" s="0">
-        <v>-0.027430360000009202</v>
+        <v>-0.023809266119033182</v>
       </c>
       <c r="L30" s="0">
-        <v>-0.10096319599999326</v>
+        <v>-0.21159772250833259</v>
       </c>
       <c r="M30" s="0">
-        <v>-0.093836401999991992</v>
+        <v>-0.19656941893736107</v>
       </c>
       <c r="N30" s="0">
-        <v>-0.096480615999992025</v>
+        <v>-0.21082624835474217</v>
       </c>
       <c r="O30" s="0">
-        <v>-0.1002093619999993</v>
+        <v>-0.22908312011734286</v>
       </c>
       <c r="P30" s="0">
-        <v>-0.10769944999999659</v>
+        <v>-0.25794477289949996</v>
       </c>
       <c r="Q30" s="0">
-        <v>-0.11369579999998614</v>
+        <v>-0.28592573084221634</v>
       </c>
       <c r="R30" s="0">
-        <v>-0.12197154999999604</v>
+        <v>-0.31919023422051213</v>
       </c>
       <c r="S30" s="0">
-        <v>-0.12066593599999287</v>
+        <v>-0.32874493547013428</v>
       </c>
       <c r="T30" s="0">
-        <v>-0.10888339800000146</v>
+        <v>-0.31979617977859026</v>
       </c>
       <c r="U30" s="0">
-        <v>-0.1462866339999902</v>
+        <v>-0.49214429970062767</v>
       </c>
       <c r="V30" s="0">
-        <v>-0.16705223200000141</v>
+        <v>-0.57727276729719035</v>
       </c>
       <c r="W30" s="0">
-        <v>-0.14992840199999868</v>
+        <v>-0.53524107366649332</v>
       </c>
       <c r="X30" s="0">
-        <v>-0.1685514619999946</v>
+        <v>-0.6522384850653199</v>
       </c>
       <c r="Y30" s="0">
-        <v>-0.18652148399998048</v>
+        <v>-0.76195845141974283</v>
       </c>
       <c r="Z30" s="0">
-        <v>-0.19141376400000176</v>
+        <v>-0.81149757573169967</v>
       </c>
       <c r="AA30" s="0">
-        <v>-0.18456320799999837</v>
+        <v>-0.82207602077398056</v>
       </c>
       <c r="AB30" s="0">
-        <v>-0.19956099199998611</v>
+        <v>-0.94895267529725791</v>
       </c>
       <c r="AC30" s="0">
-        <v>-0.20252198599997762</v>
+        <v>-0.99833954425187665</v>
       </c>
       <c r="AD30" s="0">
-        <v>-0.20313677399998475</v>
+        <v>-1.0246192094435647</v>
       </c>
       <c r="AE30" s="0">
-        <v>-0.20373348199998809</v>
+        <v>-1.0517530379192408</v>
       </c>
       <c r="AF30" s="0">
-        <v>-0.20665218599999768</v>
+        <v>-1.1071793237219971</v>
       </c>
       <c r="AG30" s="0">
-        <v>-0.21078739399999158</v>
+        <v>-1.1840156106430155</v>
       </c>
       <c r="AH30" s="0">
-        <v>-0.2145688200000091</v>
+        <v>-1.2638917122036306</v>
       </c>
       <c r="AI30" s="0">
-        <v>-0.21798023799999378</v>
+        <v>-1.3464805307495162</v>
       </c>
       <c r="AJ30" s="0">
-        <v>-0.22102689999998226</v>
+        <v>-1.4317599520697095</v>
       </c>
       <c r="AK30" s="0">
-        <v>-0.22371523200000176</v>
+        <v>-1.5196965491067795</v>
       </c>
       <c r="AL30" s="0">
-        <v>-0.22605272200000393</v>
+        <v>-1.6102488938545825</v>
       </c>
       <c r="AM30" s="0">
-        <v>-0.22804773600000594</v>
+        <v>-1.7033634022469777</v>
       </c>
       <c r="AN30" s="0">
-        <v>-0.22970990599998053</v>
+        <v>-1.7989809601207873</v>
       </c>
       <c r="AO30" s="0">
-        <v>-0.23104904799998671</v>
+        <v>-1.8970273005019784</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>350</v>
+        <v>510</v>
       </c>
       <c r="B31" s="0">
-        <v>-117.55515469999999</v>
+        <v>-7.6932518058702772</v>
       </c>
       <c r="C31" s="0">
-        <v>-0.050087417999999495</v>
+        <v>-0.060948397442608819</v>
       </c>
       <c r="D31" s="0">
-        <v>-0.034959785999997273</v>
+        <v>-0.02984098174645405</v>
       </c>
       <c r="E31" s="0">
-        <v>-0.051129593999998058</v>
+        <v>-0.062785065239385443</v>
       </c>
       <c r="F31" s="0">
-        <v>-0.032831197999992234</v>
+        <v>-0.0257740890235745</v>
       </c>
       <c r="G31" s="0">
-        <v>-0.053260681999996784</v>
+        <v>-0.067570701427930299</v>
       </c>
       <c r="H31" s="0">
-        <v>-0.031962301999992171</v>
+        <v>-0.024264475013722097</v>
       </c>
       <c r="I31" s="0">
-        <v>-0.050158077999976847</v>
+        <v>-0.062986728433279293</v>
       </c>
       <c r="J31" s="0">
-        <v>-0.067221361999993512</v>
+        <v>-0.095898469380928539</v>
       </c>
       <c r="K31" s="0">
-        <v>-0.010270651999984004</v>
+        <v>0.01959737589814084</v>
       </c>
       <c r="L31" s="0">
-        <v>-0.063738407999987423</v>
+        <v>-0.094123496410659285</v>
       </c>
       <c r="M31" s="0">
-        <v>-0.055104432000002923</v>
+        <v>-0.075905539733758617</v>
       </c>
       <c r="N31" s="0">
-        <v>-0.058753453999993432</v>
+        <v>-0.085351745551674338</v>
       </c>
       <c r="O31" s="0">
-        <v>-0.062877854000002564</v>
+        <v>-0.09699640552402819</v>
       </c>
       <c r="P31" s="0">
-        <v>-0.070449897999988131</v>
+        <v>-0.11622627821535404</v>
       </c>
       <c r="Q31" s="0">
-        <v>-0.073893523999994493</v>
+        <v>-0.126389635619056</v>
       </c>
       <c r="R31" s="0">
-        <v>-0.083101066000007329</v>
+        <v>-0.15010252784879469</v>
       </c>
       <c r="S31" s="0">
-        <v>-0.083229049999995475</v>
+        <v>-0.15320571283181086</v>
       </c>
       <c r="T31" s="0">
-        <v>-0.076877879999993404</v>
+        <v>-0.14579977108836648</v>
       </c>
       <c r="U31" s="0">
-        <v>-0.10476572399998485</v>
+        <v>-0.22629358048356146</v>
       </c>
       <c r="V31" s="0">
-        <v>-0.10366789799999321</v>
+        <v>-0.23459884703085296</v>
       </c>
       <c r="W31" s="0">
-        <v>-0.10934264799999038</v>
+        <v>-0.24471759420083361</v>
       </c>
       <c r="X31" s="0">
-        <v>-0.12551636999998106</v>
+        <v>-0.29787379420905807</v>
       </c>
       <c r="Y31" s="0">
-        <v>-0.14136020599999721</v>
+        <v>-0.3467417799594924</v>
       </c>
       <c r="Z31" s="0">
-        <v>-0.13794744199999354</v>
+        <v>-0.34440316863152232</v>
       </c>
       <c r="AA31" s="0">
-        <v>-0.13242249799999239</v>
+        <v>-0.33903495413641088</v>
       </c>
       <c r="AB31" s="0">
-        <v>-0.14312261799998804</v>
+        <v>-0.38414788861924343</v>
       </c>
       <c r="AC31" s="0">
-        <v>-0.14493561800000077</v>
+        <v>-0.4001756399226864</v>
       </c>
       <c r="AD31" s="0">
-        <v>-0.14619145199999206</v>
+        <v>-0.41324671232425664</v>
       </c>
       <c r="AE31" s="0">
-        <v>-0.14706510000000161</v>
+        <v>-0.4227752970777639</v>
       </c>
       <c r="AF31" s="0">
-        <v>-0.14791270599999518</v>
+        <v>-0.43249174287753489</v>
       </c>
       <c r="AG31" s="0">
-        <v>-0.14913557999998783</v>
+        <v>-0.44659299591637674</v>
       </c>
       <c r="AH31" s="0">
-        <v>-0.1503808179999977</v>
+        <v>-0.46379119027192361</v>
       </c>
       <c r="AI31" s="0">
-        <v>-0.15147115199998051</v>
+        <v>-0.48130779846013666</v>
       </c>
       <c r="AJ31" s="0">
-        <v>-0.15240810399998406</v>
+        <v>-0.49908999382880997</v>
       </c>
       <c r="AK31" s="0">
-        <v>-0.15319492999999351</v>
+        <v>-0.51713960612782828</v>
       </c>
       <c r="AL31" s="0">
-        <v>-0.15383468399999867</v>
+        <v>-0.53545646848593798</v>
       </c>
       <c r="AM31" s="0">
-        <v>-0.15433120399998312</v>
+        <v>-0.55404235393650525</v>
       </c>
       <c r="AN31" s="0">
-        <v>-0.15468782399998826</v>
+        <v>-0.57289632637829779</v>
       </c>
       <c r="AO31" s="0">
-        <v>-0.15490846999999075</v>
+        <v>-0.59201835733491526</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>351</v>
+        <v>511</v>
       </c>
       <c r="B32" s="0">
-        <v>-117.57656259999999</v>
+        <v>-7.7340743461890771</v>
       </c>
       <c r="C32" s="0">
-        <v>-0.023590593999994525</v>
+        <v>-0.0044302408342347145</v>
       </c>
       <c r="D32" s="0">
-        <v>-0.016524344000000468</v>
+        <v>0.0091091749291551637</v>
       </c>
       <c r="E32" s="0">
-        <v>-0.023443601999996844</v>
+        <v>-0.0040448682196962318</v>
       </c>
       <c r="F32" s="0">
-        <v>-0.013735621999980907</v>
+        <v>0.014417934937947742</v>
       </c>
       <c r="G32" s="0">
-        <v>-0.025875861999988814</v>
+        <v>-0.008790457942876008</v>
       </c>
       <c r="H32" s="0">
-        <v>-0.014056003999993294</v>
+        <v>0.013757551249181243</v>
       </c>
       <c r="I32" s="0">
-        <v>-0.023514181999995998</v>
+        <v>-0.0045920576904196434</v>
       </c>
       <c r="J32" s="0">
-        <v>-0.032213679999994582</v>
+        <v>-0.020798453673516081</v>
       </c>
       <c r="K32" s="0">
-        <v>-0.0025266299999877617</v>
+        <v>0.035645805935022895</v>
       </c>
       <c r="L32" s="0">
-        <v>-0.031823179999999951</v>
+        <v>-0.021177049773697262</v>
       </c>
       <c r="M32" s="0">
-        <v>-0.025665639999996159</v>
+        <v>-0.0091216172317241037</v>
       </c>
       <c r="N32" s="0">
-        <v>-0.027717038000002248</v>
+        <v>-0.01341549316525564</v>
       </c>
       <c r="O32" s="0">
-        <v>-0.028848627999987997</v>
+        <v>-0.016098238009942523</v>
       </c>
       <c r="P32" s="0">
-        <v>-0.035038435999990014</v>
+        <v>-0.028878533173974513</v>
       </c>
       <c r="Q32" s="0">
-        <v>-0.037452819999995057</v>
+        <v>-0.034139357936781078</v>
       </c>
       <c r="R32" s="0">
-        <v>-0.042362421999992961</v>
+        <v>-0.044415724270944271</v>
       </c>
       <c r="S32" s="0">
-        <v>-0.043191731999979055</v>
+        <v>-0.046476126510930908</v>
       </c>
       <c r="T32" s="0">
-        <v>-0.027809057999984788</v>
+        <v>-0.017189352232677577</v>
       </c>
       <c r="U32" s="0">
-        <v>-0.035400921999990231</v>
+        <v>-0.035593876289051765</v>
       </c>
       <c r="V32" s="0">
-        <v>-0.041145557999993088</v>
+        <v>-0.048965707625425882</v>
       </c>
       <c r="W32" s="0">
-        <v>-0.017966031999986143</v>
+        <v>-0.0015290367455734538</v>
       </c>
       <c r="X32" s="0">
-        <v>-0.047287981999996731</v>
+        <v>-0.063401838318097231</v>
       </c>
       <c r="Y32" s="0">
-        <v>-0.031358707999995517</v>
+        <v>-0.030655035121311847</v>
       </c>
       <c r="Z32" s="0">
-        <v>-0.039736511999986845</v>
+        <v>-0.048512635030151026</v>
       </c>
       <c r="AA32" s="0">
-        <v>-0.052465217999991154</v>
+        <v>-0.077693573810736716</v>
       </c>
       <c r="AB32" s="0">
-        <v>-0.059312133999991801</v>
+        <v>-0.096113085527858425</v>
       </c>
       <c r="AC32" s="0">
-        <v>-0.060707673999996103</v>
+        <v>-0.10179320639650172</v>
       </c>
       <c r="AD32" s="0">
-        <v>-0.062017679999993192</v>
+        <v>-0.10750822320241211</v>
       </c>
       <c r="AE32" s="0">
-        <v>-0.063173966000004356</v>
+        <v>-0.11259948000366644</v>
       </c>
       <c r="AF32" s="0">
-        <v>-0.063991145999988674</v>
+        <v>-0.11630316970376788</v>
       </c>
       <c r="AG32" s="0">
-        <v>-0.064743569999986761</v>
+        <v>-0.11994694415847458</v>
       </c>
       <c r="AH32" s="0">
-        <v>-0.065567330000003921</v>
+        <v>-0.12462249196714062</v>
       </c>
       <c r="AI32" s="0">
-        <v>-0.066550517999981906</v>
+        <v>-0.13054441473096212</v>
       </c>
       <c r="AJ32" s="0">
-        <v>-0.067451702000010272</v>
+        <v>-0.13654033850868758</v>
       </c>
       <c r="AK32" s="0">
-        <v>-0.068264113999997988</v>
+        <v>-0.14257909535986987</v>
       </c>
       <c r="AL32" s="0">
-        <v>-0.068988771999993759</v>
+        <v>-0.14866157732129862</v>
       </c>
       <c r="AM32" s="0">
-        <v>-0.069626787999990114</v>
+        <v>-0.1547884377256413</v>
       </c>
       <c r="AN32" s="0">
-        <v>-0.070179473999996134</v>
+        <v>-0.16096023296763504</v>
       </c>
       <c r="AO32" s="0">
-        <v>-0.070648827999999497</v>
+        <v>-0.1671790621901279</v>
       </c>
     </row>
   </sheetData>

--- a/output/med_shocks.xlsx
+++ b/output/med_shocks.xlsx
@@ -13,7 +13,103 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="544">
+  <si>
+    <t>med_Q_2</t>
+  </si>
+  <si>
+    <t>med_Q_3</t>
+  </si>
+  <si>
+    <t>med_Q_4</t>
+  </si>
+  <si>
+    <t>med_Q_5</t>
+  </si>
+  <si>
+    <t>med_Q_6</t>
+  </si>
+  <si>
+    <t>med_Q_7</t>
+  </si>
+  <si>
+    <t>med_Q_8</t>
+  </si>
+  <si>
+    <t>med_Q_9</t>
+  </si>
+  <si>
+    <t>med_Q_10</t>
+  </si>
+  <si>
+    <t>med_Q_11</t>
+  </si>
+  <si>
+    <t>med_Q_12</t>
+  </si>
+  <si>
+    <t>med_Q_13</t>
+  </si>
+  <si>
+    <t>med_Q_14</t>
+  </si>
+  <si>
+    <t>med_Q_15</t>
+  </si>
+  <si>
+    <t>med_Q_16</t>
+  </si>
+  <si>
+    <t>med_Q_17</t>
+  </si>
+  <si>
+    <t>med_NQ_2</t>
+  </si>
+  <si>
+    <t>med_NQ_3</t>
+  </si>
+  <si>
+    <t>med_NQ_4</t>
+  </si>
+  <si>
+    <t>med_NQ_5</t>
+  </si>
+  <si>
+    <t>med_NQ_6</t>
+  </si>
+  <si>
+    <t>med_NQ_7</t>
+  </si>
+  <si>
+    <t>med_NQ_8</t>
+  </si>
+  <si>
+    <t>med_NQ_9</t>
+  </si>
+  <si>
+    <t>med_NQ_10</t>
+  </si>
+  <si>
+    <t>med_NQ_11</t>
+  </si>
+  <si>
+    <t>med_NQ_12</t>
+  </si>
+  <si>
+    <t>med_NQ_13</t>
+  </si>
+  <si>
+    <t>med_NQ_14</t>
+  </si>
+  <si>
+    <t>med_NQ_15</t>
+  </si>
+  <si>
+    <t>med_NQ_16</t>
+  </si>
+  <si>
+    <t>med_NQ_17</t>
+  </si>
   <si>
     <t>med_Q_2</t>
   </si>
@@ -1569,7 +1665,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -1593,11 +1689,12 @@
     <border/>
     <border/>
     <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
@@ -1615,6 +1712,7 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1628,4046 +1726,4046 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="true"/>
-    <col min="2" max="2" width="13.42578125" customWidth="true"/>
-    <col min="3" max="3" width="14.42578125" customWidth="true"/>
-    <col min="4" max="4" width="14.42578125" customWidth="true"/>
-    <col min="5" max="5" width="14.42578125" customWidth="true"/>
-    <col min="6" max="6" width="14.42578125" customWidth="true"/>
-    <col min="7" max="7" width="14.42578125" customWidth="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true"/>
-    <col min="9" max="9" width="14.42578125" customWidth="true"/>
-    <col min="10" max="10" width="14.42578125" customWidth="true"/>
-    <col min="11" max="11" width="14.42578125" customWidth="true"/>
-    <col min="12" max="12" width="14.42578125" customWidth="true"/>
-    <col min="13" max="13" width="14.42578125" customWidth="true"/>
-    <col min="14" max="14" width="14.42578125" customWidth="true"/>
-    <col min="15" max="15" width="14.42578125" customWidth="true"/>
-    <col min="16" max="16" width="16.42578125" customWidth="true"/>
-    <col min="17" max="17" width="13.42578125" customWidth="true"/>
-    <col min="18" max="18" width="14.42578125" customWidth="true"/>
-    <col min="19" max="19" width="14.42578125" customWidth="true"/>
-    <col min="20" max="20" width="14.42578125" customWidth="true"/>
-    <col min="21" max="21" width="14.42578125" customWidth="true"/>
-    <col min="22" max="22" width="15.42578125" customWidth="true"/>
-    <col min="23" max="23" width="15.42578125" customWidth="true"/>
-    <col min="24" max="24" width="14.42578125" customWidth="true"/>
-    <col min="25" max="25" width="15.42578125" customWidth="true"/>
-    <col min="26" max="26" width="15.42578125" customWidth="true"/>
-    <col min="27" max="27" width="14.42578125" customWidth="true"/>
-    <col min="28" max="28" width="14.42578125" customWidth="true"/>
-    <col min="29" max="29" width="13.7109375" customWidth="true"/>
-    <col min="30" max="30" width="15.42578125" customWidth="true"/>
-    <col min="31" max="31" width="13.7109375" customWidth="true"/>
-    <col min="32" max="32" width="14.42578125" customWidth="true"/>
-    <col min="33" max="33" width="14.42578125" customWidth="true"/>
-    <col min="34" max="34" width="14.42578125" customWidth="true"/>
-    <col min="35" max="35" width="14.7109375" customWidth="true"/>
-    <col min="36" max="36" width="14.7109375" customWidth="true"/>
-    <col min="37" max="37" width="15.7109375" customWidth="true"/>
-    <col min="38" max="38" width="14.42578125" customWidth="true"/>
-    <col min="39" max="39" width="14.42578125" customWidth="true"/>
-    <col min="40" max="40" width="14.7109375" customWidth="true"/>
-    <col min="41" max="41" width="14.42578125" customWidth="true"/>
+    <col min="2" max="2" width="12.42578125" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" customWidth="true"/>
+    <col min="6" max="6" width="12.7109375" customWidth="true"/>
+    <col min="7" max="7" width="12.7109375" customWidth="true"/>
+    <col min="8" max="8" width="12.7109375" customWidth="true"/>
+    <col min="9" max="9" width="12.7109375" customWidth="true"/>
+    <col min="10" max="10" width="12.7109375" customWidth="true"/>
+    <col min="11" max="11" width="12.7109375" customWidth="true"/>
+    <col min="12" max="12" width="12.7109375" customWidth="true"/>
+    <col min="13" max="13" width="12.7109375" customWidth="true"/>
+    <col min="14" max="14" width="12.7109375" customWidth="true"/>
+    <col min="15" max="15" width="12.7109375" customWidth="true"/>
+    <col min="16" max="16" width="12.7109375" customWidth="true"/>
+    <col min="17" max="17" width="12.7109375" customWidth="true"/>
+    <col min="18" max="18" width="12.7109375" customWidth="true"/>
+    <col min="19" max="19" width="12.7109375" customWidth="true"/>
+    <col min="20" max="20" width="12.7109375" customWidth="true"/>
+    <col min="21" max="21" width="12.7109375" customWidth="true"/>
+    <col min="22" max="22" width="12.7109375" customWidth="true"/>
+    <col min="23" max="23" width="12.7109375" customWidth="true"/>
+    <col min="24" max="24" width="12.7109375" customWidth="true"/>
+    <col min="25" max="25" width="12.7109375" customWidth="true"/>
+    <col min="26" max="26" width="12.7109375" customWidth="true"/>
+    <col min="27" max="27" width="12.7109375" customWidth="true"/>
+    <col min="28" max="28" width="12.7109375" customWidth="true"/>
+    <col min="29" max="29" width="12.7109375" customWidth="true"/>
+    <col min="30" max="30" width="12.7109375" customWidth="true"/>
+    <col min="31" max="31" width="12.7109375" customWidth="true"/>
+    <col min="32" max="32" width="12.7109375" customWidth="true"/>
+    <col min="33" max="33" width="12.7109375" customWidth="true"/>
+    <col min="34" max="34" width="12.7109375" customWidth="true"/>
+    <col min="35" max="35" width="12.7109375" customWidth="true"/>
+    <col min="36" max="36" width="12.7109375" customWidth="true"/>
+    <col min="37" max="37" width="12.7109375" customWidth="true"/>
+    <col min="38" max="38" width="12.7109375" customWidth="true"/>
+    <col min="39" max="39" width="12.7109375" customWidth="true"/>
+    <col min="40" max="40" width="12.7109375" customWidth="true"/>
+    <col min="41" max="41" width="12.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>480</v>
+        <v>512</v>
       </c>
       <c r="B1" s="0">
-        <v>13.763688546684229</v>
+        <v>-76.377728212738035</v>
       </c>
       <c r="C1" s="0">
-        <v>13.841670305400051</v>
+        <v>-76.377189135932923</v>
       </c>
       <c r="D1" s="0">
-        <v>12.660744399169122</v>
+        <v>-76.386012787437437</v>
       </c>
       <c r="E1" s="0">
-        <v>9.7627508539483259</v>
+        <v>-76.415887570190421</v>
       </c>
       <c r="F1" s="0">
-        <v>14.243527392431025</v>
+        <v>-76.374498715782153</v>
       </c>
       <c r="G1" s="0">
-        <v>14.426135269246705</v>
+        <v>-76.37332254219055</v>
       </c>
       <c r="H1" s="0">
-        <v>14.677475766554258</v>
+        <v>-76.3717485305786</v>
       </c>
       <c r="I1" s="0">
-        <v>14.851863865250989</v>
+        <v>-76.370685798072799</v>
       </c>
       <c r="J1" s="0">
-        <v>12.804849116217531</v>
+        <v>-76.384855079460138</v>
       </c>
       <c r="K1" s="0">
-        <v>15.114183338103517</v>
+        <v>-76.369130583000185</v>
       </c>
       <c r="L1" s="0">
-        <v>15.970490714943528</v>
+        <v>-76.364388825035093</v>
       </c>
       <c r="M1" s="0">
-        <v>16.123368629965043</v>
+        <v>-76.363592222404478</v>
       </c>
       <c r="N1" s="0">
-        <v>16.206046887829441</v>
+        <v>-76.363167314720158</v>
       </c>
       <c r="O1" s="0">
-        <v>16.247309408568917</v>
+        <v>-76.362956780242911</v>
       </c>
       <c r="P1" s="0">
-        <v>16.271919618840013</v>
+        <v>-76.362831690597531</v>
       </c>
       <c r="Q1" s="0">
-        <v>16.327399581392051</v>
+        <v>-76.362551000022876</v>
       </c>
       <c r="R1" s="0">
-        <v>16.32187619079075</v>
+        <v>-76.362578863906862</v>
       </c>
       <c r="S1" s="0">
-        <v>16.329368387467124</v>
+        <v>-76.362541072273245</v>
       </c>
       <c r="T1" s="0">
-        <v>16.293906757967036</v>
+        <v>-76.36272023506163</v>
       </c>
       <c r="U1" s="0">
-        <v>16.393136484121637</v>
+        <v>-76.362220736885064</v>
       </c>
       <c r="V1" s="0">
-        <v>16.537190677403942</v>
+        <v>-76.36150567417144</v>
       </c>
       <c r="W1" s="0">
-        <v>16.582141371766326</v>
+        <v>-76.361284947204581</v>
       </c>
       <c r="X1" s="0">
-        <v>16.603368983842415</v>
+        <v>-76.361181102943419</v>
       </c>
       <c r="Y1" s="0">
-        <v>16.621023248420922</v>
+        <v>-76.361094930076604</v>
       </c>
       <c r="Z1" s="0">
-        <v>16.629836508323883</v>
+        <v>-76.361051976013187</v>
       </c>
       <c r="AA1" s="0">
-        <v>16.645338813776547</v>
+        <v>-76.360976525115959</v>
       </c>
       <c r="AB1" s="0">
-        <v>16.66014583946971</v>
+        <v>-76.360904582023608</v>
       </c>
       <c r="AC1" s="0">
-        <v>16.673639549032011</v>
+        <v>-76.360839125061034</v>
       </c>
       <c r="AD1" s="0">
-        <v>16.685936914494885</v>
+        <v>-76.360779558563223</v>
       </c>
       <c r="AE1" s="0">
-        <v>16.697156106099861</v>
+        <v>-76.360725286865232</v>
       </c>
       <c r="AF1" s="0">
-        <v>16.707388926810324</v>
+        <v>-76.360675846672052</v>
       </c>
       <c r="AG1" s="0">
-        <v>16.716714250533187</v>
+        <v>-76.360630840873711</v>
       </c>
       <c r="AH1" s="0">
-        <v>16.725225325706155</v>
+        <v>-76.360589806175227</v>
       </c>
       <c r="AI1" s="0">
-        <v>16.732988518781337</v>
+        <v>-76.360552411651611</v>
       </c>
       <c r="AJ1" s="0">
-        <v>16.740070636792751</v>
+        <v>-76.360518326377871</v>
       </c>
       <c r="AK1" s="0">
-        <v>16.74653887334723</v>
+        <v>-76.360487219429018</v>
       </c>
       <c r="AL1" s="0">
-        <v>16.752460759457247</v>
+        <v>-76.360458759880061</v>
       </c>
       <c r="AM1" s="0">
-        <v>16.75784897993616</v>
+        <v>-76.360432881546018</v>
       </c>
       <c r="AN1" s="0">
-        <v>16.762771520113017</v>
+        <v>-76.360409253501885</v>
       </c>
       <c r="AO1" s="0">
-        <v>16.767269000027493</v>
+        <v>-76.360387677192676</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>481</v>
+        <v>513</v>
       </c>
       <c r="B2" s="0">
-        <v>4.6728152077517064</v>
+        <v>-76.379645856857294</v>
       </c>
       <c r="C2" s="0">
-        <v>0.071112428963982385</v>
+        <v>0.82286646025848875</v>
       </c>
       <c r="D2" s="0">
-        <v>-0.66570656558753949</v>
+        <v>0.81738077630234252</v>
       </c>
       <c r="E2" s="0">
-        <v>-2.0290593162406791</v>
+        <v>0.80179775954055721</v>
       </c>
       <c r="F2" s="0">
-        <v>4.5456791432856338</v>
+        <v>0.86408395376586555</v>
       </c>
       <c r="G2" s="0">
-        <v>0.29105903064158495</v>
+        <v>0.82442252911758485</v>
       </c>
       <c r="H2" s="0">
-        <v>0.31832034131072012</v>
+        <v>0.82459841045379312</v>
       </c>
       <c r="I2" s="0">
-        <v>0.19360958724971558</v>
+        <v>0.82382276464080784</v>
       </c>
       <c r="J2" s="0">
-        <v>-1.1267409139238747</v>
+        <v>0.81501447732162791</v>
       </c>
       <c r="K2" s="0">
-        <v>2.7046756030447567</v>
+        <v>0.84072002087021003</v>
       </c>
       <c r="L2" s="0">
-        <v>0.93837843227430406</v>
+        <v>0.82808018741225853</v>
       </c>
       <c r="M2" s="0">
-        <v>0.28382720186636112</v>
+        <v>0.82442114188003446</v>
       </c>
       <c r="N2" s="0">
-        <v>0.22287933282620914</v>
+        <v>0.82410833304977682</v>
       </c>
       <c r="O2" s="0">
-        <v>0.18151749067296744</v>
+        <v>0.82389914874649817</v>
       </c>
       <c r="P2" s="0">
-        <v>0.20059699979948042</v>
+        <v>0.82400197508239903</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.24746827561451679</v>
+        <v>0.8242453240814217</v>
       </c>
       <c r="R2" s="0">
-        <v>0.21340228659883984</v>
+        <v>0.82407435631942938</v>
       </c>
       <c r="S2" s="0">
-        <v>0.22615880274326181</v>
+        <v>0.82413925600432703</v>
       </c>
       <c r="T2" s="0">
-        <v>0.19208391980472106</v>
+        <v>0.82396521725844529</v>
       </c>
       <c r="U2" s="0">
-        <v>0.32079216377166492</v>
+        <v>0.82462043946837504</v>
       </c>
       <c r="V2" s="0">
-        <v>0.40355331583391252</v>
+        <v>0.82503541543197301</v>
       </c>
       <c r="W2" s="0">
-        <v>0.32140649463286186</v>
+        <v>0.82462719166183185</v>
       </c>
       <c r="X2" s="0">
-        <v>0.31926171622851351</v>
+        <v>0.8246173764266933</v>
       </c>
       <c r="Y2" s="0">
-        <v>0.30899374240018018</v>
+        <v>0.8245673657188386</v>
       </c>
       <c r="Z2" s="0">
-        <v>0.30188942273143249</v>
+        <v>0.82453295216751277</v>
       </c>
       <c r="AA2" s="0">
-        <v>0.31508869493819708</v>
+        <v>0.82459781214142391</v>
       </c>
       <c r="AB2" s="0">
-        <v>0.31897999617784029</v>
+        <v>0.82461712492370765</v>
       </c>
       <c r="AC2" s="0">
-        <v>0.32189579760358061</v>
+        <v>0.82463160223006793</v>
       </c>
       <c r="AD2" s="0">
-        <v>0.32456790082080211</v>
+        <v>0.82464482466888622</v>
       </c>
       <c r="AE2" s="0">
-        <v>0.32703687586918812</v>
+        <v>0.82465700270842979</v>
       </c>
       <c r="AF2" s="0">
-        <v>0.32928926753684351</v>
+        <v>0.82466808207702547</v>
       </c>
       <c r="AG2" s="0">
-        <v>0.33136603364779038</v>
+        <v>0.82467827059555199</v>
       </c>
       <c r="AH2" s="0">
-        <v>0.33326726910714166</v>
+        <v>0.82468757620620059</v>
       </c>
       <c r="AI2" s="0">
-        <v>0.33502090544470747</v>
+        <v>0.82469614054489504</v>
       </c>
       <c r="AJ2" s="0">
-        <v>0.33662723316398335</v>
+        <v>0.824703970230103</v>
       </c>
       <c r="AK2" s="0">
-        <v>0.33811413410954511</v>
+        <v>0.82471120425033129</v>
       </c>
       <c r="AL2" s="0">
-        <v>0.33948221499234915</v>
+        <v>0.82471784922409486</v>
       </c>
       <c r="AM2" s="0">
-        <v>0.34071842191046497</v>
+        <v>0.82472384558487022</v>
       </c>
       <c r="AN2" s="0">
-        <v>0.34186378307192261</v>
+        <v>0.82472939321136907</v>
       </c>
       <c r="AO2" s="0">
-        <v>0.34293297406447393</v>
+        <v>0.82473456490707564</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>482</v>
+        <v>514</v>
       </c>
       <c r="B3" s="0">
-        <v>4.2457758651727842</v>
+        <v>-76.382819295120242</v>
       </c>
       <c r="C3" s="0">
-        <v>-0.072142068225175521</v>
+        <v>0.82173241474151992</v>
       </c>
       <c r="D3" s="0">
-        <v>-0.32642781267680782</v>
+        <v>0.81979804832076886</v>
       </c>
       <c r="E3" s="0">
-        <v>-1.0377463128940123</v>
+        <v>0.81288958944320189</v>
       </c>
       <c r="F3" s="0">
-        <v>3.5670887177465382</v>
+        <v>0.85414640742874237</v>
       </c>
       <c r="G3" s="0">
-        <v>-0.027757761363267942</v>
+        <v>0.82225250174713826</v>
       </c>
       <c r="H3" s="0">
-        <v>0.033814188109069956</v>
+        <v>0.82271075740432897</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.096748243119955585</v>
+        <v>0.82189062335968588</v>
       </c>
       <c r="J3" s="0">
-        <v>-0.91308162986310015</v>
+        <v>0.81623774551010009</v>
       </c>
       <c r="K3" s="0">
-        <v>1.7992726831117625</v>
+        <v>0.83437547935104373</v>
       </c>
       <c r="L3" s="0">
-        <v>0.43313166400542391</v>
+        <v>0.82525258561707315</v>
       </c>
       <c r="M3" s="0">
-        <v>0.13857660857771562</v>
+        <v>0.8236157710609473</v>
       </c>
       <c r="N3" s="0">
-        <v>0.060723660408635152</v>
+        <v>0.82321505531692185</v>
       </c>
       <c r="O3" s="0">
-        <v>-0.016867941373918911</v>
+        <v>0.82280850602721878</v>
       </c>
       <c r="P3" s="0">
-        <v>0.0041348444385134325</v>
+        <v>0.82293138641738717</v>
       </c>
       <c r="Q3" s="0">
-        <v>0.057589869801941355</v>
+        <v>0.82323076895905112</v>
       </c>
       <c r="R3" s="0">
-        <v>0.063909368098273064</v>
+        <v>0.82327654117965621</v>
       </c>
       <c r="S3" s="0">
-        <v>0.092860592213634782</v>
+        <v>0.82343290058899121</v>
       </c>
       <c r="T3" s="0">
-        <v>0.090245460387550061</v>
+        <v>0.82342021689606215</v>
       </c>
       <c r="U3" s="0">
-        <v>0.19254500504856598</v>
+        <v>0.82395384005737549</v>
       </c>
       <c r="V3" s="0">
-        <v>0.31526195817079627</v>
+        <v>0.82459192564773587</v>
       </c>
       <c r="W3" s="0">
-        <v>0.22772827421082284</v>
+        <v>0.82415598624802622</v>
       </c>
       <c r="X3" s="0">
-        <v>0.23303504334469735</v>
+        <v>0.82418659019088669</v>
       </c>
       <c r="Y3" s="0">
-        <v>0.23459033793745981</v>
+        <v>0.82419707389450236</v>
       </c>
       <c r="Z3" s="0">
-        <v>0.24532355158059896</v>
+        <v>0.82425112321090344</v>
       </c>
       <c r="AA3" s="0">
-        <v>0.26477402364655456</v>
+        <v>0.82434815835953656</v>
       </c>
       <c r="AB3" s="0">
-        <v>0.27086619961583891</v>
+        <v>0.82437928648757564</v>
       </c>
       <c r="AC3" s="0">
-        <v>0.27732243682405194</v>
+        <v>0.82441192760466886</v>
       </c>
       <c r="AD3" s="0">
-        <v>0.28326396675860144</v>
+        <v>0.824441822044368</v>
       </c>
       <c r="AE3" s="0">
-        <v>0.28875270753839516</v>
+        <v>0.82446931396865708</v>
       </c>
       <c r="AF3" s="0">
-        <v>0.2937983016290367</v>
+        <v>0.82449448544693205</v>
       </c>
       <c r="AG3" s="0">
-        <v>0.2984648691395797</v>
+        <v>0.82451767799377496</v>
       </c>
       <c r="AH3" s="0">
-        <v>0.30275011016091563</v>
+        <v>0.82453890484618775</v>
       </c>
       <c r="AI3" s="0">
-        <v>0.3067195988264334</v>
+        <v>0.82455850487136784</v>
       </c>
       <c r="AJ3" s="0">
-        <v>0.31038585573442545</v>
+        <v>0.82457655616759984</v>
       </c>
       <c r="AK3" s="0">
-        <v>0.31376106299279</v>
+        <v>0.82459313153838987</v>
       </c>
       <c r="AL3" s="0">
-        <v>0.31687188997003873</v>
+        <v>0.82460837261963282</v>
       </c>
       <c r="AM3" s="0">
-        <v>0.31974500579721754</v>
+        <v>0.82462241839980777</v>
       </c>
       <c r="AN3" s="0">
-        <v>0.32239350389829635</v>
+        <v>0.82463534035873243</v>
       </c>
       <c r="AO3" s="0">
-        <v>0.32485815741776086</v>
+        <v>0.82464734234619941</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="B4" s="0">
-        <v>3.8617441345936458</v>
+        <v>-76.385842559623711</v>
       </c>
       <c r="C4" s="0">
-        <v>-0.14979585347489208</v>
+        <v>0.82094124192810525</v>
       </c>
       <c r="D4" s="0">
-        <v>-0.064377547956065193</v>
+        <v>0.82165794073485987</v>
       </c>
       <c r="E4" s="0">
-        <v>-0.471110831628968</v>
+        <v>0.81813317662047991</v>
       </c>
       <c r="F4" s="0">
-        <v>1.9920741010088645</v>
+        <v>0.83876345732498836</v>
       </c>
       <c r="G4" s="0">
-        <v>-0.1331939291429341</v>
+        <v>0.82135485712814105</v>
       </c>
       <c r="H4" s="0">
-        <v>-0.033118382580705097</v>
+        <v>0.82211442528151601</v>
       </c>
       <c r="I4" s="0">
-        <v>-0.17125586517384622</v>
+        <v>0.82118756395721948</v>
       </c>
       <c r="J4" s="0">
-        <v>-0.74229524012292802</v>
+        <v>0.81697142076873885</v>
       </c>
       <c r="K4" s="0">
-        <v>1.4012332189599792</v>
+        <v>0.83201023403549812</v>
       </c>
       <c r="L4" s="0">
-        <v>0.1428093052771269</v>
+        <v>0.82353596386718597</v>
       </c>
       <c r="M4" s="0">
-        <v>-0.016962255357252546</v>
+        <v>0.82265467620849242</v>
       </c>
       <c r="N4" s="0">
-        <v>-0.063251766051471162</v>
+        <v>0.82243227740859293</v>
       </c>
       <c r="O4" s="0">
-        <v>-0.16734842872738823</v>
+        <v>0.82185835155487197</v>
       </c>
       <c r="P4" s="0">
-        <v>-0.13752451561889137</v>
+        <v>0.822034449977876</v>
       </c>
       <c r="Q4" s="0">
-        <v>-0.12120867534074153</v>
+        <v>0.82214693138122963</v>
       </c>
       <c r="R4" s="0">
-        <v>-0.051119905340607563</v>
+        <v>0.82257521582413062</v>
       </c>
       <c r="S4" s="0">
-        <v>-0.017367738329386127</v>
+        <v>0.82278132914352753</v>
       </c>
       <c r="T4" s="0">
-        <v>0.024542451217253087</v>
+        <v>0.82302238019942642</v>
       </c>
       <c r="U4" s="0">
-        <v>0.049805074729334917</v>
+        <v>0.82316132236481221</v>
       </c>
       <c r="V4" s="0">
-        <v>0.17136388189526772</v>
+        <v>0.82382758555603375</v>
       </c>
       <c r="W4" s="0">
-        <v>0.11352206648272711</v>
+        <v>0.82354787849044742</v>
       </c>
       <c r="X4" s="0">
-        <v>0.13926864399558758</v>
+        <v>0.8236931625022943</v>
       </c>
       <c r="Y4" s="0">
-        <v>0.14819636356677515</v>
+        <v>0.82374649966812197</v>
       </c>
       <c r="Z4" s="0">
-        <v>0.15980677872163215</v>
+        <v>0.82381052173995839</v>
       </c>
       <c r="AA4" s="0">
-        <v>0.19242741018098053</v>
+        <v>0.82397814583587925</v>
       </c>
       <c r="AB4" s="0">
-        <v>0.2056511934430566</v>
+        <v>0.82404738460922111</v>
       </c>
       <c r="AC4" s="0">
-        <v>0.21730859432279351</v>
+        <v>0.82410808154678061</v>
       </c>
       <c r="AD4" s="0">
-        <v>0.22804412478530497</v>
+        <v>0.82416357634353954</v>
       </c>
       <c r="AE4" s="0">
-        <v>0.23794556004482573</v>
+        <v>0.82421441965866182</v>
       </c>
       <c r="AF4" s="0">
-        <v>0.2470511397849609</v>
+        <v>0.82426089608765229</v>
       </c>
       <c r="AG4" s="0">
-        <v>0.25544183656815578</v>
+        <v>0.82430348613356985</v>
       </c>
       <c r="AH4" s="0">
-        <v>0.26317463864208335</v>
+        <v>0.82434253792952883</v>
       </c>
       <c r="AI4" s="0">
-        <v>0.27030834937208936</v>
+        <v>0.82437839563751347</v>
       </c>
       <c r="AJ4" s="0">
-        <v>0.27686330119286268</v>
+        <v>0.82441120618820296</v>
       </c>
       <c r="AK4" s="0">
-        <v>0.28288805762769687</v>
+        <v>0.82444124755859383</v>
       </c>
       <c r="AL4" s="0">
-        <v>0.28844543347058466</v>
+        <v>0.82446885861587471</v>
       </c>
       <c r="AM4" s="0">
-        <v>0.2935728207266981</v>
+        <v>0.82449424982833264</v>
       </c>
       <c r="AN4" s="0">
-        <v>0.29829458291122551</v>
+        <v>0.82451756283187916</v>
       </c>
       <c r="AO4" s="0">
-        <v>0.30263539596233013</v>
+        <v>0.82453893661499544</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="B5" s="0">
-        <v>3.3835441160236299</v>
+        <v>-76.389853370475763</v>
       </c>
       <c r="C5" s="0">
-        <v>-0.3322257951734176</v>
+        <v>0.81915546612167112</v>
       </c>
       <c r="D5" s="0">
-        <v>-0.068005746648356444</v>
+        <v>0.8214312001991263</v>
       </c>
       <c r="E5" s="0">
-        <v>-0.47274054849669062</v>
+        <v>0.81799270955277159</v>
       </c>
       <c r="F5" s="0">
-        <v>0.78100115493630295</v>
+        <v>0.82854831125259876</v>
       </c>
       <c r="G5" s="0">
-        <v>-0.3748117461835504</v>
+        <v>0.81925345830535357</v>
       </c>
       <c r="H5" s="0">
-        <v>-0.23346862264039805</v>
+        <v>0.82037312182235977</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.3854106768861843</v>
+        <v>0.81926169171905483</v>
       </c>
       <c r="J5" s="0">
-        <v>-0.69259646011069032</v>
+        <v>0.81680561411284924</v>
       </c>
       <c r="K5" s="0">
-        <v>1.0399777588704404</v>
+        <v>0.82991617645263294</v>
       </c>
       <c r="L5" s="0">
-        <v>-0.22062648256635006</v>
+        <v>0.82105896915435916</v>
       </c>
       <c r="M5" s="0">
-        <v>-0.23003876679054727</v>
+        <v>0.82112723633193907</v>
       </c>
       <c r="N5" s="0">
-        <v>-0.256155999663847</v>
+        <v>0.82107033708953925</v>
       </c>
       <c r="O5" s="0">
-        <v>-0.381694964504738</v>
+        <v>0.82034104592514145</v>
       </c>
       <c r="P5" s="0">
-        <v>-0.27462567425654688</v>
+        <v>0.82101544457627029</v>
       </c>
       <c r="Q5" s="0">
-        <v>-0.28913135804615658</v>
+        <v>0.82094228367996458</v>
       </c>
       <c r="R5" s="0">
-        <v>-0.18674372455276722</v>
+        <v>0.82160615362167122</v>
       </c>
       <c r="S5" s="0">
-        <v>-0.12878305153647926</v>
+        <v>0.822017215404511</v>
       </c>
       <c r="T5" s="0">
-        <v>-0.020049000013961489</v>
+        <v>0.82268396571731484</v>
       </c>
       <c r="U5" s="0">
-        <v>-0.049343955441005519</v>
+        <v>0.82253745595932437</v>
       </c>
       <c r="V5" s="0">
-        <v>-0.0017190078717112783</v>
+        <v>0.82281643498992163</v>
       </c>
       <c r="W5" s="0">
-        <v>-0.051834133435987056</v>
+        <v>0.8225803928146378</v>
       </c>
       <c r="X5" s="0">
-        <v>-0.014866914208949249</v>
+        <v>0.82282042197418781</v>
       </c>
       <c r="Y5" s="0">
-        <v>-0.0067313383491606092</v>
+        <v>0.82288900948715804</v>
       </c>
       <c r="Z5" s="0">
-        <v>-0.003095781966734761</v>
+        <v>0.82292343098067855</v>
       </c>
       <c r="AA5" s="0">
-        <v>0.031627239163851753</v>
+        <v>0.82311830476378545</v>
       </c>
       <c r="AB5" s="0">
-        <v>0.049529211978822825</v>
+        <v>0.82322206166076817</v>
       </c>
       <c r="AC5" s="0">
-        <v>0.072805023745590544</v>
+        <v>0.82335053865432328</v>
       </c>
       <c r="AD5" s="0">
-        <v>0.09432619815697095</v>
+        <v>0.82346792436599203</v>
       </c>
       <c r="AE5" s="0">
-        <v>0.11423088030835205</v>
+        <v>0.82357530952453395</v>
       </c>
       <c r="AF5" s="0">
-        <v>0.13263060914101318</v>
+        <v>0.82367358630371224</v>
       </c>
       <c r="AG5" s="0">
-        <v>0.14963426207182526</v>
+        <v>0.82376357407379275</v>
       </c>
       <c r="AH5" s="0">
-        <v>0.16533289788822461</v>
+        <v>0.82384596115875042</v>
       </c>
       <c r="AI5" s="0">
-        <v>0.17982471815499454</v>
+        <v>0.82392143323516787</v>
       </c>
       <c r="AJ5" s="0">
-        <v>0.1931876338980304</v>
+        <v>0.82399053963852587</v>
       </c>
       <c r="AK5" s="0">
-        <v>0.20553095894470491</v>
+        <v>0.82405395942688653</v>
       </c>
       <c r="AL5" s="0">
-        <v>0.21691543827766596</v>
+        <v>0.82411210824203052</v>
       </c>
       <c r="AM5" s="0">
-        <v>0.22743181429020806</v>
+        <v>0.8241655301246662</v>
       </c>
       <c r="AN5" s="0">
-        <v>0.23712057712049145</v>
+        <v>0.82421450569915866</v>
       </c>
       <c r="AO5" s="0">
-        <v>0.24603770472634595</v>
+        <v>0.82425937780380631</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>485</v>
+        <v>517</v>
       </c>
       <c r="B6" s="0">
-        <v>2.3367529798354454</v>
+        <v>-76.399736312866196</v>
       </c>
       <c r="C6" s="0">
-        <v>-0.85963302942240349</v>
+        <v>0.81353033699417365</v>
       </c>
       <c r="D6" s="0">
-        <v>-0.53357283927478494</v>
+        <v>0.81668170256042716</v>
       </c>
       <c r="E6" s="0">
-        <v>-0.8633059408110223</v>
+        <v>0.81364271382522535</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.14521493883917475</v>
+        <v>0.82044143135833703</v>
       </c>
       <c r="G6" s="0">
-        <v>-0.79820379927726548</v>
+        <v>0.81488744051360673</v>
       </c>
       <c r="H6" s="0">
-        <v>-0.63997815452746809</v>
+        <v>0.81631927351379674</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.73862937929175099</v>
+        <v>0.81553279851150584</v>
       </c>
       <c r="J6" s="0">
-        <v>-0.94147731753397457</v>
+        <v>0.81362230766677768</v>
       </c>
       <c r="K6" s="0">
-        <v>0.51641646968585486</v>
+        <v>0.82626610428237868</v>
       </c>
       <c r="L6" s="0">
-        <v>-0.64423278370507031</v>
+        <v>0.81746145184326291</v>
       </c>
       <c r="M6" s="0">
-        <v>-0.5435744011811664</v>
+        <v>0.81839761480713502</v>
       </c>
       <c r="N6" s="0">
-        <v>-0.58716193225348279</v>
+        <v>0.81830098206329449</v>
       </c>
       <c r="O6" s="0">
-        <v>-0.66761422379892266</v>
+        <v>0.81790114922714785</v>
       </c>
       <c r="P6" s="0">
-        <v>-0.54314775690578065</v>
+        <v>0.81880706299972661</v>
       </c>
       <c r="Q6" s="0">
-        <v>-0.52313912514745342</v>
+        <v>0.81902464617919202</v>
       </c>
       <c r="R6" s="0">
-        <v>-0.40099044869431488</v>
+        <v>0.81988730937958409</v>
       </c>
       <c r="S6" s="0">
-        <v>-0.33145769037372724</v>
+        <v>0.82045600529480234</v>
       </c>
       <c r="T6" s="0">
-        <v>-0.15932535415545362</v>
+        <v>0.82167419709395884</v>
       </c>
       <c r="U6" s="0">
-        <v>-0.212674546096733</v>
+        <v>0.82142275234603446</v>
       </c>
       <c r="V6" s="0">
-        <v>-0.18566627322467255</v>
+        <v>0.82161125383757794</v>
       </c>
       <c r="W6" s="0">
-        <v>-0.18407468873605864</v>
+        <v>0.82164920828628552</v>
       </c>
       <c r="X6" s="0">
-        <v>-0.16497217836139871</v>
+        <v>0.82181413335800635</v>
       </c>
       <c r="Y6" s="0">
-        <v>-0.1449028655212054</v>
+        <v>0.82199377929686579</v>
       </c>
       <c r="Z6" s="0">
-        <v>-0.14332011729432714</v>
+        <v>0.82204060385894218</v>
       </c>
       <c r="AA6" s="0">
-        <v>-0.084486861971282454</v>
+        <v>0.82239491068267856</v>
       </c>
       <c r="AB6" s="0">
-        <v>-0.062033087422348351</v>
+        <v>0.82254300755691323</v>
       </c>
       <c r="AC6" s="0">
-        <v>-0.031119069399627025</v>
+        <v>0.82273027138900801</v>
       </c>
       <c r="AD6" s="0">
-        <v>-0.0023206973636775538</v>
+        <v>0.8229013410759034</v>
       </c>
       <c r="AE6" s="0">
-        <v>0.024446054663122323</v>
+        <v>0.82305753105164225</v>
       </c>
       <c r="AF6" s="0">
-        <v>0.04932669299978526</v>
+        <v>0.82320035033416883</v>
       </c>
       <c r="AG6" s="0">
-        <v>0.072401690555763065</v>
+        <v>0.82333084067535589</v>
       </c>
       <c r="AH6" s="0">
-        <v>0.093782157014208736</v>
+        <v>0.82345010206985192</v>
       </c>
       <c r="AI6" s="0">
-        <v>0.11360749969971522</v>
+        <v>0.82355929937362737</v>
       </c>
       <c r="AJ6" s="0">
-        <v>0.131928697614216</v>
+        <v>0.82365906531524802</v>
       </c>
       <c r="AK6" s="0">
-        <v>0.14889745748823444</v>
+        <v>0.82375048929977734</v>
       </c>
       <c r="AL6" s="0">
-        <v>0.16458524362599089</v>
+        <v>0.82383419743728403</v>
       </c>
       <c r="AM6" s="0">
-        <v>0.17907119064722388</v>
+        <v>0.82391081186676274</v>
       </c>
       <c r="AN6" s="0">
-        <v>0.19245424140617981</v>
+        <v>0.82398101958846304</v>
       </c>
       <c r="AO6" s="0">
-        <v>0.20478665144374669</v>
+        <v>0.82404523889160952</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>486</v>
+        <v>518</v>
       </c>
       <c r="B7" s="0">
-        <v>0.6342573896817455</v>
+        <v>-76.420045046997075</v>
       </c>
       <c r="C7" s="0">
-        <v>-1.5606164442804087</v>
+        <v>0.80228348991394283</v>
       </c>
       <c r="D7" s="0">
-        <v>-1.2179981131092623</v>
+        <v>0.80674809025954364</v>
       </c>
       <c r="E7" s="0">
-        <v>-1.4754706996240925</v>
+        <v>0.8039191806488073</v>
       </c>
       <c r="F7" s="0">
-        <v>-1.0002371363335647</v>
+        <v>0.8098258329582233</v>
       </c>
       <c r="G7" s="0">
-        <v>-1.4680216383737419</v>
+        <v>0.80517806033706396</v>
       </c>
       <c r="H7" s="0">
-        <v>-1.3053290050915214</v>
+        <v>0.8071892172393732</v>
       </c>
       <c r="I7" s="0">
-        <v>-1.4105340614582957</v>
+        <v>0.80621211223602851</v>
       </c>
       <c r="J7" s="0">
-        <v>-1.612915512708607</v>
+        <v>0.80368735710525696</v>
       </c>
       <c r="K7" s="0">
-        <v>-0.2013953973717221</v>
+        <v>0.81956893306733336</v>
       </c>
       <c r="L7" s="0">
-        <v>-1.2601744464418381</v>
+        <v>0.81045661569595673</v>
       </c>
       <c r="M7" s="0">
-        <v>-1.0918692142961031</v>
+        <v>0.81224390052032269</v>
       </c>
       <c r="N7" s="0">
-        <v>-1.1615156450131203</v>
+        <v>0.8120572217636195</v>
       </c>
       <c r="O7" s="0">
-        <v>-1.2694714546364219</v>
+        <v>0.81146886625671444</v>
       </c>
       <c r="P7" s="0">
-        <v>-1.0296294525628911</v>
+        <v>0.81387259417724822</v>
       </c>
       <c r="Q7" s="0">
-        <v>-0.95563231170172835</v>
+        <v>0.81471074907303043</v>
       </c>
       <c r="R7" s="0">
-        <v>-0.81275778923562081</v>
+        <v>0.81605816178512713</v>
       </c>
       <c r="S7" s="0">
-        <v>-0.71965452274329078</v>
+        <v>0.81696687518310762</v>
       </c>
       <c r="T7" s="0">
-        <v>-0.46540955133558476</v>
+        <v>0.81911952899170093</v>
       </c>
       <c r="U7" s="0">
-        <v>-0.57265134377034155</v>
+        <v>0.81864249797439848</v>
       </c>
       <c r="V7" s="0">
-        <v>-0.35764922461547749</v>
+        <v>0.82023347280120928</v>
       </c>
       <c r="W7" s="0">
-        <v>-0.30413317219934866</v>
+        <v>0.82063587891006351</v>
       </c>
       <c r="X7" s="0">
-        <v>-0.30766078415576104</v>
+        <v>0.82065098762131294</v>
       </c>
       <c r="Y7" s="0">
-        <v>-0.32912365132445953</v>
+        <v>0.82059061896133634</v>
       </c>
       <c r="Z7" s="0">
-        <v>-0.34466894282716182</v>
+        <v>0.82059329018784055</v>
       </c>
       <c r="AA7" s="0">
-        <v>-0.26142520285895054</v>
+        <v>0.82116537609863194</v>
       </c>
       <c r="AB7" s="0">
-        <v>-0.23177425250312722</v>
+        <v>0.82139914018630833</v>
       </c>
       <c r="AC7" s="0">
-        <v>-0.19089952953604616</v>
+        <v>0.82168350932312095</v>
       </c>
       <c r="AD7" s="0">
-        <v>-0.15242549124238003</v>
+        <v>0.82194307099914943</v>
       </c>
       <c r="AE7" s="0">
-        <v>-0.11629770331817545</v>
+        <v>0.82218003844070542</v>
       </c>
       <c r="AF7" s="0">
-        <v>-0.082423018850557098</v>
+        <v>0.82239654545211716</v>
       </c>
       <c r="AG7" s="0">
-        <v>-0.05074982837032236</v>
+        <v>0.82259426254272672</v>
       </c>
       <c r="AH7" s="0">
-        <v>-0.021176824312667524</v>
+        <v>0.82277491316986573</v>
       </c>
       <c r="AI7" s="0">
-        <v>0.0064300628039393347</v>
+        <v>0.82294021417237007</v>
       </c>
       <c r="AJ7" s="0">
-        <v>0.032110306093803491</v>
+        <v>0.82309122053909034</v>
       </c>
       <c r="AK7" s="0">
-        <v>0.056013411609087203</v>
+        <v>0.82322943731688869</v>
       </c>
       <c r="AL7" s="0">
-        <v>0.078209957582743378</v>
+        <v>0.82335584272003226</v>
       </c>
       <c r="AM7" s="0">
-        <v>0.098813151104439528</v>
+        <v>0.8234715380668618</v>
       </c>
       <c r="AN7" s="0">
-        <v>0.11792616737165813</v>
+        <v>0.82357748833466415</v>
       </c>
       <c r="AO7" s="0">
-        <v>0.13563931552931624</v>
+        <v>0.82367452613067382</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>487</v>
+        <v>519</v>
       </c>
       <c r="B8" s="0">
-        <v>-1.2947345630025511</v>
+        <v>-76.45288041706084</v>
       </c>
       <c r="C8" s="0">
-        <v>-1.8569699639107349</v>
+        <v>0.78786323766327482</v>
       </c>
       <c r="D8" s="0">
-        <v>-1.4447994520159686</v>
+        <v>0.79576274804687297</v>
       </c>
       <c r="E8" s="0">
-        <v>-1.7650270701389945</v>
+        <v>0.79097673085021936</v>
       </c>
       <c r="F8" s="0">
-        <v>-1.3158592852491462</v>
+        <v>0.79935649678420484</v>
       </c>
       <c r="G8" s="0">
-        <v>-1.7195942683255485</v>
+        <v>0.79377740329360347</v>
       </c>
       <c r="H8" s="0">
-        <v>-1.4962252248236469</v>
+        <v>0.79781249345016425</v>
       </c>
       <c r="I8" s="0">
-        <v>-1.6123266664659848</v>
+        <v>0.79652918355560798</v>
       </c>
       <c r="J8" s="0">
-        <v>-1.8792530639775762</v>
+        <v>0.79166571667480956</v>
       </c>
       <c r="K8" s="0">
-        <v>-0.51004878599025327</v>
+        <v>0.81371641876220535</v>
       </c>
       <c r="L8" s="0">
-        <v>-1.5095780289730312</v>
+        <v>0.8027706525306697</v>
       </c>
       <c r="M8" s="0">
-        <v>-1.3664864319547594</v>
+        <v>0.80518513418961579</v>
       </c>
       <c r="N8" s="0">
-        <v>-1.4168136001430287</v>
+        <v>0.80523866196823879</v>
       </c>
       <c r="O8" s="0">
-        <v>-1.5338388354238104</v>
+        <v>0.80434982524871468</v>
       </c>
       <c r="P8" s="0">
-        <v>-1.2580160308909025</v>
+        <v>0.80813058631515955</v>
       </c>
       <c r="Q8" s="0">
-        <v>-1.2132366801108141</v>
+        <v>0.80957663320541828</v>
       </c>
       <c r="R8" s="0">
-        <v>-1.0335357569682713</v>
+        <v>0.81195923355102928</v>
       </c>
       <c r="S8" s="0">
-        <v>-0.91187095152011222</v>
+        <v>0.81365212930298114</v>
       </c>
       <c r="T8" s="0">
-        <v>-0.63895346842742884</v>
+        <v>0.81655165433503174</v>
       </c>
       <c r="U8" s="0">
-        <v>-0.82095882317146007</v>
+        <v>0.81552879299545233</v>
       </c>
       <c r="V8" s="0">
-        <v>-0.48448995098604825</v>
+        <v>0.81860888393784348</v>
       </c>
       <c r="W8" s="0">
-        <v>-0.55380117246467486</v>
+        <v>0.81837208328246669</v>
       </c>
       <c r="X8" s="0">
-        <v>-0.54394189461860654</v>
+        <v>0.81855637408447957</v>
       </c>
       <c r="Y8" s="0">
-        <v>-0.60007729546283883</v>
+        <v>0.81819804983138877</v>
       </c>
       <c r="Z8" s="0">
-        <v>-0.59155971196372537</v>
+        <v>0.81837111698149956</v>
       </c>
       <c r="AA8" s="0">
-        <v>-0.48215243340476344</v>
+        <v>0.81928850590896807</v>
       </c>
       <c r="AB8" s="0">
-        <v>-0.45752716955655121</v>
+        <v>0.81958948350906269</v>
       </c>
       <c r="AC8" s="0">
-        <v>-0.40580809555095115</v>
+        <v>0.8200314775123605</v>
       </c>
       <c r="AD8" s="0">
-        <v>-0.35631317530455803</v>
+        <v>0.82043480094527976</v>
       </c>
       <c r="AE8" s="0">
-        <v>-0.30913502861761216</v>
+        <v>0.82080284777450674</v>
       </c>
       <c r="AF8" s="0">
-        <v>-0.26431497137974774</v>
+        <v>0.82113880017471585</v>
       </c>
       <c r="AG8" s="0">
-        <v>-0.2218822876774991</v>
+        <v>0.8214454286499101</v>
       </c>
       <c r="AH8" s="0">
-        <v>-0.18181113156123271</v>
+        <v>0.8217254282531733</v>
       </c>
       <c r="AI8" s="0">
-        <v>-0.14405844170499063</v>
+        <v>0.82198121738433672</v>
       </c>
       <c r="AJ8" s="0">
-        <v>-0.10862003048799129</v>
+        <v>0.8222146783447235</v>
       </c>
       <c r="AK8" s="0">
-        <v>-0.075387094369860838</v>
+        <v>0.82242801112366526</v>
       </c>
       <c r="AL8" s="0">
-        <v>-0.044279237808109835</v>
+        <v>0.8226230146293656</v>
       </c>
       <c r="AM8" s="0">
-        <v>-0.015227493523464374</v>
+        <v>0.82280121508788995</v>
       </c>
       <c r="AN8" s="0">
-        <v>0.011879916576076498</v>
+        <v>0.82296419829178458</v>
       </c>
       <c r="AO8" s="0">
-        <v>0.037121602047098037</v>
+        <v>0.82311321249007796</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>488</v>
+        <v>520</v>
       </c>
       <c r="B9" s="0">
-        <v>-3.2126749646342412</v>
+        <v>-76.504593336868282</v>
       </c>
       <c r="C9" s="0">
-        <v>-1.8334626419256059</v>
+        <v>0.76820925185776023</v>
       </c>
       <c r="D9" s="0">
-        <v>-1.5335718348560086</v>
+        <v>0.77683491226578594</v>
       </c>
       <c r="E9" s="0">
-        <v>-1.9075131064168089</v>
+        <v>0.76815505693435582</v>
       </c>
       <c r="F9" s="0">
-        <v>-1.4342108194785281</v>
+        <v>0.78288477434921611</v>
       </c>
       <c r="G9" s="0">
-        <v>-1.8739355427735516</v>
+        <v>0.77368091650772264</v>
       </c>
       <c r="H9" s="0">
-        <v>-1.6232707577576735</v>
+        <v>0.78071862541961523</v>
       </c>
       <c r="I9" s="0">
-        <v>-1.7848181424945087</v>
+        <v>0.77825165243911976</v>
       </c>
       <c r="J9" s="0">
-        <v>-2.0883902591846168</v>
+        <v>0.76947909045791785</v>
       </c>
       <c r="K9" s="0">
-        <v>-0.84211757957753375</v>
+        <v>0.80137046654891919</v>
       </c>
       <c r="L9" s="0">
-        <v>-1.7760070814453595</v>
+        <v>0.78728423806762637</v>
       </c>
       <c r="M9" s="0">
-        <v>-1.6522866422399425</v>
+        <v>0.79143423067474306</v>
       </c>
       <c r="N9" s="0">
-        <v>-1.6744330049753893</v>
+        <v>0.79272157255935405</v>
       </c>
       <c r="O9" s="0">
-        <v>-1.8277645461944341</v>
+        <v>0.79076709516524912</v>
       </c>
       <c r="P9" s="0">
-        <v>-1.5475887212595199</v>
+        <v>0.79655805742263486</v>
       </c>
       <c r="Q9" s="0">
-        <v>-1.4880955393425639</v>
+        <v>0.79955788449477827</v>
       </c>
       <c r="R9" s="0">
-        <v>-1.3570266477429989</v>
+        <v>0.8033477036399832</v>
       </c>
       <c r="S9" s="0">
-        <v>-1.2690381324679074</v>
+        <v>0.80592925873566124</v>
       </c>
       <c r="T9" s="0">
-        <v>-0.95637754414134135</v>
+        <v>0.81094790560913621</v>
       </c>
       <c r="U9" s="0">
-        <v>-1.2315465632411828</v>
+        <v>0.80886990318298657</v>
       </c>
       <c r="V9" s="0">
-        <v>-0.67391752468762522</v>
+        <v>0.81545383054351683</v>
       </c>
       <c r="W9" s="0">
-        <v>-0.72058210841637049</v>
+        <v>0.81580751258087525</v>
       </c>
       <c r="X9" s="0">
-        <v>-0.71515804733071497</v>
+        <v>0.81621065599060316</v>
       </c>
       <c r="Y9" s="0">
-        <v>-0.77403124696524617</v>
+        <v>0.81586819231032703</v>
       </c>
       <c r="Z9" s="0">
-        <v>-0.79875774578935865</v>
+        <v>0.81567095307540216</v>
       </c>
       <c r="AA9" s="0">
-        <v>-0.66030570099129238</v>
+        <v>0.81700894501495602</v>
       </c>
       <c r="AB9" s="0">
-        <v>-0.66345875745118366</v>
+        <v>0.81727634167099994</v>
       </c>
       <c r="AC9" s="0">
-        <v>-0.6104434077801173</v>
+        <v>0.81789861301804634</v>
       </c>
       <c r="AD9" s="0">
-        <v>-0.55823130006847688</v>
+        <v>0.81846806476593525</v>
       </c>
       <c r="AE9" s="0">
-        <v>-0.50715853064795036</v>
+        <v>0.81898897246551094</v>
       </c>
       <c r="AF9" s="0">
-        <v>-0.45745537823617138</v>
+        <v>0.81946565534973215</v>
       </c>
       <c r="AG9" s="0">
-        <v>-0.40935282645472443</v>
+        <v>0.81990175359344863</v>
       </c>
       <c r="AH9" s="0">
-        <v>-0.36298169652486389</v>
+        <v>0.820300951053618</v>
       </c>
       <c r="AI9" s="0">
-        <v>-0.31849186254931577</v>
+        <v>0.82066625914764413</v>
       </c>
       <c r="AJ9" s="0">
-        <v>-0.27597800990619326</v>
+        <v>0.8210005397148068</v>
       </c>
       <c r="AK9" s="0">
-        <v>-0.23544155694307101</v>
+        <v>0.82130676975632799</v>
       </c>
       <c r="AL9" s="0">
-        <v>-0.19693887307331009</v>
+        <v>0.82158719161986948</v>
       </c>
       <c r="AM9" s="0">
-        <v>-0.16048169835377443</v>
+        <v>0.82184396955490313</v>
       </c>
       <c r="AN9" s="0">
-        <v>-0.12601827832887794</v>
+        <v>0.82207932075881873</v>
       </c>
       <c r="AO9" s="0">
-        <v>-0.093542462830045275</v>
+        <v>0.82229492765426637</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="B10" s="0">
-        <v>-4.9428506831170758</v>
+        <v>-76.586281772994994</v>
       </c>
       <c r="C10" s="0">
-        <v>-1.6505749107313774</v>
+        <v>0.73684446081542521</v>
       </c>
       <c r="D10" s="0">
-        <v>-1.42004460674209</v>
+        <v>0.7491131963157639</v>
       </c>
       <c r="E10" s="0">
-        <v>-1.6417556060474525</v>
+        <v>0.73976235350800101</v>
       </c>
       <c r="F10" s="0">
-        <v>-1.2732676371382974</v>
+        <v>0.76001584699249181</v>
       </c>
       <c r="G10" s="0">
-        <v>-1.7261158877625009</v>
+        <v>0.74418240076065334</v>
       </c>
       <c r="H10" s="0">
-        <v>-1.4682304692465939</v>
+        <v>0.75697234179305684</v>
       </c>
       <c r="I10" s="0">
-        <v>-1.6192930661569931</v>
+        <v>0.75343734283065467</v>
       </c>
       <c r="J10" s="0">
-        <v>-1.9251548721634584</v>
+        <v>0.73791829386901608</v>
       </c>
       <c r="K10" s="0">
-        <v>-0.88113453193694746</v>
+        <v>0.78460654396819662</v>
       </c>
       <c r="L10" s="0">
-        <v>-1.7303120233487759</v>
+        <v>0.76306426047134623</v>
       </c>
       <c r="M10" s="0">
-        <v>-1.657516514325307</v>
+        <v>0.76943989437865934</v>
       </c>
       <c r="N10" s="0">
-        <v>-1.7035877055107278</v>
+        <v>0.77221772902679331</v>
       </c>
       <c r="O10" s="0">
-        <v>-1.8121144196941286</v>
+        <v>0.77169350942993731</v>
       </c>
       <c r="P10" s="0">
-        <v>-1.598145384458004</v>
+        <v>0.77877056267546985</v>
       </c>
       <c r="Q10" s="0">
-        <v>-1.6091823929960545</v>
+        <v>0.78214777792739831</v>
       </c>
       <c r="R10" s="0">
-        <v>-1.5997426344639214</v>
+        <v>0.78647951453780884</v>
       </c>
       <c r="S10" s="0">
-        <v>-1.5464630436653346</v>
+        <v>0.79181418153763039</v>
       </c>
       <c r="T10" s="0">
-        <v>-1.2143369252771332</v>
+        <v>0.80108167757797577</v>
       </c>
       <c r="U10" s="0">
-        <v>-1.5887779596797609</v>
+        <v>0.79771801701355349</v>
       </c>
       <c r="V10" s="0">
-        <v>-1.0609365869259437</v>
+        <v>0.80698957019423778</v>
       </c>
       <c r="W10" s="0">
-        <v>-1.2264209167555744</v>
+        <v>0.80723194892120742</v>
       </c>
       <c r="X10" s="0">
-        <v>-1.2380929268079226</v>
+        <v>0.80859177529144155</v>
       </c>
       <c r="Y10" s="0">
-        <v>-1.327517753338824</v>
+        <v>0.80829707335281897</v>
       </c>
       <c r="Z10" s="0">
-        <v>-1.3999981656781157</v>
+        <v>0.80768437632751811</v>
       </c>
       <c r="AA10" s="0">
-        <v>-1.1797483398980531</v>
+        <v>0.81011585694123234</v>
       </c>
       <c r="AB10" s="0">
-        <v>-1.2197624391986648</v>
+        <v>0.8102888023109458</v>
       </c>
       <c r="AC10" s="0">
-        <v>-1.163054174623785</v>
+        <v>0.81144422558212304</v>
       </c>
       <c r="AD10" s="0">
-        <v>-1.1037777224778196</v>
+        <v>0.8125144303741465</v>
       </c>
       <c r="AE10" s="0">
-        <v>-1.0430662730892157</v>
+        <v>0.81349725640868809</v>
       </c>
       <c r="AF10" s="0">
-        <v>-0.98148100095857793</v>
+        <v>0.81439983975218977</v>
       </c>
       <c r="AG10" s="0">
-        <v>-0.91958835394005001</v>
+        <v>0.81522843488693919</v>
       </c>
       <c r="AH10" s="0">
-        <v>-0.85786321163769452</v>
+        <v>0.81598913348006452</v>
       </c>
       <c r="AI10" s="0">
-        <v>-0.79674865785721383</v>
+        <v>0.81668741035461834</v>
       </c>
       <c r="AJ10" s="0">
-        <v>-0.73663059079707327</v>
+        <v>0.81732831939696915</v>
       </c>
       <c r="AK10" s="0">
-        <v>-0.67778805519248286</v>
+        <v>0.81791689463806794</v>
       </c>
       <c r="AL10" s="0">
-        <v>-0.62054537696801093</v>
+        <v>0.81845709658813603</v>
       </c>
       <c r="AM10" s="0">
-        <v>-0.5650614997499368</v>
+        <v>0.81895332787322883</v>
       </c>
       <c r="AN10" s="0">
-        <v>-0.51154734187195461</v>
+        <v>0.81940898510742155</v>
       </c>
       <c r="AO10" s="0">
-        <v>-0.46012172661797118</v>
+        <v>0.81982751917648178</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>490</v>
+        <v>522</v>
       </c>
       <c r="B11" s="0">
-        <v>-6.091327955903342</v>
+        <v>-76.682594446182236</v>
       </c>
       <c r="C11" s="0">
-        <v>-1.0851163346302817</v>
+        <v>0.72021727511597</v>
       </c>
       <c r="D11" s="0">
-        <v>-0.94612439594720521</v>
+        <v>0.73312659667587654</v>
       </c>
       <c r="E11" s="0">
-        <v>-1.1423108745306449</v>
+        <v>0.71832273353195841</v>
       </c>
       <c r="F11" s="0">
-        <v>-0.87524842992492158</v>
+        <v>0.74366132627487846</v>
       </c>
       <c r="G11" s="0">
-        <v>-1.2550125394570215</v>
+        <v>0.71769195476531888</v>
       </c>
       <c r="H11" s="0">
-        <v>-1.002647546917723</v>
+        <v>0.74046688486480605</v>
       </c>
       <c r="I11" s="0">
-        <v>-1.1756092142785881</v>
+        <v>0.73190373353957916</v>
       </c>
       <c r="J11" s="0">
-        <v>-1.512815550102053</v>
+        <v>0.700923052425384</v>
       </c>
       <c r="K11" s="0">
-        <v>-0.67372559790855269</v>
+        <v>0.76829424663162005</v>
       </c>
       <c r="L11" s="0">
-        <v>-1.3413280255608413</v>
+        <v>0.73778980496216473</v>
       </c>
       <c r="M11" s="0">
-        <v>-1.2598795261353286</v>
+        <v>0.74731998661042331</v>
       </c>
       <c r="N11" s="0">
-        <v>-1.3627292908750213</v>
+        <v>0.74822188162995396</v>
       </c>
       <c r="O11" s="0">
-        <v>-1.4568103340593281</v>
+        <v>0.74913968355179883</v>
       </c>
       <c r="P11" s="0">
-        <v>-1.3968773986363947</v>
+        <v>0.75558229932403254</v>
       </c>
       <c r="Q11" s="0">
-        <v>-1.4071669029487679</v>
+        <v>0.75979970664596708</v>
       </c>
       <c r="R11" s="0">
-        <v>-1.461239852509103</v>
+        <v>0.76347707218551497</v>
       </c>
       <c r="S11" s="0">
-        <v>-1.4677087926630947</v>
+        <v>0.77051458254241667</v>
       </c>
       <c r="T11" s="0">
-        <v>-1.2335614306345153</v>
+        <v>0.78591266915512403</v>
       </c>
       <c r="U11" s="0">
-        <v>-1.7078384122682095</v>
+        <v>0.77950472902678736</v>
       </c>
       <c r="V11" s="0">
-        <v>-1.3098108904359527</v>
+        <v>0.79268609210587038</v>
       </c>
       <c r="W11" s="0">
-        <v>-1.4569199335783618</v>
+        <v>0.79425226079559508</v>
       </c>
       <c r="X11" s="0">
-        <v>-1.5374731922103975</v>
+        <v>0.79654020071029485</v>
       </c>
       <c r="Y11" s="0">
-        <v>-1.7158341024678005</v>
+        <v>0.79622233799362918</v>
       </c>
       <c r="Z11" s="0">
-        <v>-1.8370903032586885</v>
+        <v>0.79520781464004409</v>
       </c>
       <c r="AA11" s="0">
-        <v>-1.5895508694481808</v>
+        <v>0.79931831333541814</v>
       </c>
       <c r="AB11" s="0">
-        <v>-1.6840147668795538</v>
+        <v>0.79878373446274142</v>
       </c>
       <c r="AC11" s="0">
-        <v>-1.6566760606573849</v>
+        <v>0.80021830487441814</v>
       </c>
       <c r="AD11" s="0">
-        <v>-1.6035362730104443</v>
+        <v>0.80230761964034825</v>
       </c>
       <c r="AE11" s="0">
-        <v>-1.5442178346702122</v>
+        <v>0.8042423116912818</v>
       </c>
       <c r="AF11" s="0">
-        <v>-1.4800471970851681</v>
+        <v>0.80601686781692994</v>
       </c>
       <c r="AG11" s="0">
-        <v>-1.4118634784701869</v>
+        <v>0.80764319337463952</v>
       </c>
       <c r="AH11" s="0">
-        <v>-1.34046390777812</v>
+        <v>0.80913302296447154</v>
       </c>
       <c r="AI11" s="0">
-        <v>-1.2666849357464702</v>
+        <v>0.81049680057907569</v>
       </c>
       <c r="AJ11" s="0">
-        <v>-1.1912744094120959</v>
+        <v>0.81174487093353542</v>
       </c>
       <c r="AK11" s="0">
-        <v>-1.1149641546076925</v>
+        <v>0.81288655419922196</v>
       </c>
       <c r="AL11" s="0">
-        <v>-1.0384511735341293</v>
+        <v>0.81393042265700799</v>
       </c>
       <c r="AM11" s="0">
-        <v>-0.96231931678153459</v>
+        <v>0.81488474810790901</v>
       </c>
       <c r="AN11" s="0">
-        <v>-0.88716089225488415</v>
+        <v>0.81575666529465996</v>
       </c>
       <c r="AO11" s="0">
-        <v>-0.81340392428703223</v>
+        <v>0.81655340823745204</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>491</v>
+        <v>523</v>
       </c>
       <c r="B12" s="0">
-        <v>-6.88664930758409</v>
+        <v>-76.793791264915455</v>
       </c>
       <c r="C12" s="0">
-        <v>-0.73812807832194272</v>
+        <v>0.70411141540527378</v>
       </c>
       <c r="D12" s="0">
-        <v>-0.63142623591496116</v>
+        <v>0.72070521871567528</v>
       </c>
       <c r="E12" s="0">
-        <v>-0.78042571162728258</v>
+        <v>0.70029597869491556</v>
       </c>
       <c r="F12" s="0">
-        <v>-0.57656320981038645</v>
+        <v>0.7317492246627807</v>
       </c>
       <c r="G12" s="0">
-        <v>-0.85356937950311851</v>
+        <v>0.69855269100952333</v>
       </c>
       <c r="H12" s="0">
-        <v>-0.63095638653898867</v>
+        <v>0.72956255838394934</v>
       </c>
       <c r="I12" s="0">
-        <v>-0.80108369879896879</v>
+        <v>0.71489924570083163</v>
       </c>
       <c r="J12" s="0">
-        <v>-1.057685307462775</v>
+        <v>0.67481142288207852</v>
       </c>
       <c r="K12" s="0">
-        <v>-0.38275798618410695</v>
+        <v>0.76333094232940579</v>
       </c>
       <c r="L12" s="0">
-        <v>-0.92478817343493791</v>
+        <v>0.71497616590500301</v>
       </c>
       <c r="M12" s="0">
-        <v>-0.8962061959031683</v>
+        <v>0.72354386811066029</v>
       </c>
       <c r="N12" s="0">
-        <v>-0.99057453191598277</v>
+        <v>0.72163807904815669</v>
       </c>
       <c r="O12" s="0">
-        <v>-1.0388830104129825</v>
+        <v>0.72446744004059282</v>
       </c>
       <c r="P12" s="0">
-        <v>-1.0760032383809497</v>
+        <v>0.72766441765976309</v>
       </c>
       <c r="Q12" s="0">
-        <v>-1.110904361232228</v>
+        <v>0.73155613655090879</v>
       </c>
       <c r="R12" s="0">
-        <v>-1.1904431818502008</v>
+        <v>0.73219745329285824</v>
       </c>
       <c r="S12" s="0">
-        <v>-1.2012853818442721</v>
+        <v>0.740680254707338</v>
       </c>
       <c r="T12" s="0">
-        <v>-1.0895205669289825</v>
+        <v>0.76010053996277305</v>
       </c>
       <c r="U12" s="0">
-        <v>-1.6356651404427305</v>
+        <v>0.74630784194564037</v>
       </c>
       <c r="V12" s="0">
-        <v>-1.4435975756611903</v>
+        <v>0.76286577828217073</v>
       </c>
       <c r="W12" s="0">
-        <v>-1.6563208386542194</v>
+        <v>0.76539158840180088</v>
       </c>
       <c r="X12" s="0">
-        <v>-1.8557161620681046</v>
+        <v>0.76678984045791965</v>
       </c>
       <c r="Y12" s="0">
-        <v>-2.1020877098636901</v>
+        <v>0.76667132695389006</v>
       </c>
       <c r="Z12" s="0">
-        <v>-2.2145040890172156</v>
+        <v>0.76789206555176337</v>
       </c>
       <c r="AA12" s="0">
-        <v>-1.9109312322286123</v>
+        <v>0.77768771522522073</v>
       </c>
       <c r="AB12" s="0">
-        <v>-2.0551493222670985</v>
+        <v>0.77648538532257338</v>
       </c>
       <c r="AC12" s="0">
-        <v>-2.0602927960921109</v>
+        <v>0.77753609069061014</v>
       </c>
       <c r="AD12" s="0">
-        <v>-2.0716536475618259</v>
+        <v>0.77980112265396728</v>
       </c>
       <c r="AE12" s="0">
-        <v>-2.0900437237286726</v>
+        <v>0.78284593831634808</v>
       </c>
       <c r="AF12" s="0">
-        <v>-2.0996671844222035</v>
+        <v>0.78573062996673559</v>
       </c>
       <c r="AG12" s="0">
-        <v>-2.0999668855959386</v>
+        <v>0.78844394880295254</v>
       </c>
       <c r="AH12" s="0">
-        <v>-2.091007657845815</v>
+        <v>0.79099187397766746</v>
       </c>
       <c r="AI12" s="0">
-        <v>-2.0730155228010565</v>
+        <v>0.79338080690384394</v>
       </c>
       <c r="AJ12" s="0">
-        <v>-2.0463088559445266</v>
+        <v>0.79561788497162222</v>
       </c>
       <c r="AK12" s="0">
-        <v>-2.0113777819888377</v>
+        <v>0.79770988022994826</v>
       </c>
       <c r="AL12" s="0">
-        <v>-1.9687578985016356</v>
+        <v>0.79966430732345151</v>
       </c>
       <c r="AM12" s="0">
-        <v>-1.9191017033215434</v>
+        <v>0.80148831555557609</v>
       </c>
       <c r="AN12" s="0">
-        <v>-1.8631131673222965</v>
+        <v>0.80318907938004114</v>
       </c>
       <c r="AO12" s="0">
-        <v>-1.8015324739616063</v>
+        <v>0.80477373883438008</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>492</v>
+        <v>524</v>
       </c>
       <c r="B13" s="0">
-        <v>-7.3135658288570538</v>
+        <v>-76.882820808601366</v>
       </c>
       <c r="C13" s="0">
-        <v>-0.38835007991020476</v>
+        <v>0.72224241028976555</v>
       </c>
       <c r="D13" s="0">
-        <v>-0.33635222706046775</v>
+        <v>0.73387544285965056</v>
       </c>
       <c r="E13" s="0">
-        <v>-0.45386145991429877</v>
+        <v>0.71005582625579511</v>
       </c>
       <c r="F13" s="0">
-        <v>-0.29808792889159907</v>
+        <v>0.74353412268066543</v>
       </c>
       <c r="G13" s="0">
-        <v>-0.51158817827195824</v>
+        <v>0.70289152000427157</v>
       </c>
       <c r="H13" s="0">
-        <v>-0.34419149143351208</v>
+        <v>0.73732177378082731</v>
       </c>
       <c r="I13" s="0">
-        <v>-0.46678328597039498</v>
+        <v>0.71852160488891903</v>
       </c>
       <c r="J13" s="0">
-        <v>-0.66113684570105191</v>
+        <v>0.67508928073883057</v>
       </c>
       <c r="K13" s="0">
-        <v>-0.18968572163327146</v>
+        <v>0.76847571133423342</v>
       </c>
       <c r="L13" s="0">
-        <v>-0.56674971099523241</v>
+        <v>0.71023368255234476</v>
       </c>
       <c r="M13" s="0">
-        <v>-0.53654040519990664</v>
+        <v>0.71841551828002914</v>
       </c>
       <c r="N13" s="0">
-        <v>-0.59120229849749562</v>
+        <v>0.71556329169464039</v>
       </c>
       <c r="O13" s="0">
-        <v>-0.61988873246244935</v>
+        <v>0.71663525171279763</v>
       </c>
       <c r="P13" s="0">
-        <v>-0.66612273503950237</v>
+        <v>0.71637303072357683</v>
       </c>
       <c r="Q13" s="0">
-        <v>-0.72141515684445512</v>
+        <v>0.71461088428497432</v>
       </c>
       <c r="R13" s="0">
-        <v>-0.79296423054312026</v>
+        <v>0.71177170938110668</v>
       </c>
       <c r="S13" s="0">
-        <v>-0.79265360903453319</v>
+        <v>0.71909188792038181</v>
       </c>
       <c r="T13" s="0">
-        <v>-0.73778552502898198</v>
+        <v>0.73843691950989054</v>
       </c>
       <c r="U13" s="0">
-        <v>-1.1654482681870215</v>
+        <v>0.71248700241851448</v>
       </c>
       <c r="V13" s="0">
-        <v>-1.1222032626180107</v>
+        <v>0.7280049434433048</v>
       </c>
       <c r="W13" s="0">
-        <v>-1.3484985498321906</v>
+        <v>0.72623696478271171</v>
       </c>
       <c r="X13" s="0">
-        <v>-1.6020300160622316</v>
+        <v>0.7228181403465237</v>
       </c>
       <c r="Y13" s="0">
-        <v>-1.8439348939121423</v>
+        <v>0.71816411456679696</v>
       </c>
       <c r="Z13" s="0">
-        <v>-2.0379565250556935</v>
+        <v>0.71597742578506363</v>
       </c>
       <c r="AA13" s="0">
-        <v>-2.0094916991798106</v>
+        <v>0.72595765879821472</v>
       </c>
       <c r="AB13" s="0">
-        <v>-2.2522204596128668</v>
+        <v>0.72296727632521829</v>
       </c>
       <c r="AC13" s="0">
-        <v>-2.2799465397031144</v>
+        <v>0.72471066328811928</v>
       </c>
       <c r="AD13" s="0">
-        <v>-2.3043503716303153</v>
+        <v>0.72652606217575222</v>
       </c>
       <c r="AE13" s="0">
-        <v>-2.4030726915519702</v>
+        <v>0.72808405039977842</v>
       </c>
       <c r="AF13" s="0">
-        <v>-2.5726802952650827</v>
+        <v>0.72921303144073346</v>
       </c>
       <c r="AG13" s="0">
-        <v>-2.7433311011958668</v>
+        <v>0.73054578152847471</v>
       </c>
       <c r="AH13" s="0">
-        <v>-2.912269859962425</v>
+        <v>0.73207202080917655</v>
       </c>
       <c r="AI13" s="0">
-        <v>-3.078361887808736</v>
+        <v>0.7337640799827585</v>
       </c>
       <c r="AJ13" s="0">
-        <v>-3.2405047294054419</v>
+        <v>0.73559591260529167</v>
       </c>
       <c r="AK13" s="0">
-        <v>-3.3976117042306626</v>
+        <v>0.73754401108932377</v>
       </c>
       <c r="AL13" s="0">
-        <v>-3.5486370595733296</v>
+        <v>0.73958701091766377</v>
       </c>
       <c r="AM13" s="0">
-        <v>-3.6926092504985188</v>
+        <v>0.74170536501312845</v>
       </c>
       <c r="AN13" s="0">
-        <v>-3.8286203807443311</v>
+        <v>0.74388173555374282</v>
       </c>
       <c r="AO13" s="0">
-        <v>-3.9558561372328453</v>
+        <v>0.74610026726150347</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
       <c r="B14" s="0">
-        <v>-7.5392328889964304</v>
+        <v>-76.943465989494314</v>
       </c>
       <c r="C14" s="0">
-        <v>-0.20801450143482741</v>
+        <v>0.74408145804977255</v>
       </c>
       <c r="D14" s="0">
-        <v>-0.15917055545865538</v>
+        <v>0.75770237952422936</v>
       </c>
       <c r="E14" s="0">
-        <v>-0.21945805273921204</v>
+        <v>0.74153980986022949</v>
       </c>
       <c r="F14" s="0">
-        <v>-0.13860586423112292</v>
+        <v>0.76331775165939453</v>
       </c>
       <c r="G14" s="0">
-        <v>-0.26465344532010188</v>
+        <v>0.73101484916687709</v>
       </c>
       <c r="H14" s="0">
-        <v>-0.14756162810258339</v>
+        <v>0.76199421187591487</v>
       </c>
       <c r="I14" s="0">
-        <v>-0.24212457983555324</v>
+        <v>0.73977634104537626</v>
       </c>
       <c r="J14" s="0">
-        <v>-0.34392642614458047</v>
+        <v>0.71046373101425009</v>
       </c>
       <c r="K14" s="0">
-        <v>-0.044124585195319081</v>
+        <v>0.78957616231918804</v>
       </c>
       <c r="L14" s="0">
-        <v>-0.29734887769914159</v>
+        <v>0.73045281146239671</v>
       </c>
       <c r="M14" s="0">
-        <v>-0.27544959270733571</v>
+        <v>0.73680087667083571</v>
       </c>
       <c r="N14" s="0">
-        <v>-0.29411022481962396</v>
+        <v>0.73544691561507547</v>
       </c>
       <c r="O14" s="0">
-        <v>-0.31837770166667684</v>
+        <v>0.7331551184387155</v>
       </c>
       <c r="P14" s="0">
-        <v>-0.35602046404599119</v>
+        <v>0.72817706811905336</v>
       </c>
       <c r="Q14" s="0">
-        <v>-0.39510143622012306</v>
+        <v>0.7238947650833174</v>
       </c>
       <c r="R14" s="0">
-        <v>-0.43668374418269523</v>
+        <v>0.71856406521225002</v>
       </c>
       <c r="S14" s="0">
-        <v>-0.45152065377813694</v>
+        <v>0.71989326248932106</v>
       </c>
       <c r="T14" s="0">
-        <v>-0.43699062235139252</v>
+        <v>0.73077358234786438</v>
       </c>
       <c r="U14" s="0">
-        <v>-0.66428533555778879</v>
+        <v>0.70531838355255183</v>
       </c>
       <c r="V14" s="0">
-        <v>-0.65988453458327123</v>
+        <v>0.71247929451370395</v>
       </c>
       <c r="W14" s="0">
-        <v>-0.82936503770999914</v>
+        <v>0.7012614933814918</v>
       </c>
       <c r="X14" s="0">
-        <v>-0.99949161605193571</v>
+        <v>0.69057005491638168</v>
       </c>
       <c r="Y14" s="0">
-        <v>-1.1622635436781341</v>
+        <v>0.67933346651077009</v>
       </c>
       <c r="Z14" s="0">
-        <v>-1.2367329842825383</v>
+        <v>0.67687329999543044</v>
       </c>
       <c r="AA14" s="0">
-        <v>-1.2430262393269012</v>
+        <v>0.6844231338577349</v>
       </c>
       <c r="AB14" s="0">
-        <v>-1.4274637431333324</v>
+        <v>0.67626940425110182</v>
       </c>
       <c r="AC14" s="0">
-        <v>-1.4957020407555444</v>
+        <v>0.67579252678299195</v>
       </c>
       <c r="AD14" s="0">
-        <v>-1.5302333474507734</v>
+        <v>0.67654944224166902</v>
       </c>
       <c r="AE14" s="0">
-        <v>-1.5654575337281822</v>
+        <v>0.6773192386245791</v>
       </c>
       <c r="AF14" s="0">
-        <v>-1.640160927565171</v>
+        <v>0.67692432465743613</v>
       </c>
       <c r="AG14" s="0">
-        <v>-1.743944634719206</v>
+        <v>0.67601637371063239</v>
       </c>
       <c r="AH14" s="0">
-        <v>-1.8505532714375577</v>
+        <v>0.67536176437378415</v>
       </c>
       <c r="AI14" s="0">
-        <v>-1.959394956060635</v>
+        <v>0.6749547173728907</v>
       </c>
       <c r="AJ14" s="0">
-        <v>-2.0703093553434537</v>
+        <v>0.67478109162139532</v>
       </c>
       <c r="AK14" s="0">
-        <v>-2.1831181832978621</v>
+        <v>0.67482694591141068</v>
       </c>
       <c r="AL14" s="0">
-        <v>-2.2976348304532666</v>
+        <v>0.67507834830093616</v>
       </c>
       <c r="AM14" s="0">
-        <v>-2.4136597923635725</v>
+        <v>0.67552170042037951</v>
       </c>
       <c r="AN14" s="0">
-        <v>-2.5309814377057998</v>
+        <v>0.67614380233384053</v>
       </c>
       <c r="AO14" s="0">
-        <v>-2.6493836474281607</v>
+        <v>0.67693165663147725</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
       <c r="B15" s="0">
-        <v>-7.6651419814735116</v>
+        <v>-76.982874787330616</v>
       </c>
       <c r="C15" s="0">
-        <v>-0.095002581644028194</v>
+        <v>0.76894716427994414</v>
       </c>
       <c r="D15" s="0">
-        <v>-0.053349547579485838</v>
+        <v>0.78178810747147109</v>
       </c>
       <c r="E15" s="0">
-        <v>-0.096067893261691184</v>
+        <v>0.76848764184189067</v>
       </c>
       <c r="F15" s="0">
-        <v>-0.049535955581193142</v>
+        <v>0.78315924882888732</v>
       </c>
       <c r="G15" s="0">
-        <v>-0.10405498781324446</v>
+        <v>0.76623891124344279</v>
       </c>
       <c r="H15" s="0">
-        <v>-0.04591340010202246</v>
+        <v>0.7844206951713556</v>
       </c>
       <c r="I15" s="0">
-        <v>-0.097474328921851205</v>
+        <v>0.76925235389328472</v>
       </c>
       <c r="J15" s="0">
-        <v>-0.14179817889328869</v>
+        <v>0.75442592695998978</v>
       </c>
       <c r="K15" s="0">
-        <v>0.012014179018862729</v>
+        <v>0.80266376773070403</v>
       </c>
       <c r="L15" s="0">
-        <v>-0.14025306646385022</v>
+        <v>0.75778177901840249</v>
       </c>
       <c r="M15" s="0">
-        <v>-0.1139791269513839</v>
+        <v>0.76560103082656439</v>
       </c>
       <c r="N15" s="0">
-        <v>-0.12643289839371444</v>
+        <v>0.76279238176727404</v>
       </c>
       <c r="O15" s="0">
-        <v>-0.14219030808087033</v>
+        <v>0.75963723306655451</v>
       </c>
       <c r="P15" s="0">
-        <v>-0.16666450578192124</v>
+        <v>0.75399151908111728</v>
       </c>
       <c r="Q15" s="0">
-        <v>-0.18248228467051084</v>
+        <v>0.75081675844193141</v>
       </c>
       <c r="R15" s="0">
-        <v>-0.21273895507109283</v>
+        <v>0.74389959623717894</v>
       </c>
       <c r="S15" s="0">
-        <v>-0.21782284372899396</v>
+        <v>0.74378573289108496</v>
       </c>
       <c r="T15" s="0">
-        <v>-0.20558249863874228</v>
+        <v>0.750211381477355</v>
       </c>
       <c r="U15" s="0">
-        <v>-0.31185734960943734</v>
+        <v>0.72908481918716384</v>
       </c>
       <c r="V15" s="0">
-        <v>-0.25727868606953824</v>
+        <v>0.74741534992598568</v>
       </c>
       <c r="W15" s="0">
-        <v>-0.39546891464508538</v>
+        <v>0.71881100540923526</v>
       </c>
       <c r="X15" s="0">
-        <v>-0.47364427531405723</v>
+        <v>0.70683791035080923</v>
       </c>
       <c r="Y15" s="0">
-        <v>-0.54957011559392854</v>
+        <v>0.6939473575324977</v>
       </c>
       <c r="Z15" s="0">
-        <v>-0.54966247667542567</v>
+        <v>0.6966943923301735</v>
       </c>
       <c r="AA15" s="0">
-        <v>-0.53635671394273043</v>
+        <v>0.70341508966446198</v>
       </c>
       <c r="AB15" s="0">
-        <v>-0.60699109015676</v>
+        <v>0.69584896370314631</v>
       </c>
       <c r="AC15" s="0">
-        <v>-0.63068269037124469</v>
+        <v>0.69556302598189601</v>
       </c>
       <c r="AD15" s="0">
-        <v>-0.65020171014072681</v>
+        <v>0.69556763775253294</v>
       </c>
       <c r="AE15" s="0">
-        <v>-0.6646581484952353</v>
+        <v>0.69567024567794755</v>
       </c>
       <c r="AF15" s="0">
-        <v>-0.67923842680965263</v>
+        <v>0.69581692486954272</v>
       </c>
       <c r="AG15" s="0">
-        <v>-0.69985672793717779</v>
+        <v>0.6959155166893064</v>
       </c>
       <c r="AH15" s="0">
-        <v>-0.72475369651513255</v>
+        <v>0.69618031889343468</v>
       </c>
       <c r="AI15" s="0">
-        <v>-0.749995595031828</v>
+        <v>0.69657586691283946</v>
       </c>
       <c r="AJ15" s="0">
-        <v>-0.77549690848895125</v>
+        <v>0.6970929676513643</v>
       </c>
       <c r="AK15" s="0">
-        <v>-0.80125310102822767</v>
+        <v>0.69772420838928551</v>
       </c>
       <c r="AL15" s="0">
-        <v>-0.82725533773756543</v>
+        <v>0.69846277736664153</v>
       </c>
       <c r="AM15" s="0">
-        <v>-0.85349403031739135</v>
+        <v>0.69930193827438636</v>
       </c>
       <c r="AN15" s="0">
-        <v>-0.87995992428094505</v>
+        <v>0.70023489788437343</v>
       </c>
       <c r="AO15" s="0">
-        <v>-0.90664287529725374</v>
+        <v>0.70125507078933835</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="B16" s="0">
-        <v>-7.7195868772964538</v>
+        <v>-77.001393018722524</v>
       </c>
       <c r="C16" s="0">
-        <v>-0.019705552145279449</v>
+        <v>0.79103609746932957</v>
       </c>
       <c r="D16" s="0">
-        <v>-0.0010773772196410183</v>
+        <v>0.79733155884169804</v>
       </c>
       <c r="E16" s="0">
-        <v>-0.017943814370821345</v>
+        <v>0.7915762014656087</v>
       </c>
       <c r="F16" s="0">
-        <v>0.0051628227904002844</v>
+        <v>0.79946779082870401</v>
       </c>
       <c r="G16" s="0">
-        <v>-0.025271801829531846</v>
+        <v>0.78914992431640618</v>
       </c>
       <c r="H16" s="0">
-        <v>0.005021502360974559</v>
+        <v>0.79944872293090097</v>
       </c>
       <c r="I16" s="0">
-        <v>-0.019362299525767988</v>
+        <v>0.79134771761704636</v>
       </c>
       <c r="J16" s="0">
-        <v>-0.041494648580837921</v>
+        <v>0.78359696860504202</v>
       </c>
       <c r="K16" s="0">
-        <v>0.033856629959637133</v>
+        <v>0.80931289922714733</v>
       </c>
       <c r="L16" s="0">
-        <v>-0.042189577795273769</v>
+        <v>0.78402751657486824</v>
       </c>
       <c r="M16" s="0">
-        <v>-0.025044630711771119</v>
+        <v>0.78966282495498974</v>
       </c>
       <c r="N16" s="0">
-        <v>-0.031204223911179274</v>
+        <v>0.78780667993546627</v>
       </c>
       <c r="O16" s="0">
-        <v>-0.03455354853112378</v>
+        <v>0.78698453783798106</v>
       </c>
       <c r="P16" s="0">
-        <v>-0.051729131108967152</v>
+        <v>0.78174415930938812</v>
       </c>
       <c r="Q16" s="0">
-        <v>-0.059851294696622225</v>
+        <v>0.77940266514205703</v>
       </c>
       <c r="R16" s="0">
-        <v>-0.072825298869628574</v>
+        <v>0.77551693202209582</v>
       </c>
       <c r="S16" s="0">
-        <v>-0.076383092205673658</v>
+        <v>0.77460273983002459</v>
       </c>
       <c r="T16" s="0">
-        <v>-0.035288914676088641</v>
+        <v>0.78851262103271602</v>
       </c>
       <c r="U16" s="0">
-        <v>-0.058121009369750891</v>
+        <v>0.7829552441635097</v>
       </c>
       <c r="V16" s="0">
-        <v>-0.03547539787448855</v>
+        <v>0.79036549121856514</v>
       </c>
       <c r="W16" s="0">
-        <v>-0.0086619765977891585</v>
+        <v>0.79966387712097964</v>
       </c>
       <c r="X16" s="0">
-        <v>-0.1089626598137438</v>
+        <v>0.77120026044083612</v>
       </c>
       <c r="Y16" s="0">
-        <v>-0.048407153514077435</v>
+        <v>0.788810355567925</v>
       </c>
       <c r="Z16" s="0">
-        <v>-0.092219337583150388</v>
+        <v>0.77657404806900432</v>
       </c>
       <c r="AA16" s="0">
-        <v>-0.13953848739772665</v>
+        <v>0.76423721747208084</v>
       </c>
       <c r="AB16" s="0">
-        <v>-0.16955201176406162</v>
+        <v>0.75813586081313855</v>
       </c>
       <c r="AC16" s="0">
-        <v>-0.1783134167691906</v>
+        <v>0.75730757277680294</v>
       </c>
       <c r="AD16" s="0">
-        <v>-0.18711320309296564</v>
+        <v>0.75658478892135528</v>
       </c>
       <c r="AE16" s="0">
-        <v>-0.19503330765274401</v>
+        <v>0.75595483349609605</v>
       </c>
       <c r="AF16" s="0">
-        <v>-0.20100221661378287</v>
+        <v>0.75552810837173368</v>
       </c>
       <c r="AG16" s="0">
-        <v>-0.20684319477129878</v>
+        <v>0.75517852053833279</v>
       </c>
       <c r="AH16" s="0">
-        <v>-0.21409897766554567</v>
+        <v>0.75488753952026955</v>
       </c>
       <c r="AI16" s="0">
-        <v>-0.22307816109667822</v>
+        <v>0.75457509735489225</v>
       </c>
       <c r="AJ16" s="0">
-        <v>-0.23213662291508433</v>
+        <v>0.75435574571227226</v>
       </c>
       <c r="AK16" s="0">
-        <v>-0.24122945107861379</v>
+        <v>0.75423004848862518</v>
       </c>
       <c r="AL16" s="0">
-        <v>-0.25035457866931821</v>
+        <v>0.75419441713332869</v>
       </c>
       <c r="AM16" s="0">
-        <v>-0.25951019448530527</v>
+        <v>0.75424508174896521</v>
       </c>
       <c r="AN16" s="0">
-        <v>-0.26869617769831949</v>
+        <v>0.75437775354767334</v>
       </c>
       <c r="AO16" s="0">
-        <v>-0.27790986255253863</v>
+        <v>0.75458854879379</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>496</v>
+        <v>528</v>
       </c>
       <c r="B17" s="0">
-        <v>11.112193565071852</v>
+        <v>-76.400194974899279</v>
       </c>
       <c r="C17" s="0">
-        <v>11.192131316424655</v>
+        <v>-76.399374545669559</v>
       </c>
       <c r="D17" s="0">
-        <v>9.3741302829065187</v>
+        <v>-76.421165426635739</v>
       </c>
       <c r="E17" s="0">
-        <v>5.9653175970610288</v>
+        <v>-76.492772894859314</v>
       </c>
       <c r="F17" s="0">
-        <v>11.786564867301285</v>
+        <v>-76.393595933532708</v>
       </c>
       <c r="G17" s="0">
-        <v>12.045674476136387</v>
+        <v>-76.391242130279537</v>
       </c>
       <c r="H17" s="0">
-        <v>12.40869508713142</v>
+        <v>-76.388097614860527</v>
       </c>
       <c r="I17" s="0">
-        <v>12.649210645582901</v>
+        <v>-76.386106505393968</v>
       </c>
       <c r="J17" s="0">
-        <v>9.2587922090337447</v>
+        <v>-76.422808932495116</v>
       </c>
       <c r="K17" s="0">
-        <v>13.084488028157285</v>
+        <v>-76.382676203155512</v>
       </c>
       <c r="L17" s="0">
-        <v>14.806803497696549</v>
+        <v>-76.370958149337753</v>
       </c>
       <c r="M17" s="0">
-        <v>15.050532947514396</v>
+        <v>-76.369503270721424</v>
       </c>
       <c r="N17" s="0">
-        <v>15.221950068945205</v>
+        <v>-76.368506259918206</v>
       </c>
       <c r="O17" s="0">
-        <v>15.311307936202594</v>
+        <v>-76.367994848442066</v>
       </c>
       <c r="P17" s="0">
-        <v>15.363147859849482</v>
+        <v>-76.367700722312918</v>
       </c>
       <c r="Q17" s="0">
-        <v>15.492122013946597</v>
+        <v>-76.366976989364616</v>
       </c>
       <c r="R17" s="0">
-        <v>15.461342946950905</v>
+        <v>-76.367148673248295</v>
       </c>
       <c r="S17" s="0">
-        <v>15.463937041784851</v>
+        <v>-76.367134178733821</v>
       </c>
       <c r="T17" s="0">
-        <v>15.348568149138677</v>
+        <v>-76.367783255004881</v>
       </c>
       <c r="U17" s="0">
-        <v>15.629019768404772</v>
+        <v>-76.366221090507509</v>
       </c>
       <c r="V17" s="0">
-        <v>15.237848447951757</v>
+        <v>-76.36841485843658</v>
       </c>
       <c r="W17" s="0">
-        <v>15.476172295196472</v>
+        <v>-76.367065875816337</v>
       </c>
       <c r="X17" s="0">
-        <v>15.586813812146698</v>
+        <v>-76.36645280418395</v>
       </c>
       <c r="Y17" s="0">
-        <v>15.683950935019105</v>
+        <v>-76.365921272468569</v>
       </c>
       <c r="Z17" s="0">
-        <v>15.734581825888496</v>
+        <v>-76.365646670913691</v>
       </c>
       <c r="AA17" s="0">
-        <v>15.820816236134835</v>
+        <v>-76.365182780265798</v>
       </c>
       <c r="AB17" s="0">
-        <v>15.904659400955953</v>
+        <v>-76.36473629627227</v>
       </c>
       <c r="AC17" s="0">
-        <v>15.981689006562448</v>
+        <v>-76.364329986572258</v>
       </c>
       <c r="AD17" s="0">
-        <v>16.052329513874906</v>
+        <v>-76.363960608100882</v>
       </c>
       <c r="AE17" s="0">
-        <v>16.11711657206499</v>
+        <v>-76.363624520683288</v>
       </c>
       <c r="AF17" s="0">
-        <v>16.17646418145705</v>
+        <v>-76.363318878364566</v>
       </c>
       <c r="AG17" s="0">
-        <v>16.230811793332485</v>
+        <v>-76.363040835189821</v>
       </c>
       <c r="AH17" s="0">
-        <v>16.280569391892218</v>
+        <v>-76.362787809944138</v>
       </c>
       <c r="AI17" s="0">
-        <v>16.326113536629499</v>
+        <v>-76.362557486152639</v>
       </c>
       <c r="AJ17" s="0">
-        <v>16.367744351978008</v>
+        <v>-76.362348010635372</v>
       </c>
       <c r="AK17" s="0">
-        <v>16.405827337928233</v>
+        <v>-76.362157265472405</v>
       </c>
       <c r="AL17" s="0">
-        <v>16.440646804137184</v>
+        <v>-76.361983596038812</v>
       </c>
       <c r="AM17" s="0">
-        <v>16.472496115176465</v>
+        <v>-76.36182534770964</v>
       </c>
       <c r="AN17" s="0">
-        <v>16.501569518505619</v>
+        <v>-76.361681395339957</v>
       </c>
       <c r="AO17" s="0">
-        <v>16.528147556025992</v>
+        <v>-76.3615502166748</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="B18" s="0">
-        <v>1.8080897133163241</v>
+        <v>-76.405404925537113</v>
       </c>
       <c r="C18" s="0">
-        <v>-0.17641720644900249</v>
+        <v>0.81952014148712626</v>
       </c>
       <c r="D18" s="0">
-        <v>-1.4092304865141752</v>
+        <v>0.8045146073608419</v>
       </c>
       <c r="E18" s="0">
-        <v>-2.7161931911706452</v>
+        <v>0.76618112776947978</v>
       </c>
       <c r="F18" s="0">
-        <v>5.659418997783435</v>
+        <v>0.91846687829970797</v>
       </c>
       <c r="G18" s="0">
-        <v>0.11253115350294371</v>
+        <v>0.82278955593872305</v>
       </c>
       <c r="H18" s="0">
-        <v>0.11711006795277727</v>
+        <v>0.82288415283202898</v>
       </c>
       <c r="I18" s="0">
-        <v>-0.11927970972210683</v>
+        <v>0.82087915907668829</v>
       </c>
       <c r="J18" s="0">
-        <v>-2.3399151587128708</v>
+        <v>0.79799368944168425</v>
       </c>
       <c r="K18" s="0">
-        <v>4.2823506434824274</v>
+        <v>0.8655662647399901</v>
       </c>
       <c r="L18" s="0">
-        <v>1.4932616007698876</v>
+        <v>0.83286779437256186</v>
       </c>
       <c r="M18" s="0">
-        <v>0.12212036033834474</v>
+        <v>0.82339268393706821</v>
       </c>
       <c r="N18" s="0">
-        <v>0.0331841273624583</v>
+        <v>0.82288945557404169</v>
       </c>
       <c r="O18" s="0">
-        <v>-0.061669466107211017</v>
+        <v>0.82235608921051107</v>
       </c>
       <c r="P18" s="0">
-        <v>-0.00030916580828198699</v>
+        <v>0.82274588840103224</v>
       </c>
       <c r="Q18" s="0">
-        <v>0.110785215026576</v>
+        <v>0.82340753187942195</v>
       </c>
       <c r="R18" s="0">
-        <v>0.023066121834111133</v>
+        <v>0.82292237599181539</v>
       </c>
       <c r="S18" s="0">
-        <v>0.035113772923830694</v>
+        <v>0.82298578916168574</v>
       </c>
       <c r="T18" s="0">
-        <v>-0.065125399762318889</v>
+        <v>0.82240212881851271</v>
       </c>
       <c r="U18" s="0">
-        <v>0.31107318951208762</v>
+        <v>0.82455644122314453</v>
       </c>
       <c r="V18" s="0">
-        <v>-0.47425292421577658</v>
+        <v>0.82003409049605502</v>
       </c>
       <c r="W18" s="0">
-        <v>0.198104828541879</v>
+        <v>0.82390088808822659</v>
       </c>
       <c r="X18" s="0">
-        <v>0.17292666609283289</v>
+        <v>0.82377901768111539</v>
       </c>
       <c r="Y18" s="0">
-        <v>0.11945129230175003</v>
+        <v>0.82348960789490955</v>
       </c>
       <c r="Z18" s="0">
-        <v>0.077930381427799636</v>
+        <v>0.82327084132766681</v>
       </c>
       <c r="AA18" s="0">
-        <v>0.14669737276753156</v>
+        <v>0.82366119911956281</v>
       </c>
       <c r="AB18" s="0">
-        <v>0.16645176487624955</v>
+        <v>0.82377961599350324</v>
       </c>
       <c r="AC18" s="0">
-        <v>0.18033063957084611</v>
+        <v>0.82386359946059906</v>
       </c>
       <c r="AD18" s="0">
-        <v>0.19325152662394576</v>
+        <v>0.82394022712707748</v>
       </c>
       <c r="AE18" s="0">
-        <v>0.20533872379463217</v>
+        <v>0.82401055662917477</v>
       </c>
       <c r="AF18" s="0">
-        <v>0.21656676532797584</v>
+        <v>0.82407479314040721</v>
       </c>
       <c r="AG18" s="0">
-        <v>0.22704387028225659</v>
+        <v>0.82413378779983471</v>
       </c>
       <c r="AH18" s="0">
-        <v>0.2367474399796187</v>
+        <v>0.82418766371155172</v>
       </c>
       <c r="AI18" s="0">
-        <v>0.24576288834726442</v>
+        <v>0.82423706816482523</v>
       </c>
       <c r="AJ18" s="0">
-        <v>0.25406559121927891</v>
+        <v>0.82428204748916789</v>
       </c>
       <c r="AK18" s="0">
-        <v>0.26184254046370886</v>
+        <v>0.82432369770813518</v>
       </c>
       <c r="AL18" s="0">
-        <v>0.26898694622547831</v>
+        <v>0.82436159788513708</v>
       </c>
       <c r="AM18" s="0">
-        <v>0.27557640986223036</v>
+        <v>0.82439624440764825</v>
       </c>
       <c r="AN18" s="0">
-        <v>0.2816660475527657</v>
+        <v>0.82442800129318083</v>
       </c>
       <c r="AO18" s="0">
-        <v>0.28731268799349641</v>
+        <v>0.82445722196960392</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="B19" s="0">
-        <v>1.4759070774031562</v>
+        <v>-76.409238691520684</v>
       </c>
       <c r="C19" s="0">
-        <v>-0.061042806539168694</v>
+        <v>0.82051964349365925</v>
       </c>
       <c r="D19" s="0">
-        <v>-0.53525229574625521</v>
+        <v>0.81478470021819505</v>
       </c>
       <c r="E19" s="0">
-        <v>-1.2628558744292957</v>
+        <v>0.80023548649978571</v>
       </c>
       <c r="F19" s="0">
-        <v>4.8266548553042394</v>
+        <v>0.9009670751762322</v>
       </c>
       <c r="G19" s="0">
-        <v>-0.069930286490449328</v>
+        <v>0.82088596818924386</v>
       </c>
       <c r="H19" s="0">
-        <v>0.032662151353418559</v>
+        <v>0.82198067731475244</v>
       </c>
       <c r="I19" s="0">
-        <v>-0.20202090004922035</v>
+        <v>0.81981024886321885</v>
       </c>
       <c r="J19" s="0">
-        <v>-1.4123176836212834</v>
+        <v>0.80701995440292917</v>
       </c>
       <c r="K19" s="0">
-        <v>3.1647561285986203</v>
+        <v>0.85267152241135025</v>
       </c>
       <c r="L19" s="0">
-        <v>0.67031942607997042</v>
+        <v>0.82714054444123097</v>
       </c>
       <c r="M19" s="0">
-        <v>0.055437777754306097</v>
+        <v>0.82287107997131714</v>
       </c>
       <c r="N19" s="0">
-        <v>-0.096435125335435898</v>
+        <v>0.82195216481781352</v>
       </c>
       <c r="O19" s="0">
-        <v>-0.2578888235165826</v>
+        <v>0.82095275679398128</v>
       </c>
       <c r="P19" s="0">
-        <v>-0.23130531910554503</v>
+        <v>0.82115872980118054</v>
       </c>
       <c r="Q19" s="0">
-        <v>-0.15190634856914814</v>
+        <v>0.8217245612297055</v>
       </c>
       <c r="R19" s="0">
-        <v>-0.14607546255743128</v>
+        <v>0.82181788472365747</v>
       </c>
       <c r="S19" s="0">
-        <v>-0.10197345280352471</v>
+        <v>0.8221008732414351</v>
       </c>
       <c r="T19" s="0">
-        <v>-0.10566204930256297</v>
+        <v>0.82207269961165985</v>
       </c>
       <c r="U19" s="0">
-        <v>0.18476752341085512</v>
+        <v>0.82380647651291672</v>
       </c>
       <c r="V19" s="0">
-        <v>-0.6233564629570415</v>
+        <v>0.81891876606750758</v>
       </c>
       <c r="W19" s="0">
-        <v>0.21424981328727222</v>
+        <v>0.82396292593383502</v>
       </c>
       <c r="X19" s="0">
-        <v>0.17397361017271415</v>
+        <v>0.82374648907852632</v>
       </c>
       <c r="Y19" s="0">
-        <v>0.1378621691345423</v>
+        <v>0.82355889829253959</v>
       </c>
       <c r="Z19" s="0">
-        <v>0.17331479172484701</v>
+        <v>0.82377056453322395</v>
       </c>
       <c r="AA19" s="0">
-        <v>0.24781082473548308</v>
+        <v>0.82420025739288039</v>
       </c>
       <c r="AB19" s="0">
-        <v>0.24940867714481083</v>
+        <v>0.82421563084411531</v>
       </c>
       <c r="AC19" s="0">
-        <v>0.25591897527739477</v>
+        <v>0.82425713942718548</v>
       </c>
       <c r="AD19" s="0">
-        <v>0.26210467643192814</v>
+        <v>0.82429563262176331</v>
       </c>
       <c r="AE19" s="0">
-        <v>0.2679469432480524</v>
+        <v>0.824331205734254</v>
       </c>
       <c r="AF19" s="0">
-        <v>0.27346636451016004</v>
+        <v>0.82436414203643504</v>
       </c>
       <c r="AG19" s="0">
-        <v>0.27867440215960743</v>
+        <v>0.82439464934921702</v>
       </c>
       <c r="AH19" s="0">
-        <v>0.28354784860638388</v>
+        <v>0.82442273429108393</v>
       </c>
       <c r="AI19" s="0">
-        <v>0.28817828398265077</v>
+        <v>0.82444898458481275</v>
       </c>
       <c r="AJ19" s="0">
-        <v>0.29249636153636471</v>
+        <v>0.82447313284302104</v>
       </c>
       <c r="AK19" s="0">
-        <v>0.29659829181079878</v>
+        <v>0.82449575487518478</v>
       </c>
       <c r="AL19" s="0">
-        <v>0.30037835752611131</v>
+        <v>0.8245163794441196</v>
       </c>
       <c r="AM19" s="0">
-        <v>0.30397439802555909</v>
+        <v>0.82453576767731418</v>
       </c>
       <c r="AN19" s="0">
-        <v>0.30734610280176605</v>
+        <v>0.8245537633781469</v>
       </c>
       <c r="AO19" s="0">
-        <v>0.31047939408730996</v>
+        <v>0.82457034007263363</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="B20" s="0">
-        <v>0.9967027992220765</v>
+        <v>-76.415184884071351</v>
       </c>
       <c r="C20" s="0">
-        <v>-0.33268893129687355</v>
+        <v>0.81683767280197583</v>
       </c>
       <c r="D20" s="0">
-        <v>-0.23807926234453178</v>
+        <v>0.8181105731201147</v>
       </c>
       <c r="E20" s="0">
-        <v>-0.67123854056298904</v>
+        <v>0.81142405901336923</v>
       </c>
       <c r="F20" s="0">
-        <v>2.7363870963110526</v>
+        <v>0.85993745307922365</v>
       </c>
       <c r="G20" s="0">
-        <v>-0.36944242317039144</v>
+        <v>0.81736297783279499</v>
       </c>
       <c r="H20" s="0">
-        <v>-0.19444488220181913</v>
+        <v>0.81936176343536227</v>
       </c>
       <c r="I20" s="0">
-        <v>-0.42073654653237685</v>
+        <v>0.8171179450874303</v>
       </c>
       <c r="J20" s="0">
-        <v>-1.1931065800411071</v>
+        <v>0.80809873412322597</v>
       </c>
       <c r="K20" s="0">
-        <v>2.0872157091429733</v>
+        <v>0.84263729700087464</v>
       </c>
       <c r="L20" s="0">
-        <v>-0.016878305568161785</v>
+        <v>0.82198596946716085</v>
       </c>
       <c r="M20" s="0">
-        <v>-0.32828763336139422</v>
+        <v>0.81989698694992286</v>
       </c>
       <c r="N20" s="0">
-        <v>-0.40678862229821355</v>
+        <v>0.81951799312210616</v>
       </c>
       <c r="O20" s="0">
-        <v>-0.60204693275768395</v>
+        <v>0.81819463336182197</v>
       </c>
       <c r="P20" s="0">
-        <v>-0.54310629283149059</v>
+        <v>0.81861816439819002</v>
       </c>
       <c r="Q20" s="0">
-        <v>-0.53699420875888926</v>
+        <v>0.8187387958221416</v>
       </c>
       <c r="R20" s="0">
-        <v>-0.41055376271705057</v>
+        <v>0.81979013391875877</v>
       </c>
       <c r="S20" s="0">
-        <v>-0.36115640960367978</v>
+        <v>0.82022354637527251</v>
       </c>
       <c r="T20" s="0">
-        <v>-0.27952375552209541</v>
+        <v>0.82080927566146888</v>
       </c>
       <c r="U20" s="0">
-        <v>-0.18778579673378121</v>
+        <v>0.82140113103103651</v>
       </c>
       <c r="V20" s="0">
-        <v>-1.0992927488656019</v>
+        <v>0.81531325493240703</v>
       </c>
       <c r="W20" s="0">
-        <v>-0.092037018626554112</v>
+        <v>0.82190432894897958</v>
       </c>
       <c r="X20" s="0">
-        <v>-0.072127343139922806</v>
+        <v>0.82214440708542402</v>
       </c>
       <c r="Y20" s="0">
-        <v>-0.083298444566019203</v>
+        <v>0.82214785135269242</v>
       </c>
       <c r="Z20" s="0">
-        <v>-0.073963037184025679</v>
+        <v>0.82225571436691669</v>
       </c>
       <c r="AA20" s="0">
-        <v>0.024195760801015549</v>
+        <v>0.82287164386749256</v>
       </c>
       <c r="AB20" s="0">
-        <v>0.046924993241142576</v>
+        <v>0.8230322298507714</v>
       </c>
       <c r="AC20" s="0">
-        <v>0.068374453855855222</v>
+        <v>0.82317889183426396</v>
       </c>
       <c r="AD20" s="0">
-        <v>0.088612637446316048</v>
+        <v>0.82331313089370839</v>
       </c>
       <c r="AE20" s="0">
-        <v>0.10765506906251607</v>
+        <v>0.82343597554398162</v>
       </c>
       <c r="AF20" s="0">
-        <v>0.12552790980116585</v>
+        <v>0.82354838149643383</v>
       </c>
       <c r="AG20" s="0">
-        <v>0.14226545839271074</v>
+        <v>0.82365123165893617</v>
       </c>
       <c r="AH20" s="0">
-        <v>0.15790774298275367</v>
+        <v>0.82374533216476398</v>
       </c>
       <c r="AI20" s="0">
-        <v>0.17252265032508263</v>
+        <v>0.82383154871367914</v>
       </c>
       <c r="AJ20" s="0">
-        <v>0.18610492653657457</v>
+        <v>0.82391028106307884</v>
       </c>
       <c r="AK20" s="0">
-        <v>0.19875990870409674</v>
+        <v>0.82398244653701747</v>
       </c>
       <c r="AL20" s="0">
-        <v>0.21050323308800814</v>
+        <v>0.82404843297958641</v>
       </c>
       <c r="AM20" s="0">
-        <v>0.22142187399731039</v>
+        <v>0.824108949893957</v>
       </c>
       <c r="AN20" s="0">
-        <v>0.23153399519294438</v>
+        <v>0.82416430967330934</v>
       </c>
       <c r="AO20" s="0">
-        <v>0.24090169606145803</v>
+        <v>0.82421501399993768</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>500</v>
+        <v>532</v>
       </c>
       <c r="B21" s="0">
-        <v>0.4339672446899997</v>
+        <v>-76.422878492927538</v>
       </c>
       <c r="C21" s="0">
-        <v>-0.51909252526170202</v>
+        <v>0.81347508840560989</v>
       </c>
       <c r="D21" s="0">
-        <v>-0.18981695315642805</v>
+        <v>0.81815213994598679</v>
       </c>
       <c r="E21" s="0">
-        <v>-0.63225793572733202</v>
+        <v>0.81188788347625274</v>
       </c>
       <c r="F21" s="0">
-        <v>1.0123433027201632</v>
+        <v>0.83478909190368589</v>
       </c>
       <c r="G21" s="0">
-        <v>-0.63423335332623065</v>
+        <v>0.81338359426498474</v>
       </c>
       <c r="H21" s="0">
-        <v>-0.41820577622868255</v>
+        <v>0.81601720783234022</v>
       </c>
       <c r="I21" s="0">
-        <v>-0.63784240970629424</v>
+        <v>0.81353319486236397</v>
       </c>
       <c r="J21" s="0">
-        <v>-1.0198496352117512</v>
+        <v>0.80851102032852551</v>
       </c>
       <c r="K21" s="0">
-        <v>1.4123746724955004</v>
+        <v>0.83722178767394773</v>
       </c>
       <c r="L21" s="0">
-        <v>-0.53254318135985568</v>
+        <v>0.81684499683380452</v>
       </c>
       <c r="M21" s="0">
-        <v>-0.59157391086699851</v>
+        <v>0.81681424066542629</v>
       </c>
       <c r="N21" s="0">
-        <v>-0.65832398056328001</v>
+        <v>0.81667214677047795</v>
       </c>
       <c r="O21" s="0">
-        <v>-0.88541104733055076</v>
+        <v>0.81498176340103023</v>
       </c>
       <c r="P21" s="0">
-        <v>-0.6939820782278685</v>
+        <v>0.81658667678833208</v>
       </c>
       <c r="Q21" s="0">
-        <v>-0.73870811497523325</v>
+        <v>0.81625527262115449</v>
       </c>
       <c r="R21" s="0">
-        <v>-0.56093816176293754</v>
+        <v>0.81784862481308374</v>
       </c>
       <c r="S21" s="0">
-        <v>-0.48642421880772324</v>
+        <v>0.81873536082077658</v>
       </c>
       <c r="T21" s="0">
-        <v>-0.30200699565668121</v>
+        <v>0.82026067880630837</v>
       </c>
       <c r="U21" s="0">
-        <v>-0.34800597639611142</v>
+        <v>0.82002101234054425</v>
       </c>
       <c r="V21" s="0">
-        <v>-1.3619182524487807</v>
+        <v>0.81230186137009808</v>
       </c>
       <c r="W21" s="0">
-        <v>-0.30561774832394811</v>
+        <v>0.81994579970932391</v>
       </c>
       <c r="X21" s="0">
-        <v>-0.28999743835139696</v>
+        <v>0.82033727602767748</v>
       </c>
       <c r="Y21" s="0">
-        <v>-0.32341554635896014</v>
+        <v>0.82029201607895408</v>
       </c>
       <c r="Z21" s="0">
-        <v>-0.35112713966673231</v>
+        <v>0.82022644130707179</v>
       </c>
       <c r="AA21" s="0">
-        <v>-0.27960539926632105</v>
+        <v>0.82079684611892778</v>
       </c>
       <c r="AB21" s="0">
-        <v>-0.26460034118039627</v>
+        <v>0.82098138180541724</v>
       </c>
       <c r="AC21" s="0">
-        <v>-0.22452107563613902</v>
+        <v>0.82130002682877501</v>
       </c>
       <c r="AD21" s="0">
-        <v>-0.186184598678931</v>
+        <v>0.82159198606109585</v>
       </c>
       <c r="AE21" s="0">
-        <v>-0.14968916405832164</v>
+        <v>0.82185925167083451</v>
       </c>
       <c r="AF21" s="0">
-        <v>-0.11505607175565304</v>
+        <v>0.82210392966461465</v>
       </c>
       <c r="AG21" s="0">
-        <v>-0.082302451436026394</v>
+        <v>0.82232785336684766</v>
       </c>
       <c r="AH21" s="0">
-        <v>-0.051424536365789045</v>
+        <v>0.82253271578978904</v>
       </c>
       <c r="AI21" s="0">
-        <v>-0.02236610746101712</v>
+        <v>0.8227202642173701</v>
       </c>
       <c r="AJ21" s="0">
-        <v>0.0048943088425406865</v>
+        <v>0.82289184352874112</v>
       </c>
       <c r="AK21" s="0">
-        <v>0.030397390605630719</v>
+        <v>0.82304872050475697</v>
       </c>
       <c r="AL21" s="0">
-        <v>0.054258730292422598</v>
+        <v>0.82319242534255643</v>
       </c>
       <c r="AM21" s="0">
-        <v>0.076510341039651222</v>
+        <v>0.82332388198470263</v>
       </c>
       <c r="AN21" s="0">
-        <v>0.097228121690554253</v>
+        <v>0.82344414409637468</v>
       </c>
       <c r="AO21" s="0">
-        <v>0.11648149903793738</v>
+        <v>0.82355412503052006</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>501</v>
+        <v>533</v>
       </c>
       <c r="B22" s="0">
-        <v>-0.47577486334376801</v>
+        <v>-76.43728048076629</v>
       </c>
       <c r="C22" s="0">
-        <v>-0.80873539099481639</v>
+        <v>0.80731883261489812</v>
       </c>
       <c r="D22" s="0">
-        <v>-0.43298766564134644</v>
+        <v>0.81339151793289022</v>
       </c>
       <c r="E22" s="0">
-        <v>-0.79029546553267283</v>
+        <v>0.80789822270202361</v>
       </c>
       <c r="F22" s="0">
-        <v>0.010988212950822047</v>
+        <v>0.82056377697372573</v>
       </c>
       <c r="G22" s="0">
-        <v>-0.82197565351654356</v>
+        <v>0.80890360855483567</v>
       </c>
       <c r="H22" s="0">
-        <v>-0.62769938149540383</v>
+        <v>0.81169812711715039</v>
       </c>
       <c r="I22" s="0">
-        <v>-0.75248873137903571</v>
+        <v>0.81004639313889082</v>
       </c>
       <c r="J22" s="0">
-        <v>-0.9705338458069469</v>
+        <v>0.80655636820602694</v>
       </c>
       <c r="K22" s="0">
-        <v>0.81843195980347683</v>
+        <v>0.8315251747779836</v>
       </c>
       <c r="L22" s="0">
-        <v>-0.80544634379026947</v>
+        <v>0.81231293014907757</v>
       </c>
       <c r="M22" s="0">
-        <v>-0.70920689799576031</v>
+        <v>0.81385642782974721</v>
       </c>
       <c r="N22" s="0">
-        <v>-0.82305389300716747</v>
+        <v>0.81326949530028958</v>
       </c>
       <c r="O22" s="0">
-        <v>-0.96879091250142102</v>
+        <v>0.81230203874587403</v>
       </c>
       <c r="P22" s="0">
-        <v>-0.78641727170991349</v>
+        <v>0.81423014009476002</v>
       </c>
       <c r="Q22" s="0">
-        <v>-0.79656923918404465</v>
+        <v>0.8143601049270579</v>
       </c>
       <c r="R22" s="0">
-        <v>-0.60790850481967917</v>
+        <v>0.81623331376267361</v>
       </c>
       <c r="S22" s="0">
-        <v>-0.52821159576599996</v>
+        <v>0.81730486078643605</v>
       </c>
       <c r="T22" s="0">
-        <v>-0.29641427749300919</v>
+        <v>0.81969764170837311</v>
       </c>
       <c r="U22" s="0">
-        <v>-0.41726124182258856</v>
+        <v>0.8189807602310204</v>
       </c>
       <c r="V22" s="0">
-        <v>-1.3778918300295309</v>
+        <v>0.81086025152206376</v>
       </c>
       <c r="W22" s="0">
-        <v>-0.30146439199430769</v>
+        <v>0.81934746350479093</v>
       </c>
       <c r="X22" s="0">
-        <v>-0.32007344831118861</v>
+        <v>0.81943510700225364</v>
       </c>
       <c r="Y22" s="0">
-        <v>-0.35382820666940357</v>
+        <v>0.81948543936920537</v>
       </c>
       <c r="Z22" s="0">
-        <v>-0.40025130511444107</v>
+        <v>0.81933490291594657</v>
       </c>
       <c r="AA22" s="0">
-        <v>-0.30114572894392538</v>
+        <v>0.82020766462325856</v>
       </c>
       <c r="AB22" s="0">
-        <v>-0.2939344962343588</v>
+        <v>0.82039511377334695</v>
       </c>
       <c r="AC22" s="0">
-        <v>-0.25599896898464586</v>
+        <v>0.82076410572433933</v>
       </c>
       <c r="AD22" s="0">
-        <v>-0.21906309180313085</v>
+        <v>0.82110260757065168</v>
       </c>
       <c r="AE22" s="0">
-        <v>-0.18334700213983698</v>
+        <v>0.82141266310501448</v>
       </c>
       <c r="AF22" s="0">
-        <v>-0.14895771229706972</v>
+        <v>0.82169669866943751</v>
       </c>
       <c r="AG22" s="0">
-        <v>-0.11600782976193853</v>
+        <v>0.82195672761153915</v>
       </c>
       <c r="AH22" s="0">
-        <v>-0.084559770315822777</v>
+        <v>0.82219475004195619</v>
       </c>
       <c r="AI22" s="0">
-        <v>-0.054638869544227309</v>
+        <v>0.82241268929672673</v>
       </c>
       <c r="AJ22" s="0">
-        <v>-0.026326318307209318</v>
+        <v>0.82261186245727813</v>
       </c>
       <c r="AK22" s="0">
-        <v>0.00042458296035238335</v>
+        <v>0.82279410284805621</v>
       </c>
       <c r="AL22" s="0">
-        <v>0.02565396136998167</v>
+        <v>0.82296096581649714</v>
       </c>
       <c r="AM22" s="0">
-        <v>0.049315617771001914</v>
+        <v>0.82311334883117526</v>
       </c>
       <c r="AN22" s="0">
-        <v>0.071509443200682823</v>
+        <v>0.82325278870773866</v>
       </c>
       <c r="AO22" s="0">
-        <v>0.092265933930751165</v>
+        <v>0.82338029278183233</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>502</v>
+        <v>534</v>
       </c>
       <c r="B23" s="0">
-        <v>-1.7860605633308562</v>
+        <v>-76.463769636154169</v>
       </c>
       <c r="C23" s="0">
-        <v>-1.239896519927727</v>
+        <v>0.79399433388901297</v>
       </c>
       <c r="D23" s="0">
-        <v>-0.89505346042239253</v>
+        <v>0.80149445355224336</v>
       </c>
       <c r="E23" s="0">
-        <v>-1.1504806283714273</v>
+        <v>0.79676259289169282</v>
       </c>
       <c r="F23" s="0">
-        <v>-0.70361570240151039</v>
+        <v>0.80612881312180307</v>
       </c>
       <c r="G23" s="0">
-        <v>-1.2163350803554143</v>
+        <v>0.79752462445068584</v>
       </c>
       <c r="H23" s="0">
-        <v>-1.0618320670424832</v>
+        <v>0.80066162125397511</v>
       </c>
       <c r="I23" s="0">
-        <v>-1.178393793419747</v>
+        <v>0.79876565669251309</v>
       </c>
       <c r="J23" s="0">
-        <v>-1.3629499396616001</v>
+        <v>0.79475396160889256</v>
       </c>
       <c r="K23" s="0">
-        <v>0.097840726129378303</v>
+        <v>0.82180469272994972</v>
       </c>
       <c r="L23" s="0">
-        <v>-1.2128024887367956</v>
+        <v>0.80352893801879866</v>
       </c>
       <c r="M23" s="0">
-        <v>-1.0465778605585778</v>
+        <v>0.80629403205490502</v>
       </c>
       <c r="N23" s="0">
-        <v>-1.1691856872248465</v>
+        <v>0.80545884886550434</v>
       </c>
       <c r="O23" s="0">
-        <v>-1.3280401681414471</v>
+        <v>0.80409412612915765</v>
       </c>
       <c r="P23" s="0">
-        <v>-1.0825049225634802</v>
+        <v>0.80812921628570344</v>
       </c>
       <c r="Q23" s="0">
-        <v>-1.0377545351567075</v>
+        <v>0.80922630939483742</v>
       </c>
       <c r="R23" s="0">
-        <v>-0.87447768148289862</v>
+        <v>0.81159824601363617</v>
       </c>
       <c r="S23" s="0">
-        <v>-0.78058820935043438</v>
+        <v>0.81308348501206051</v>
       </c>
       <c r="T23" s="0">
-        <v>-0.48303388826207189</v>
+        <v>0.81687640955734264</v>
       </c>
       <c r="U23" s="0">
-        <v>-0.70757658719746497</v>
+        <v>0.81540862751389154</v>
       </c>
       <c r="V23" s="0">
-        <v>-1.3452029511385188</v>
+        <v>0.80945946722793394</v>
       </c>
       <c r="W23" s="0">
-        <v>-0.29446144553467113</v>
+        <v>0.81885350633621357</v>
       </c>
       <c r="X23" s="0">
-        <v>-0.31810122429193732</v>
+        <v>0.81874431962203831</v>
       </c>
       <c r="Y23" s="0">
-        <v>-0.39300946517587076</v>
+        <v>0.81830390744018233</v>
       </c>
       <c r="Z23" s="0">
-        <v>-0.49438933562332149</v>
+        <v>0.81776966346359237</v>
       </c>
       <c r="AA23" s="0">
-        <v>-0.39171586630386079</v>
+        <v>0.81889147402191353</v>
       </c>
       <c r="AB23" s="0">
-        <v>-0.38598293776424475</v>
+        <v>0.81915888126755398</v>
       </c>
       <c r="AC23" s="0">
-        <v>-0.34888852512472646</v>
+        <v>0.81962581774902388</v>
       </c>
       <c r="AD23" s="0">
-        <v>-0.31193119922507406</v>
+        <v>0.82005502083969128</v>
       </c>
       <c r="AE23" s="0">
-        <v>-0.27542455325287929</v>
+        <v>0.82044899895095968</v>
       </c>
       <c r="AF23" s="0">
-        <v>-0.23957340734000201</v>
+        <v>0.82081062715911679</v>
       </c>
       <c r="AG23" s="0">
-        <v>-0.20460573376902366</v>
+        <v>0.82114224444198469</v>
       </c>
       <c r="AH23" s="0">
-        <v>-0.1706746388603336</v>
+        <v>0.82144629832076366</v>
       </c>
       <c r="AI23" s="0">
-        <v>-0.13793977895591658</v>
+        <v>0.82172482596970475</v>
       </c>
       <c r="AJ23" s="0">
-        <v>-0.10649102687413804</v>
+        <v>0.82197998501968594</v>
       </c>
       <c r="AK23" s="0">
-        <v>-0.076396846608717636</v>
+        <v>0.82221371204376448</v>
       </c>
       <c r="AL23" s="0">
-        <v>-0.047736461753236765</v>
+        <v>0.82242761004257492</v>
       </c>
       <c r="AM23" s="0">
-        <v>-0.020513510186051891</v>
+        <v>0.8226234620399514</v>
       </c>
       <c r="AN23" s="0">
-        <v>0.0052634382854758023</v>
+        <v>0.82280277705383309</v>
       </c>
       <c r="AO23" s="0">
-        <v>0.029597834683479263</v>
+        <v>0.8229669224662689</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>503</v>
+        <v>535</v>
       </c>
       <c r="B24" s="0">
-        <v>-3.1490875641051423</v>
+        <v>-76.502400826454164</v>
       </c>
       <c r="C24" s="0">
-        <v>-1.3291196650073853</v>
+        <v>0.77969416637420907</v>
       </c>
       <c r="D24" s="0">
-        <v>-0.95763756944841827</v>
+        <v>0.79120729026031911</v>
       </c>
       <c r="E24" s="0">
-        <v>-1.2474656588229438</v>
+        <v>0.78390410405732291</v>
       </c>
       <c r="F24" s="0">
-        <v>-0.86722408794613037</v>
+        <v>0.79553611208343256</v>
       </c>
       <c r="G24" s="0">
-        <v>-1.2497601986687115</v>
+        <v>0.78663353894042576</v>
       </c>
       <c r="H24" s="0">
-        <v>-1.0476184567951428</v>
+        <v>0.7924658535842809</v>
       </c>
       <c r="I24" s="0">
-        <v>-1.1615303513297603</v>
+        <v>0.7901910434494035</v>
       </c>
       <c r="J24" s="0">
-        <v>-1.3820265501981692</v>
+        <v>0.78341077829361216</v>
       </c>
       <c r="K24" s="0">
-        <v>-0.13680372462042931</v>
+        <v>0.81599475258635412</v>
       </c>
       <c r="L24" s="0">
-        <v>-1.1874971443667359</v>
+        <v>0.79667450595474987</v>
       </c>
       <c r="M24" s="0">
-        <v>-1.0604943651008167</v>
+        <v>0.80001838249969381</v>
       </c>
       <c r="N24" s="0">
-        <v>-1.1240502805796282</v>
+        <v>0.79970223000336249</v>
       </c>
       <c r="O24" s="0">
-        <v>-1.2586253909472023</v>
+        <v>0.79788640091323915</v>
       </c>
       <c r="P24" s="0">
-        <v>-0.99902279242343583</v>
+        <v>0.80356033485794298</v>
       </c>
       <c r="Q24" s="0">
-        <v>-1.0167425227345794</v>
+        <v>0.80490660654067658</v>
       </c>
       <c r="R24" s="0">
-        <v>-0.85253228897743449</v>
+        <v>0.8083920779457141</v>
       </c>
       <c r="S24" s="0">
-        <v>-0.74890424006838863</v>
+        <v>0.81077064497757356</v>
       </c>
       <c r="T24" s="0">
-        <v>-0.4691330281215636</v>
+        <v>0.81520657927703555</v>
       </c>
       <c r="U24" s="0">
-        <v>-0.74896095980738187</v>
+        <v>0.81274422071456898</v>
       </c>
       <c r="V24" s="0">
-        <v>-1.1955753709594521</v>
+        <v>0.80811315715789978</v>
       </c>
       <c r="W24" s="0">
-        <v>-0.43033887136531085</v>
+        <v>0.81660173917007794</v>
       </c>
       <c r="X24" s="0">
-        <v>-0.44720999739607475</v>
+        <v>0.81667467768478985</v>
       </c>
       <c r="Y24" s="0">
-        <v>-0.54044571015552711</v>
+        <v>0.81578654252624683</v>
       </c>
       <c r="Z24" s="0">
-        <v>-0.5752265380856505</v>
+        <v>0.81573111259079067</v>
       </c>
       <c r="AA24" s="0">
-        <v>-0.47162853237220181</v>
+        <v>0.8172024077339225</v>
       </c>
       <c r="AB24" s="0">
-        <v>-0.48973907374620146</v>
+        <v>0.81740032602691948</v>
       </c>
       <c r="AC24" s="0">
-        <v>-0.45515348932673666</v>
+        <v>0.81800729937362515</v>
       </c>
       <c r="AD24" s="0">
-        <v>-0.41961144236319042</v>
+        <v>0.81856678498458735</v>
       </c>
       <c r="AE24" s="0">
-        <v>-0.38348028497135439</v>
+        <v>0.81908188693618977</v>
       </c>
       <c r="AF24" s="0">
-        <v>-0.34712129939142194</v>
+        <v>0.81955548957061641</v>
       </c>
       <c r="AG24" s="0">
-        <v>-0.31080617042811309</v>
+        <v>0.81999085183716103</v>
       </c>
       <c r="AH24" s="0">
-        <v>-0.2748532335795974</v>
+        <v>0.82039048744202192</v>
       </c>
       <c r="AI24" s="0">
-        <v>-0.23947909379262533</v>
+        <v>0.82075728602219133</v>
       </c>
       <c r="AJ24" s="0">
-        <v>-0.2049087240350618</v>
+        <v>0.82109365274047785</v>
       </c>
       <c r="AK24" s="0">
-        <v>-0.17133757116025838</v>
+        <v>0.82140185112380348</v>
       </c>
       <c r="AL24" s="0">
-        <v>-0.13889565280093238</v>
+        <v>0.8216841844100935</v>
       </c>
       <c r="AM24" s="0">
-        <v>-0.10765142618726078</v>
+        <v>0.82194301275634929</v>
       </c>
       <c r="AN24" s="0">
-        <v>-0.077746446676479605</v>
+        <v>0.82217988753891902</v>
       </c>
       <c r="AO24" s="0">
-        <v>-0.049216128846108417</v>
+        <v>0.82239674268340845</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>504</v>
+        <v>536</v>
       </c>
       <c r="B25" s="0">
-        <v>-4.4552403480175498</v>
+        <v>-76.557907536506647</v>
       </c>
       <c r="C25" s="0">
-        <v>-1.2457954891914167</v>
+        <v>0.76254988920212041</v>
       </c>
       <c r="D25" s="0">
-        <v>-0.99075757345761295</v>
+        <v>0.77381832318116217</v>
       </c>
       <c r="E25" s="0">
-        <v>-1.298071375396429</v>
+        <v>0.76233426642227298</v>
       </c>
       <c r="F25" s="0">
-        <v>-0.91590434823970335</v>
+        <v>0.78049817775345209</v>
       </c>
       <c r="G25" s="0">
-        <v>-1.2876459855401139</v>
+        <v>0.76791251936340943</v>
       </c>
       <c r="H25" s="0">
-        <v>-1.0788542911021759</v>
+        <v>0.776802024940493</v>
       </c>
       <c r="I25" s="0">
-        <v>-1.218485298605267</v>
+        <v>0.7730893351440451</v>
       </c>
       <c r="J25" s="0">
-        <v>-1.4533565462586175</v>
+        <v>0.76247162544250724</v>
       </c>
       <c r="K25" s="0">
-        <v>-0.4106243147076255</v>
+        <v>0.80356085110091768</v>
       </c>
       <c r="L25" s="0">
-        <v>-1.2675681723628467</v>
+        <v>0.78187993121338195</v>
       </c>
       <c r="M25" s="0">
-        <v>-1.1652443137741535</v>
+        <v>0.78694553501891484</v>
       </c>
       <c r="N25" s="0">
-        <v>-1.1924541202956451</v>
+        <v>0.78815346020125909</v>
       </c>
       <c r="O25" s="0">
-        <v>-1.327689617521091</v>
+        <v>0.785261928993226</v>
       </c>
       <c r="P25" s="0">
-        <v>-1.0733801892217323</v>
+        <v>0.79308358993530359</v>
       </c>
       <c r="Q25" s="0">
-        <v>-1.0583594110876537</v>
+        <v>0.7960812554054213</v>
       </c>
       <c r="R25" s="0">
-        <v>-0.96533451745535082</v>
+        <v>0.80059054386138784</v>
       </c>
       <c r="S25" s="0">
-        <v>-0.91403995719597164</v>
+        <v>0.8035071380043004</v>
       </c>
       <c r="T25" s="0">
-        <v>-0.64109498102401452</v>
+        <v>0.81000876696777091</v>
       </c>
       <c r="U25" s="0">
-        <v>-0.96530910080661125</v>
+        <v>0.80617855511856351</v>
       </c>
       <c r="V25" s="0">
-        <v>-1.1354857717118414</v>
+        <v>0.80462505820846297</v>
       </c>
       <c r="W25" s="0">
-        <v>-0.45580308542226788</v>
+        <v>0.81475054346466247</v>
       </c>
       <c r="X25" s="0">
-        <v>-0.49869828963941881</v>
+        <v>0.81480174814987316</v>
       </c>
       <c r="Y25" s="0">
-        <v>-0.58840244262981434</v>
+        <v>0.81395038802337061</v>
       </c>
       <c r="Z25" s="0">
-        <v>-0.62412984970615804</v>
+        <v>0.81353469329071404</v>
       </c>
       <c r="AA25" s="0">
-        <v>-0.48423636047410173</v>
+        <v>0.8156341873092634</v>
       </c>
       <c r="AB25" s="0">
-        <v>-0.53979207027838738</v>
+        <v>0.81556421388244171</v>
       </c>
       <c r="AC25" s="0">
-        <v>-0.51392824540961368</v>
+        <v>0.81629121769332491</v>
       </c>
       <c r="AD25" s="0">
-        <v>-0.48609198446012958</v>
+        <v>0.81696403319930799</v>
       </c>
       <c r="AE25" s="0">
-        <v>-0.45660502244430035</v>
+        <v>0.81758597759247509</v>
       </c>
       <c r="AF25" s="0">
-        <v>-0.42581111603685229</v>
+        <v>0.81816014435958484</v>
       </c>
       <c r="AG25" s="0">
-        <v>-0.39402384287330355</v>
+        <v>0.81868980039214934</v>
       </c>
       <c r="AH25" s="0">
-        <v>-0.36158520437434877</v>
+        <v>0.81917780091095027</v>
       </c>
       <c r="AI25" s="0">
-        <v>-0.32876676915717978</v>
+        <v>0.81962730029296826</v>
       </c>
       <c r="AJ25" s="0">
-        <v>-0.29587964366879743</v>
+        <v>0.82004084401321653</v>
       </c>
       <c r="AK25" s="0">
-        <v>-0.26314110860577544</v>
+        <v>0.82042134421157209</v>
       </c>
       <c r="AL25" s="0">
-        <v>-0.23080371261526852</v>
+        <v>0.82077110544968257</v>
       </c>
       <c r="AM25" s="0">
-        <v>-0.19902671685605425</v>
+        <v>0.82109273806380889</v>
       </c>
       <c r="AN25" s="0">
-        <v>-0.16803668286127998</v>
+        <v>0.82138805022812056</v>
       </c>
       <c r="AO25" s="0">
-        <v>-0.13793460495570387</v>
+        <v>0.8216593491516111</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>505</v>
+        <v>537</v>
       </c>
       <c r="B26" s="0">
-        <v>-5.6207084853144673</v>
+        <v>-76.636726455879199</v>
       </c>
       <c r="C26" s="0">
-        <v>-1.1002098605005526</v>
+        <v>0.73838560098648043</v>
       </c>
       <c r="D26" s="0">
-        <v>-0.91315822554133674</v>
+        <v>0.75214644681167053</v>
       </c>
       <c r="E26" s="0">
-        <v>-1.0888290679672601</v>
+        <v>0.74135163002776583</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.79411476964521044</v>
+        <v>0.76362142828369495</v>
       </c>
       <c r="G26" s="0">
-        <v>-1.1555656528055063</v>
+        <v>0.74465774803161544</v>
       </c>
       <c r="H26" s="0">
-        <v>-0.9468432542269466</v>
+        <v>0.75894688383101927</v>
       </c>
       <c r="I26" s="0">
-        <v>-1.0653292260660883</v>
+        <v>0.75440544270324539</v>
       </c>
       <c r="J26" s="0">
-        <v>-1.3044089264221415</v>
+        <v>0.73753373917770426</v>
       </c>
       <c r="K26" s="0">
-        <v>-0.46274417824802505</v>
+        <v>0.79027239672470173</v>
       </c>
       <c r="L26" s="0">
-        <v>-1.1631823334777143</v>
+        <v>0.76241547276688082</v>
       </c>
       <c r="M26" s="0">
-        <v>-1.0979714873255459</v>
+        <v>0.76928407503890295</v>
       </c>
       <c r="N26" s="0">
-        <v>-1.1357336864468148</v>
+        <v>0.77171673506927707</v>
       </c>
       <c r="O26" s="0">
-        <v>-1.224291885846067</v>
+        <v>0.77059819802093577</v>
       </c>
       <c r="P26" s="0">
-        <v>-1.0349367157177833</v>
+        <v>0.77913219882583162</v>
       </c>
       <c r="Q26" s="0">
-        <v>-1.0504492096758069</v>
+        <v>0.78219734387207285</v>
       </c>
       <c r="R26" s="0">
-        <v>-1.050360050464922</v>
+        <v>0.78638680391693672</v>
       </c>
       <c r="S26" s="0">
-        <v>-1.0236207520880107</v>
+        <v>0.79165053118896955</v>
       </c>
       <c r="T26" s="0">
-        <v>-0.74532293723193899</v>
+        <v>0.80221050904083924</v>
       </c>
       <c r="U26" s="0">
-        <v>-1.1240763524955786</v>
+        <v>0.79662748680878315</v>
       </c>
       <c r="V26" s="0">
-        <v>-1.2707571571068519</v>
+        <v>0.79454635515594307</v>
       </c>
       <c r="W26" s="0">
-        <v>-0.80550902236683786</v>
+        <v>0.80545943261719266</v>
       </c>
       <c r="X26" s="0">
-        <v>-0.88296056380020094</v>
+        <v>0.80628994844054713</v>
       </c>
       <c r="Y26" s="0">
-        <v>-1.0102718361734704</v>
+        <v>0.80529012742234152</v>
       </c>
       <c r="Z26" s="0">
-        <v>-1.1009655741396147</v>
+        <v>0.80413399464798063</v>
       </c>
       <c r="AA26" s="0">
-        <v>-0.86729447439097851</v>
+        <v>0.80796952512359865</v>
       </c>
       <c r="AB26" s="0">
-        <v>-0.95047841529662991</v>
+        <v>0.80768396995163005</v>
       </c>
       <c r="AC26" s="0">
-        <v>-0.93263324912562795</v>
+        <v>0.8089572501716692</v>
       </c>
       <c r="AD26" s="0">
-        <v>-0.91039551368123295</v>
+        <v>0.81015390934371534</v>
       </c>
       <c r="AE26" s="0">
-        <v>-0.88426150150870897</v>
+        <v>0.81126740706634393</v>
       </c>
       <c r="AF26" s="0">
-        <v>-0.85460166064083243</v>
+        <v>0.81230164825439377</v>
       </c>
       <c r="AG26" s="0">
-        <v>-0.82180426262558592</v>
+        <v>0.81326090581131028</v>
       </c>
       <c r="AH26" s="0">
-        <v>-0.7862686530166636</v>
+        <v>0.81414969620132804</v>
       </c>
       <c r="AI26" s="0">
-        <v>-0.74844775664999985</v>
+        <v>0.81497211627579336</v>
       </c>
       <c r="AJ26" s="0">
-        <v>-0.70879014596343159</v>
+        <v>0.81573230392074458</v>
       </c>
       <c r="AK26" s="0">
-        <v>-0.66769952568825597</v>
+        <v>0.81643463661193549</v>
       </c>
       <c r="AL26" s="0">
-        <v>-0.62561494990160682</v>
+        <v>0.81708287365722987</v>
       </c>
       <c r="AM26" s="0">
-        <v>-0.58290622155154304</v>
+        <v>0.81768101527786552</v>
       </c>
       <c r="AN26" s="0">
-        <v>-0.5399761791858172</v>
+        <v>0.81823238131332998</v>
       </c>
       <c r="AO26" s="0">
-        <v>-0.49712369396056172</v>
+        <v>0.81874066488646857</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>506</v>
+        <v>538</v>
       </c>
       <c r="B27" s="0">
-        <v>-6.5130280583996081</v>
+        <v>-76.734852134704582</v>
       </c>
       <c r="C27" s="0">
-        <v>-0.83446930723014723</v>
+        <v>0.71751305274581489</v>
       </c>
       <c r="D27" s="0">
-        <v>-0.72607529215551392</v>
+        <v>0.73048285415649772</v>
       </c>
       <c r="E27" s="0">
-        <v>-0.88009937986906184</v>
+        <v>0.71514955868530239</v>
       </c>
       <c r="F27" s="0">
-        <v>-0.67383919077934562</v>
+        <v>0.74037526100159057</v>
       </c>
       <c r="G27" s="0">
-        <v>-0.97262419822402724</v>
+        <v>0.71320637907028905</v>
       </c>
       <c r="H27" s="0">
-        <v>-0.77666251741298387</v>
+        <v>0.73612256648636132</v>
       </c>
       <c r="I27" s="0">
-        <v>-0.9141223550127312</v>
+        <v>0.7266874331130958</v>
       </c>
       <c r="J27" s="0">
-        <v>-1.1717687175375799</v>
+        <v>0.69606599887084852</v>
       </c>
       <c r="K27" s="0">
-        <v>-0.52046714080139844</v>
+        <v>0.76455731856536358</v>
       </c>
       <c r="L27" s="0">
-        <v>-1.0607865563673347</v>
+        <v>0.7302241330299436</v>
       </c>
       <c r="M27" s="0">
-        <v>-0.9987672244053164</v>
+        <v>0.73985589673614061</v>
       </c>
       <c r="N27" s="0">
-        <v>-1.0879284088311167</v>
+        <v>0.73992644464874846</v>
       </c>
       <c r="O27" s="0">
-        <v>-1.1705069193118691</v>
+        <v>0.74014744165039081</v>
       </c>
       <c r="P27" s="0">
-        <v>-1.1256942829116023</v>
+        <v>0.74682558864975457</v>
       </c>
       <c r="Q27" s="0">
-        <v>-1.1398761553619325</v>
+        <v>0.75095171229934576</v>
       </c>
       <c r="R27" s="0">
-        <v>-1.1945368940142829</v>
+        <v>0.75429784707641501</v>
       </c>
       <c r="S27" s="0">
-        <v>-1.2185488076399367</v>
+        <v>0.76130102595139071</v>
       </c>
       <c r="T27" s="0">
-        <v>-1.0539715392105695</v>
+        <v>0.77803590655517563</v>
       </c>
       <c r="U27" s="0">
-        <v>-1.4953746170402902</v>
+        <v>0.76943195217895133</v>
       </c>
       <c r="V27" s="0">
-        <v>-1.6829142536377868</v>
+        <v>0.76607682815551281</v>
       </c>
       <c r="W27" s="0">
-        <v>-1.2750721898963937</v>
+        <v>0.78208602600097277</v>
       </c>
       <c r="X27" s="0">
-        <v>-1.4064865614034463</v>
+        <v>0.78440720799254948</v>
       </c>
       <c r="Y27" s="0">
-        <v>-1.6267348106756949</v>
+        <v>0.78326148744201218</v>
       </c>
       <c r="Z27" s="0">
-        <v>-1.764400493089457</v>
+        <v>0.78151956978607273</v>
       </c>
       <c r="AA27" s="0">
-        <v>-1.5402324172232518</v>
+        <v>0.78747233185958676</v>
       </c>
       <c r="AB27" s="0">
-        <v>-1.6559752736217095</v>
+        <v>0.78645542055130169</v>
       </c>
       <c r="AC27" s="0">
-        <v>-1.6615731065739545</v>
+        <v>0.78832642145538701</v>
       </c>
       <c r="AD27" s="0">
-        <v>-1.6566418021010534</v>
+        <v>0.79109781895064324</v>
       </c>
       <c r="AE27" s="0">
-        <v>-1.6435595423358071</v>
+        <v>0.79372096469879583</v>
       </c>
       <c r="AF27" s="0">
-        <v>-1.622598585688348</v>
+        <v>0.79617555578994148</v>
       </c>
       <c r="AG27" s="0">
-        <v>-1.5940188196032696</v>
+        <v>0.79846622782135102</v>
       </c>
       <c r="AH27" s="0">
-        <v>-1.5581773554493568</v>
+        <v>0.80059911746597379</v>
       </c>
       <c r="AI27" s="0">
-        <v>-1.5156062135052706</v>
+        <v>0.80258027932739739</v>
       </c>
       <c r="AJ27" s="0">
-        <v>-1.4668602614963977</v>
+        <v>0.80441732600403126</v>
       </c>
       <c r="AK27" s="0">
-        <v>-1.4126142014602678</v>
+        <v>0.80611758152771074</v>
       </c>
       <c r="AL27" s="0">
-        <v>-1.3536210698776703</v>
+        <v>0.80768841625976129</v>
       </c>
       <c r="AM27" s="0">
-        <v>-1.2905986874903121</v>
+        <v>0.80913796036529595</v>
       </c>
       <c r="AN27" s="0">
-        <v>-1.2243571775078337</v>
+        <v>0.81047346507262941</v>
       </c>
       <c r="AO27" s="0">
-        <v>-1.1556281802145085</v>
+        <v>0.81170274550627886</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>507</v>
+        <v>539</v>
       </c>
       <c r="B28" s="0">
-        <v>-7.1129329966667791</v>
+        <v>-76.837457214164729</v>
       </c>
       <c r="C28" s="0">
-        <v>-0.54596580193260724</v>
+        <v>0.71221812454224187</v>
       </c>
       <c r="D28" s="0">
-        <v>-0.46558287034186974</v>
+        <v>0.72718017380142896</v>
       </c>
       <c r="E28" s="0">
-        <v>-0.58085691062658573</v>
+        <v>0.70784529234313642</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.42548182579144811</v>
+        <v>0.73662379738616801</v>
       </c>
       <c r="G28" s="0">
-        <v>-0.63604810598829686</v>
+        <v>0.70515687495040724</v>
       </c>
       <c r="H28" s="0">
-        <v>-0.46785018996300892</v>
+        <v>0.73373888467788906</v>
       </c>
       <c r="I28" s="0">
-        <v>-0.59837312565108447</v>
+        <v>0.71887229404067943</v>
       </c>
       <c r="J28" s="0">
-        <v>-0.79144624561860644</v>
+        <v>0.68278362821960992</v>
       </c>
       <c r="K28" s="0">
-        <v>-0.28221201058072654</v>
+        <v>0.76482345505905214</v>
       </c>
       <c r="L28" s="0">
-        <v>-0.69772876715462873</v>
+        <v>0.7164614128456076</v>
       </c>
       <c r="M28" s="0">
-        <v>-0.67762374839114037</v>
+        <v>0.7238635337066649</v>
       </c>
       <c r="N28" s="0">
-        <v>-0.75289141904964574</v>
+        <v>0.7208122451515222</v>
       </c>
       <c r="O28" s="0">
-        <v>-0.79348787857160386</v>
+        <v>0.72243609274291509</v>
       </c>
       <c r="P28" s="0">
-        <v>-0.82508046846913619</v>
+        <v>0.72466412596892682</v>
       </c>
       <c r="Q28" s="0">
-        <v>-0.85482722128556887</v>
+        <v>0.72770056922912307</v>
       </c>
       <c r="R28" s="0">
-        <v>-0.92057153540234238</v>
+        <v>0.72739164148712465</v>
       </c>
       <c r="S28" s="0">
-        <v>-0.9347602627136018</v>
+        <v>0.73492198916244833</v>
       </c>
       <c r="T28" s="0">
-        <v>-0.86075007074290033</v>
+        <v>0.75353739998627378</v>
       </c>
       <c r="U28" s="0">
-        <v>-1.3182652918224245</v>
+        <v>0.73648791826248527</v>
       </c>
       <c r="V28" s="0">
-        <v>-1.5144137957518349</v>
+        <v>0.72978812479782673</v>
       </c>
       <c r="W28" s="0">
-        <v>-1.2578889017278605</v>
+        <v>0.7504497599830624</v>
       </c>
       <c r="X28" s="0">
-        <v>-1.4489155259666515</v>
+        <v>0.75036431382750768</v>
       </c>
       <c r="Y28" s="0">
-        <v>-1.6917581172928418</v>
+        <v>0.74845294536972029</v>
       </c>
       <c r="Z28" s="0">
-        <v>-1.8174355888721012</v>
+        <v>0.74901444432830966</v>
       </c>
       <c r="AA28" s="0">
-        <v>-1.5913434956176551</v>
+        <v>0.76126899241256951</v>
       </c>
       <c r="AB28" s="0">
-        <v>-1.7353105970548677</v>
+        <v>0.75912334494781397</v>
       </c>
       <c r="AC28" s="0">
-        <v>-1.7541377983866893</v>
+        <v>0.76024560821151788</v>
       </c>
       <c r="AD28" s="0">
-        <v>-1.7958504544148988</v>
+        <v>0.76268518325042745</v>
       </c>
       <c r="AE28" s="0">
-        <v>-1.8612894719298925</v>
+        <v>0.76600014621734802</v>
       </c>
       <c r="AF28" s="0">
-        <v>-1.9222390295402001</v>
+        <v>0.76924869518661598</v>
       </c>
       <c r="AG28" s="0">
-        <v>-1.9770791918795265</v>
+        <v>0.7724038385925287</v>
       </c>
       <c r="AH28" s="0">
-        <v>-2.0249893219130608</v>
+        <v>0.77545646143722802</v>
       </c>
       <c r="AI28" s="0">
-        <v>-2.065262651699173</v>
+        <v>0.77839891405869055</v>
       </c>
       <c r="AJ28" s="0">
-        <v>-2.0972711841939611</v>
+        <v>0.78122584606171008</v>
       </c>
       <c r="AK28" s="0">
-        <v>-2.1205590529838378</v>
+        <v>0.78393290114975478</v>
       </c>
       <c r="AL28" s="0">
-        <v>-2.1347621603263214</v>
+        <v>0.7865180103797923</v>
       </c>
       <c r="AM28" s="0">
-        <v>-2.1396780595401172</v>
+        <v>0.78898014523697091</v>
       </c>
       <c r="AN28" s="0">
-        <v>-2.135282116327609</v>
+        <v>0.79131911907959518</v>
       </c>
       <c r="AO28" s="0">
-        <v>-2.1216542049654405</v>
+        <v>0.79353629796600655</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
       <c r="B29" s="0">
-        <v>-7.4310707020244564</v>
+        <v>-76.912956955909721</v>
       </c>
       <c r="C29" s="0">
-        <v>-0.27835954804251245</v>
+        <v>0.73597009743118158</v>
       </c>
       <c r="D29" s="0">
-        <v>-0.23973666868941237</v>
+        <v>0.74568702534484965</v>
       </c>
       <c r="E29" s="0">
-        <v>-0.3299005271152527</v>
+        <v>0.72474690354537674</v>
       </c>
       <c r="F29" s="0">
-        <v>-0.21080751286849217</v>
+        <v>0.75358870924377419</v>
       </c>
       <c r="G29" s="0">
-        <v>-0.37101454942206535</v>
+        <v>0.71840313109589093</v>
       </c>
       <c r="H29" s="0">
-        <v>-0.24663631752951895</v>
+        <v>0.74749351705551048</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.33951598399481026</v>
+        <v>0.7302501543235792</v>
       </c>
       <c r="J29" s="0">
-        <v>-0.4847420892640249</v>
+        <v>0.69402789143753341</v>
       </c>
       <c r="K29" s="0">
-        <v>-0.13247913778042306</v>
+        <v>0.77388406473921745</v>
       </c>
       <c r="L29" s="0">
-        <v>-0.41407314602097522</v>
+        <v>0.72161283873748971</v>
       </c>
       <c r="M29" s="0">
-        <v>-0.39308591049649527</v>
+        <v>0.72803982426070857</v>
       </c>
       <c r="N29" s="0">
-        <v>-0.43480526803929809</v>
+        <v>0.72446363969803007</v>
       </c>
       <c r="O29" s="0">
-        <v>-0.45836650686657826</v>
+        <v>0.72423908194351572</v>
       </c>
       <c r="P29" s="0">
-        <v>-0.49498954621568664</v>
+        <v>0.72274439702224902</v>
       </c>
       <c r="Q29" s="0">
-        <v>-0.53598529255515426</v>
+        <v>0.72050389189529507</v>
       </c>
       <c r="R29" s="0">
-        <v>-0.5927090980021138</v>
+        <v>0.71659975669860887</v>
       </c>
       <c r="S29" s="0">
-        <v>-0.5932011547283913</v>
+        <v>0.72246171692657679</v>
       </c>
       <c r="T29" s="0">
-        <v>-0.55669368830768684</v>
+        <v>0.7386193809585514</v>
       </c>
       <c r="U29" s="0">
-        <v>-0.88924251058560011</v>
+        <v>0.71089407778168079</v>
       </c>
       <c r="V29" s="0">
-        <v>-1.0444949327076032</v>
+        <v>0.69990067688369717</v>
       </c>
       <c r="W29" s="0">
-        <v>-0.92426611085854427</v>
+        <v>0.71892957715606653</v>
       </c>
       <c r="X29" s="0">
-        <v>-1.1163457479893055</v>
+        <v>0.71224633126449843</v>
       </c>
       <c r="Y29" s="0">
-        <v>-1.3015630861372924</v>
+        <v>0.70498320684051985</v>
       </c>
       <c r="Z29" s="0">
-        <v>-1.4534048147688809</v>
+        <v>0.70082368756484592</v>
       </c>
       <c r="AA29" s="0">
-        <v>-1.4537544837768679</v>
+        <v>0.70965935032272631</v>
       </c>
       <c r="AB29" s="0">
-        <v>-1.6531388931756936</v>
+        <v>0.70424649898529434</v>
       </c>
       <c r="AC29" s="0">
-        <v>-1.6847892329349772</v>
+        <v>0.70537724981307226</v>
       </c>
       <c r="AD29" s="0">
-        <v>-1.7144317775745033</v>
+        <v>0.70664380696105977</v>
       </c>
       <c r="AE29" s="0">
-        <v>-1.8095422328525677</v>
+        <v>0.7070308303527828</v>
       </c>
       <c r="AF29" s="0">
-        <v>-1.9694375874415644</v>
+        <v>0.70650276011275936</v>
       </c>
       <c r="AG29" s="0">
-        <v>-2.1363556948249878</v>
+        <v>0.70629804462050938</v>
       </c>
       <c r="AH29" s="0">
-        <v>-2.3082439599284372</v>
+        <v>0.70642887647629071</v>
       </c>
       <c r="AI29" s="0">
-        <v>-2.4843304763956184</v>
+        <v>0.70687297383880465</v>
       </c>
       <c r="AJ29" s="0">
-        <v>-2.6637537316481374</v>
+        <v>0.70760703429412586</v>
       </c>
       <c r="AK29" s="0">
-        <v>-2.8455648280018959</v>
+        <v>0.70860758599471696</v>
       </c>
       <c r="AL29" s="0">
-        <v>-3.0287469320627114</v>
+        <v>0.70985084734726078</v>
       </c>
       <c r="AM29" s="0">
-        <v>-3.2122307774623353</v>
+        <v>0.7113133187065146</v>
       </c>
       <c r="AN29" s="0">
-        <v>-3.3949028104665882</v>
+        <v>0.71297190018462508</v>
       </c>
       <c r="AO29" s="0">
-        <v>-3.5756188881789637</v>
+        <v>0.71480435097503581</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>509</v>
+        <v>541</v>
       </c>
       <c r="B30" s="0">
-        <v>-7.5985644522885867</v>
+        <v>-76.961474794960026</v>
       </c>
       <c r="C30" s="0">
-        <v>-0.14404377627418527</v>
+        <v>0.75768230031967498</v>
       </c>
       <c r="D30" s="0">
-        <v>-0.10824262387552123</v>
+        <v>0.76836333053207717</v>
       </c>
       <c r="E30" s="0">
-        <v>-0.15573535263083974</v>
+        <v>0.75461028262329666</v>
       </c>
       <c r="F30" s="0">
-        <v>-0.09208079365711884</v>
+        <v>0.77305806405639976</v>
       </c>
       <c r="G30" s="0">
-        <v>-0.18687728631367348</v>
+        <v>0.7466103563613854</v>
       </c>
       <c r="H30" s="0">
-        <v>-0.10058908388307428</v>
+        <v>0.77129934600067229</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.17093630033866183</v>
+        <v>0.75293796643447786</v>
       </c>
       <c r="J30" s="0">
-        <v>-0.24729725557721324</v>
+        <v>0.72960925984192093</v>
       </c>
       <c r="K30" s="0">
-        <v>-0.023809266119033182</v>
+        <v>0.793405275497433</v>
       </c>
       <c r="L30" s="0">
-        <v>-0.21159772250833259</v>
+        <v>0.74473756978607453</v>
       </c>
       <c r="M30" s="0">
-        <v>-0.19656941893736107</v>
+        <v>0.74945443822098134</v>
       </c>
       <c r="N30" s="0">
-        <v>-0.21082624835474217</v>
+        <v>0.74770436524963158</v>
       </c>
       <c r="O30" s="0">
-        <v>-0.22908312011734286</v>
+        <v>0.74523649480056808</v>
       </c>
       <c r="P30" s="0">
-        <v>-0.25794477289949996</v>
+        <v>0.740279180240629</v>
       </c>
       <c r="Q30" s="0">
-        <v>-0.28592573084221634</v>
+        <v>0.7363104961395267</v>
       </c>
       <c r="R30" s="0">
-        <v>-0.31919023422051213</v>
+        <v>0.73083319120406809</v>
       </c>
       <c r="S30" s="0">
-        <v>-0.32874493547013428</v>
+        <v>0.73169731179810249</v>
       </c>
       <c r="T30" s="0">
-        <v>-0.31979617977859026</v>
+        <v>0.73949558428574047</v>
       </c>
       <c r="U30" s="0">
-        <v>-0.49214429970062767</v>
+        <v>0.71474025345229997</v>
       </c>
       <c r="V30" s="0">
-        <v>-0.57727276729719035</v>
+        <v>0.70099654292297464</v>
       </c>
       <c r="W30" s="0">
-        <v>-0.53524107366649332</v>
+        <v>0.7123299493904186</v>
       </c>
       <c r="X30" s="0">
-        <v>-0.6522384850653199</v>
+        <v>0.70000427758408001</v>
       </c>
       <c r="Y30" s="0">
-        <v>-0.76195845141974283</v>
+        <v>0.68811081896209447</v>
       </c>
       <c r="Z30" s="0">
-        <v>-0.81149757573169967</v>
+        <v>0.68487286356354149</v>
       </c>
       <c r="AA30" s="0">
-        <v>-0.82207602077398056</v>
+        <v>0.6894069038848859</v>
       </c>
       <c r="AB30" s="0">
-        <v>-0.94895267529725791</v>
+        <v>0.67948062091064343</v>
       </c>
       <c r="AC30" s="0">
-        <v>-0.99833954425187665</v>
+        <v>0.67752088710404079</v>
       </c>
       <c r="AD30" s="0">
-        <v>-1.0246192094435647</v>
+        <v>0.6771139896812518</v>
       </c>
       <c r="AE30" s="0">
-        <v>-1.0517530379192408</v>
+        <v>0.67671905850601488</v>
       </c>
       <c r="AF30" s="0">
-        <v>-1.1071793237219971</v>
+        <v>0.67478731433487271</v>
       </c>
       <c r="AG30" s="0">
-        <v>-1.1840156106430155</v>
+        <v>0.67205042702102813</v>
       </c>
       <c r="AH30" s="0">
-        <v>-1.2638917122036306</v>
+        <v>0.66954769031524641</v>
       </c>
       <c r="AI30" s="0">
-        <v>-1.3464805307495162</v>
+        <v>0.66728984339523267</v>
       </c>
       <c r="AJ30" s="0">
-        <v>-1.4317599520697095</v>
+        <v>0.66527341022492126</v>
       </c>
       <c r="AK30" s="0">
-        <v>-1.5196965491067795</v>
+        <v>0.66349413775634614</v>
       </c>
       <c r="AL30" s="0">
-        <v>-1.6102488938545825</v>
+        <v>0.66194707005690823</v>
       </c>
       <c r="AM30" s="0">
-        <v>-1.7033634022469777</v>
+        <v>0.66062667008971732</v>
       </c>
       <c r="AN30" s="0">
-        <v>-1.7989809601207873</v>
+        <v>0.65952656291580714</v>
       </c>
       <c r="AO30" s="0">
-        <v>-1.8970273005019784</v>
+        <v>0.65864025181579811</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>510</v>
+        <v>542</v>
       </c>
       <c r="B31" s="0">
-        <v>-7.6932518058702772</v>
+        <v>-76.99231620960235</v>
       </c>
       <c r="C31" s="0">
-        <v>-0.060948397442608819</v>
+        <v>0.77840970221328887</v>
       </c>
       <c r="D31" s="0">
-        <v>-0.02984098174645405</v>
+        <v>0.78842192508315756</v>
       </c>
       <c r="E31" s="0">
-        <v>-0.062785065239385443</v>
+        <v>0.77771993805313155</v>
       </c>
       <c r="F31" s="0">
-        <v>-0.0257740890235745</v>
+        <v>0.78983073099899637</v>
       </c>
       <c r="G31" s="0">
-        <v>-0.067570701427930299</v>
+        <v>0.77630947751236579</v>
       </c>
       <c r="H31" s="0">
-        <v>-0.024264475013722097</v>
+        <v>0.79040580979537989</v>
       </c>
       <c r="I31" s="0">
-        <v>-0.062986728433279293</v>
+        <v>0.77836293589401584</v>
       </c>
       <c r="J31" s="0">
-        <v>-0.095898469380928539</v>
+        <v>0.76706960179519768</v>
       </c>
       <c r="K31" s="0">
-        <v>0.01959737589814084</v>
+        <v>0.80476242781829843</v>
       </c>
       <c r="L31" s="0">
-        <v>-0.094123496410659285</v>
+        <v>0.7693747948150621</v>
       </c>
       <c r="M31" s="0">
-        <v>-0.075905539733758617</v>
+        <v>0.77508919161987833</v>
       </c>
       <c r="N31" s="0">
-        <v>-0.085351745551674338</v>
+        <v>0.77267408649826341</v>
       </c>
       <c r="O31" s="0">
-        <v>-0.09699640552402819</v>
+        <v>0.76994435245895465</v>
       </c>
       <c r="P31" s="0">
-        <v>-0.11622627821535404</v>
+        <v>0.76493279532241942</v>
       </c>
       <c r="Q31" s="0">
-        <v>-0.126389635619056</v>
+        <v>0.76265363153839116</v>
       </c>
       <c r="R31" s="0">
-        <v>-0.15010252784879469</v>
+        <v>0.75655962009049449</v>
       </c>
       <c r="S31" s="0">
-        <v>-0.15320571283181086</v>
+        <v>0.75647491388320864</v>
       </c>
       <c r="T31" s="0">
-        <v>-0.14579977108836648</v>
+        <v>0.7606784355926508</v>
       </c>
       <c r="U31" s="0">
-        <v>-0.22629358048356146</v>
+        <v>0.7422208667221073</v>
       </c>
       <c r="V31" s="0">
-        <v>-0.23459884703085296</v>
+        <v>0.74294746283340329</v>
       </c>
       <c r="W31" s="0">
-        <v>-0.24471759420083361</v>
+        <v>0.73919162968444752</v>
       </c>
       <c r="X31" s="0">
-        <v>-0.29787379420905807</v>
+        <v>0.72848705217360987</v>
       </c>
       <c r="Y31" s="0">
-        <v>-0.3467417799594924</v>
+        <v>0.71800080970383218</v>
       </c>
       <c r="Z31" s="0">
-        <v>-0.34440316863152232</v>
+        <v>0.72025954747390941</v>
       </c>
       <c r="AA31" s="0">
-        <v>-0.33903495413641088</v>
+        <v>0.72391623152542228</v>
       </c>
       <c r="AB31" s="0">
-        <v>-0.38414788861924343</v>
+        <v>0.71683435736466139</v>
       </c>
       <c r="AC31" s="0">
-        <v>-0.4001756399226864</v>
+        <v>0.71563442335891403</v>
       </c>
       <c r="AD31" s="0">
-        <v>-0.41324671232425664</v>
+        <v>0.71480324965668485</v>
       </c>
       <c r="AE31" s="0">
-        <v>-0.4227752970777639</v>
+        <v>0.71422502574920865</v>
       </c>
       <c r="AF31" s="0">
-        <v>-0.43249174287753489</v>
+        <v>0.71366403773880205</v>
       </c>
       <c r="AG31" s="0">
-        <v>-0.44659299591637674</v>
+        <v>0.71285467861176288</v>
       </c>
       <c r="AH31" s="0">
-        <v>-0.46379119027192361</v>
+        <v>0.71203051787186233</v>
       </c>
       <c r="AI31" s="0">
-        <v>-0.48130779846013666</v>
+        <v>0.71130888034057715</v>
       </c>
       <c r="AJ31" s="0">
-        <v>-0.49908999382880997</v>
+        <v>0.71068875868225168</v>
       </c>
       <c r="AK31" s="0">
-        <v>-0.51713960612782828</v>
+        <v>0.71016799791335961</v>
       </c>
       <c r="AL31" s="0">
-        <v>-0.53545646848593798</v>
+        <v>0.70974457674408864</v>
       </c>
       <c r="AM31" s="0">
-        <v>-0.55404235393650525</v>
+        <v>0.70941595499420729</v>
       </c>
       <c r="AN31" s="0">
-        <v>-0.57289632637829779</v>
+        <v>0.70917992605591007</v>
       </c>
       <c r="AO31" s="0">
-        <v>-0.59201835733491526</v>
+        <v>0.70903389150619589</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>511</v>
+        <v>543</v>
       </c>
       <c r="B32" s="0">
-        <v>-7.7340743461890771</v>
+        <v>-77.006485027694694</v>
       </c>
       <c r="C32" s="0">
-        <v>-0.0044302408342347145</v>
+        <v>0.79594662453079335</v>
       </c>
       <c r="D32" s="0">
-        <v>0.0091091749291551637</v>
+        <v>0.80062342192077207</v>
       </c>
       <c r="E32" s="0">
-        <v>-0.0040448682196962318</v>
+        <v>0.79604391118240203</v>
       </c>
       <c r="F32" s="0">
-        <v>0.014417934937947742</v>
+        <v>0.80246913750839732</v>
       </c>
       <c r="G32" s="0">
-        <v>-0.008790457942876008</v>
+        <v>0.79443411996078883</v>
       </c>
       <c r="H32" s="0">
-        <v>0.013757551249181243</v>
+        <v>0.80225709268951073</v>
       </c>
       <c r="I32" s="0">
-        <v>-0.0045920576904196434</v>
+        <v>0.79599719781112954</v>
       </c>
       <c r="J32" s="0">
-        <v>-0.020798453673516081</v>
+        <v>0.79023943527221763</v>
       </c>
       <c r="K32" s="0">
-        <v>0.035645805935022895</v>
+        <v>0.80988780858993248</v>
       </c>
       <c r="L32" s="0">
-        <v>-0.021177049773697262</v>
+        <v>0.79049788768768314</v>
       </c>
       <c r="M32" s="0">
-        <v>-0.0091216172317241037</v>
+        <v>0.79457325538635337</v>
       </c>
       <c r="N32" s="0">
-        <v>-0.01341549316525564</v>
+        <v>0.79321553767013797</v>
       </c>
       <c r="O32" s="0">
-        <v>-0.016098238009942523</v>
+        <v>0.79246659485626214</v>
       </c>
       <c r="P32" s="0">
-        <v>-0.028878533173974513</v>
+        <v>0.78836987058258634</v>
       </c>
       <c r="Q32" s="0">
-        <v>-0.034139357936781078</v>
+        <v>0.78677191059112472</v>
       </c>
       <c r="R32" s="0">
-        <v>-0.044415724270944271</v>
+        <v>0.78352249062729418</v>
       </c>
       <c r="S32" s="0">
-        <v>-0.046476126510930908</v>
+        <v>0.78297361182403424</v>
       </c>
       <c r="T32" s="0">
-        <v>-0.017189352232677577</v>
+        <v>0.79315463423538235</v>
       </c>
       <c r="U32" s="0">
-        <v>-0.035593876289051765</v>
+        <v>0.7881299592323302</v>
       </c>
       <c r="V32" s="0">
-        <v>-0.048965707625425882</v>
+        <v>0.7843278720359802</v>
       </c>
       <c r="W32" s="0">
-        <v>-0.0015290367455734538</v>
+        <v>0.79966924075318058</v>
       </c>
       <c r="X32" s="0">
-        <v>-0.063401838318097231</v>
+        <v>0.7802625088615498</v>
       </c>
       <c r="Y32" s="0">
-        <v>-0.030655035121311847</v>
+        <v>0.7908052984695455</v>
       </c>
       <c r="Z32" s="0">
-        <v>-0.048512635030151026</v>
+        <v>0.78526044909668247</v>
       </c>
       <c r="AA32" s="0">
-        <v>-0.077693573810736716</v>
+        <v>0.77683595534133754</v>
       </c>
       <c r="AB32" s="0">
-        <v>-0.096113085527858425</v>
+        <v>0.77230432415389894</v>
       </c>
       <c r="AC32" s="0">
-        <v>-0.10179320639650172</v>
+        <v>0.77138068603896404</v>
       </c>
       <c r="AD32" s="0">
-        <v>-0.10750822320241211</v>
+        <v>0.77051365859985277</v>
       </c>
       <c r="AE32" s="0">
-        <v>-0.11259948000366644</v>
+        <v>0.76974837073898061</v>
       </c>
       <c r="AF32" s="0">
-        <v>-0.11630316970376788</v>
+        <v>0.76920752017593308</v>
       </c>
       <c r="AG32" s="0">
-        <v>-0.11994694415847458</v>
+        <v>0.76870952836990514</v>
       </c>
       <c r="AH32" s="0">
-        <v>-0.12462249196714062</v>
+        <v>0.76816432283401004</v>
       </c>
       <c r="AI32" s="0">
-        <v>-0.13054441473096212</v>
+        <v>0.76751359988021939</v>
       </c>
       <c r="AJ32" s="0">
-        <v>-0.13654033850868758</v>
+        <v>0.7669171512718187</v>
       </c>
       <c r="AK32" s="0">
-        <v>-0.14257909535986987</v>
+        <v>0.76637945640945992</v>
       </c>
       <c r="AL32" s="0">
-        <v>-0.14866157732129862</v>
+        <v>0.76589984152984836</v>
       </c>
       <c r="AM32" s="0">
-        <v>-0.1547884377256413</v>
+        <v>0.76547757065581756</v>
       </c>
       <c r="AN32" s="0">
-        <v>-0.16096023296763504</v>
+        <v>0.76511177544020925</v>
       </c>
       <c r="AO32" s="0">
-        <v>-0.1671790621901279</v>
+        <v>0.76480113350677181</v>
       </c>
     </row>
   </sheetData>
